--- a/SAP_B1_Process_Design_Matrix.xlsx
+++ b/SAP_B1_Process_Design_Matrix.xlsx
@@ -1445,7 +1445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2745,7 +2745,7 @@
     <row r="31" ht="32" customHeight="1">
       <c r="A31" s="12" t="inlineStr">
         <is>
-          <t>2.5 [SNG-RECON]</t>
+          <t>2.5 [SNG-RECONCILIATION]</t>
         </is>
       </c>
       <c r="B31" s="12" t="inlineStr">
@@ -2792,7 +2792,7 @@
     <row r="32" ht="32" customHeight="1">
       <c r="A32" s="16" t="inlineStr">
         <is>
-          <t>2.5 [SNG-RECON]</t>
+          <t>2.5 [SNG-RECONCILIATION]</t>
         </is>
       </c>
       <c r="B32" s="16" t="inlineStr">
@@ -2833,6 +2833,147 @@
       <c r="I32" s="19" t="inlineStr">
         <is>
           <t>OIPF, IPF1, IPF2, OPCH, OJDT (200050)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="32" customHeight="1">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>2.5 [SNG-RECONCILIATION]</t>
+        </is>
+      </c>
+      <c r="B33" s="12" t="inlineStr">
+        <is>
+          <t>2.5.3</t>
+        </is>
+      </c>
+      <c r="C33" s="13" t="inlineStr">
+        <is>
+          <t>Group Report Reconciliation</t>
+        </is>
+      </c>
+      <c r="D33" s="14" t="inlineStr">
+        <is>
+          <t>new_b1 + old_b1</t>
+        </is>
+      </c>
+      <c r="E33" s="14" t="inlineStr">
+        <is>
+          <t>All Hubs</t>
+        </is>
+      </c>
+      <c r="F33" s="14" t="inlineStr">
+        <is>
+          <t>Consolidated Ledgers</t>
+        </is>
+      </c>
+      <c r="G33" s="14" t="inlineStr">
+        <is>
+          <t>Group Financial Statements</t>
+        </is>
+      </c>
+      <c r="H33" s="13" t="inlineStr">
+        <is>
+          <t>Intercompany elimination, group inventory valuation consolidation, and multi-entity profit reporting</t>
+        </is>
+      </c>
+      <c r="I33" s="15" t="inlineStr">
+        <is>
+          <t>OJDT, JDT1, OACT, Group Balance Sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="32" customHeight="1">
+      <c r="A34" s="16" t="inlineStr">
+        <is>
+          <t>2.6 [MD-MAINTENANCE]</t>
+        </is>
+      </c>
+      <c r="B34" s="16" t="inlineStr">
+        <is>
+          <t>2.6.1</t>
+        </is>
+      </c>
+      <c r="C34" s="17" t="inlineStr">
+        <is>
+          <t>SAP B1 Inventory Item Master Maintenance</t>
+        </is>
+      </c>
+      <c r="D34" s="18" t="inlineStr">
+        <is>
+          <t>new_b1 + old_b1</t>
+        </is>
+      </c>
+      <c r="E34" s="18" t="inlineStr">
+        <is>
+          <t>Master Setup</t>
+        </is>
+      </c>
+      <c r="F34" s="18" t="inlineStr">
+        <is>
+          <t>Warehouse Bins</t>
+        </is>
+      </c>
+      <c r="G34" s="18" t="inlineStr">
+        <is>
+          <t>Item Master Records</t>
+        </is>
+      </c>
+      <c r="H34" s="17" t="inlineStr">
+        <is>
+          <t>Item Code creation, valuation method setup (OITM vs OITW), purchasing/sales UoM, and barcode cataloging</t>
+        </is>
+      </c>
+      <c r="I34" s="19" t="inlineStr">
+        <is>
+          <t>OITM, OITW, ITM1, OPLN, OWHS, OBIN</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="32" customHeight="1">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>2.6 [MD-MAINTENANCE]</t>
+        </is>
+      </c>
+      <c r="B35" s="12" t="inlineStr">
+        <is>
+          <t>2.6.2</t>
+        </is>
+      </c>
+      <c r="C35" s="13" t="inlineStr">
+        <is>
+          <t>SAP B1 Business Partner Master Maintenance</t>
+        </is>
+      </c>
+      <c r="D35" s="14" t="inlineStr">
+        <is>
+          <t>new_b1 + old_b1</t>
+        </is>
+      </c>
+      <c r="E35" s="14" t="inlineStr">
+        <is>
+          <t>Master Setup</t>
+        </is>
+      </c>
+      <c r="F35" s="14" t="inlineStr">
+        <is>
+          <t>Commercial Ledger</t>
+        </is>
+      </c>
+      <c r="G35" s="14" t="inlineStr">
+        <is>
+          <t>BP Master Records</t>
+        </is>
+      </c>
+      <c r="H35" s="13" t="inlineStr">
+        <is>
+          <t>Vendor/Customer setup (OCRD/CRD1), currency assignment (USD/AUD/NZD/GBP), payment terms (OCTG), and tax group mapping</t>
+        </is>
+      </c>
+      <c r="I35" s="15" t="inlineStr">
+        <is>
+          <t>OCRD, CRD1, OCPR, OCRG, OCTG, OSTC</t>
         </is>
       </c>
     </row>

--- a/SAP_B1_Process_Design_Matrix.xlsx
+++ b/SAP_B1_Process_Design_Matrix.xlsx
@@ -692,7 +692,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>• Every international/intercompany movement between supply chain nodes (ICC, AU Whs, NZ Whs, UK) must route through an In-Transit (SIT) warehouse node (ICCSIT, NZSIT, UKSIT).
+          <t>• Every international/intercompany movement between supply chain nodes (ICC, AU Whs, NZ Whs, UK) must route through an In-Transit (SIT) warehouse node (ICCSIT, NZSIT, EuropeSIT).
 • Perpetual tracking of on-the-water stock.</t>
         </is>
       </c>
@@ -723,7 +723,7 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>• In cross-database intercompany transfers (e.g. ICCSIT in new_b1.db → FDMSYD/BDLMEL in old_b1.db), stock is discharged from SIT via Goods Issue (OIGE) in the origin database, synchronized with an Inbound Goods Receipt PO (OPDN) at the destination AU Warehouse.
+          <t>• In cross-database intercompany transfers (e.g. ICCSIT in new_b1.db → AU Warehouses in old_b1.db), stock is discharged from SIT via Goods Issue (OIGE) in the origin database, synchronized with an Inbound Goods Receipt PO (OPDN) at the destination AU Warehouse.
 • Outbound Delivery Notes (ODLN) are strictly prohibited for intercompany transfers.
 • Intercompany transfers execute strictly at source unit moving average cost (OITW.AvgPrice / MWAG), preserving zero internal profit/loss distortion.</t>
         </is>
@@ -732,7 +732,7 @@
         <is>
           <t>• Base Transfer Price = Source OITW.AvgPrice ($424.00 AUD).
 • Origin DB (new_b1.db): OIGE out from ICCSIT: Dr Intercompany AR (110020) $42,400 / Cr SIT Asset (100050) $42,400.
-• Dest DB (old_b1.db): OPDN at FDMSYD: Dr Inventory Asset (100010) $42,400 / Cr Intercompany AP (200030) $42,400.
+• Dest DB (old_b1.db): OPDN at AU Warehouse: Dr Inventory Asset (100010) $42,400 / Cr Intercompany AP (200030) $42,400.
 • Zero profit distortion; Delivery Notes (ODLN) bypassed completely.</t>
         </is>
       </c>
@@ -787,7 +787,7 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>• Delivery Notes (ODLN) are strictly forbidden as outbound documents across ALL sales order fulfillment processes (AU domestic, NZ domestic, AU-to-NZ export, UK Wayfair, and D2C Drop-Ship).
+          <t>• Delivery Notes (ODLN) are strictly forbidden as outbound documents across ALL sales order fulfillment processes (AU domestic, NZ domestic, AU-to-NZ export, EuropeMarketPlace, and D2C Drop-Ship).
 • Outbound customer orders must generate Direct AR Tax Invoices (OINV) created directly against the Sales Order (ORDR).
 • Customer receivable settlement (Incoming Payments / ORCT) and banking cash reconciliation are strictly OUT OF SCOPE of all operational supply chain processes.
 • The Direct AR Tax Invoice (OINV) concurrently consolidates stock deduction (OnHand), COGS recognition, revenue posting, and tax into a single unified financial journal entry (OJDT), establishing the open customer receivable for downstream corporate treasury.</t>
@@ -825,7 +825,7 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>• For all stock movements transferring from a physical warehouse to a Stock-in-Transit (SIT) warehouse node (ICCSIT, NZSIT, UKSIT), an Inventory Transfer Request (OWTQ) must always be created first to reserve stock (OITW.IsCommited) and transmit picking instructions to the warehouse.
+          <t>• For all stock movements transferring from a physical warehouse to a Stock-in-Transit (SIT) warehouse node (ICCSIT, NZSIT, EuropeSIT), an Inventory Transfer Request (OWTQ) must always be created first to reserve stock (OITW.IsCommited) and transmit picking instructions to the warehouse.
 • The warehouse operator completes physical picking and staging against the OWTQ.
 • Successful picking completion triggers the generation of the Inventory Transfer (OWTR) based directly on the OWTQ, executing the balance sheet transfer to In-Transit stock.</t>
         </is>
@@ -857,8 +857,8 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>• Single DB transfers (e.g. ICCNGB → ICCSIT or NZNTH → NZSTH): Use native OWTQ (Picking Request) → OWTR (Stock Transfer).
-• Cross-DB transfers (e.g. ICCSIT in new_b1.db → BDLMEL/FDMSYD in old_b1.db): Use Origin Goods Issue (OIGE) from SIT in new_b1.db synchronized with Inbound Goods Receipt PO (OPDN) in old_b1.db (strictly bypassing ODLN).
+          <t>• Single DB transfers (e.g. ICCChina → ICCSIT or NZNTH → NZSTH): Use native OWTQ (Picking Request) → OWTR (Stock Transfer).
+• Cross-DB transfers (e.g. ICCSIT in new_b1.db → AU Warehouse/AU Warehouse in old_b1.db): Use Origin Goods Issue (OIGE) from SIT in new_b1.db synchronized with Inbound Goods Receipt PO (OPDN) in old_b1.db (strictly bypassing ODLN).
 • Outbound customer sales in any DB: Use Direct AR Invoice (OINV) directly based on Sales Order (ORDR).</t>
         </is>
       </c>
@@ -1553,7 +1553,7 @@
       </c>
       <c r="G5" s="14" t="inlineStr">
         <is>
-          <t>FDMSYD</t>
+          <t>AU Warehouse</t>
         </is>
       </c>
       <c r="H5" s="13" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="G6" s="18" t="inlineStr">
         <is>
-          <t>FDMSYD</t>
+          <t>AU Warehouse</t>
         </is>
       </c>
       <c r="H6" s="17" t="inlineStr">
@@ -1627,7 +1627,7 @@
       </c>
       <c r="C7" s="13" t="inlineStr">
         <is>
-          <t>Factory → AU Warehouse → UK Wayfair</t>
+          <t>Factory → AU Warehouse → EuropeMarketPlace</t>
         </is>
       </c>
       <c r="D7" s="14" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="G7" s="14" t="inlineStr">
         <is>
-          <t>UKWYF</t>
+          <t>EuropeMarketPlace</t>
         </is>
       </c>
       <c r="H7" s="13" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="E8" s="18" t="inlineStr">
         <is>
-          <t>ICCNGB</t>
+          <t>ICCChina</t>
         </is>
       </c>
       <c r="F8" s="18" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="G8" s="18" t="inlineStr">
         <is>
-          <t>FDMSYD</t>
+          <t>AU Warehouse</t>
         </is>
       </c>
       <c r="H8" s="17" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="E9" s="14" t="inlineStr">
         <is>
-          <t>ICCNGB</t>
+          <t>ICCChina</t>
         </is>
       </c>
       <c r="F9" s="14" t="inlineStr">
@@ -1741,7 +1741,7 @@
       </c>
       <c r="G9" s="14" t="inlineStr">
         <is>
-          <t>FDMSYD</t>
+          <t>AU Warehouse</t>
         </is>
       </c>
       <c r="H9" s="13" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="E10" s="18" t="inlineStr">
         <is>
-          <t>ICCNGB</t>
+          <t>ICCChina</t>
         </is>
       </c>
       <c r="F10" s="18" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="E11" s="14" t="inlineStr">
         <is>
-          <t>ICCNGB</t>
+          <t>ICCChina</t>
         </is>
       </c>
       <c r="F11" s="14" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="G11" s="14" t="inlineStr">
         <is>
-          <t>FDMSYD</t>
+          <t>AU Warehouse</t>
         </is>
       </c>
       <c r="H11" s="13" t="inlineStr">
@@ -1872,7 +1872,7 @@
       </c>
       <c r="E12" s="18" t="inlineStr">
         <is>
-          <t>FDMSYD</t>
+          <t>AU Warehouse</t>
         </is>
       </c>
       <c r="F12" s="18" t="inlineStr">
@@ -1929,7 +1929,7 @@
       </c>
       <c r="G13" s="14" t="inlineStr">
         <is>
-          <t>FDMSYD</t>
+          <t>AU Warehouse</t>
         </is>
       </c>
       <c r="H13" s="13" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="C14" s="17" t="inlineStr">
         <is>
-          <t>Factory → ICC → AU Warehouse → UK Wayfair</t>
+          <t>Factory → ICC → AU Warehouse → EuropeMarketPlace</t>
         </is>
       </c>
       <c r="D14" s="18" t="inlineStr">
@@ -1966,17 +1966,17 @@
       </c>
       <c r="E14" s="18" t="inlineStr">
         <is>
-          <t>ICCNGB</t>
+          <t>ICCChina</t>
         </is>
       </c>
       <c r="F14" s="18" t="inlineStr">
         <is>
-          <t>ICCSIT + UKSIT</t>
+          <t>ICCSIT + EuropeSIT</t>
         </is>
       </c>
       <c r="G14" s="18" t="inlineStr">
         <is>
-          <t>UKWYF</t>
+          <t>EuropeMarketPlace</t>
         </is>
       </c>
       <c r="H14" s="17" t="inlineStr">
@@ -2003,7 +2003,7 @@
       </c>
       <c r="C15" s="13" t="inlineStr">
         <is>
-          <t>Factory → AU Warehouse → NZ Warehouse → UK Wayfair</t>
+          <t>Factory → AU Warehouse → NZ Warehouse → EuropeMarketPlace</t>
         </is>
       </c>
       <c r="D15" s="14" t="inlineStr">
@@ -2013,17 +2013,17 @@
       </c>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>FDMSYD</t>
+          <t>AU Warehouse</t>
         </is>
       </c>
       <c r="F15" s="14" t="inlineStr">
         <is>
-          <t>NZSIT + UKSIT</t>
+          <t>NZSIT + EuropeSIT</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr">
         <is>
-          <t>UKWYF</t>
+          <t>EuropeMarketPlace</t>
         </is>
       </c>
       <c r="H15" s="13" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="C16" s="17" t="inlineStr">
         <is>
-          <t>Factory → NZ Warehouse → AU Warehouse → UK Wayfair</t>
+          <t>Factory → NZ Warehouse → AU Warehouse → EuropeMarketPlace</t>
         </is>
       </c>
       <c r="D16" s="18" t="inlineStr">
@@ -2065,12 +2065,12 @@
       </c>
       <c r="F16" s="18" t="inlineStr">
         <is>
-          <t>NZSIT + UKSIT</t>
+          <t>NZSIT + EuropeSIT</t>
         </is>
       </c>
       <c r="G16" s="18" t="inlineStr">
         <is>
-          <t>UKWYF</t>
+          <t>EuropeMarketPlace</t>
         </is>
       </c>
       <c r="H16" s="17" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="C17" s="13" t="inlineStr">
         <is>
-          <t>Factory → ICC → AU Whs → NZ Whs → UK Wayfair</t>
+          <t>Factory → ICC → AU Whs → NZ Whs → EuropeMarketPlace</t>
         </is>
       </c>
       <c r="D17" s="14" t="inlineStr">
@@ -2107,17 +2107,17 @@
       </c>
       <c r="E17" s="14" t="inlineStr">
         <is>
-          <t>ICCNGB</t>
+          <t>ICCChina</t>
         </is>
       </c>
       <c r="F17" s="14" t="inlineStr">
         <is>
-          <t>ICCSIT + NZSIT + UKSIT</t>
+          <t>ICCSIT + NZSIT + EuropeSIT</t>
         </is>
       </c>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>UKWYF</t>
+          <t>EuropeMarketPlace</t>
         </is>
       </c>
       <c r="H17" s="13" t="inlineStr">
@@ -2144,7 +2144,7 @@
       </c>
       <c r="C18" s="17" t="inlineStr">
         <is>
-          <t>Factory → ICC → NZ Whs → AU Whs → UK Wayfair</t>
+          <t>Factory → ICC → NZ Whs → AU Whs → EuropeMarketPlace</t>
         </is>
       </c>
       <c r="D18" s="18" t="inlineStr">
@@ -2154,17 +2154,17 @@
       </c>
       <c r="E18" s="18" t="inlineStr">
         <is>
-          <t>ICCNGB</t>
+          <t>ICCChina</t>
         </is>
       </c>
       <c r="F18" s="18" t="inlineStr">
         <is>
-          <t>ICCSIT + NZSIT + UKSIT</t>
+          <t>ICCSIT + NZSIT + EuropeSIT</t>
         </is>
       </c>
       <c r="G18" s="18" t="inlineStr">
         <is>
-          <t>UKWYF</t>
+          <t>EuropeMarketPlace</t>
         </is>
       </c>
       <c r="H18" s="17" t="inlineStr">
@@ -2248,7 +2248,7 @@
       </c>
       <c r="E20" s="18" t="inlineStr">
         <is>
-          <t>ICCNGB</t>
+          <t>ICCChina</t>
         </is>
       </c>
       <c r="F20" s="18" t="inlineStr">
@@ -2285,7 +2285,7 @@
       </c>
       <c r="C21" s="13" t="inlineStr">
         <is>
-          <t>Factory → UK Wayfair</t>
+          <t>Factory → EuropeMarketPlace</t>
         </is>
       </c>
       <c r="D21" s="14" t="inlineStr">
@@ -2305,7 +2305,7 @@
       </c>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>UKWYF</t>
+          <t>EuropeMarketPlace</t>
         </is>
       </c>
       <c r="H21" s="13" t="inlineStr">
@@ -2332,7 +2332,7 @@
       </c>
       <c r="C22" s="17" t="inlineStr">
         <is>
-          <t>Factory → ICC → UK Wayfair</t>
+          <t>Factory → ICC → EuropeMarketPlace</t>
         </is>
       </c>
       <c r="D22" s="18" t="inlineStr">
@@ -2342,17 +2342,17 @@
       </c>
       <c r="E22" s="18" t="inlineStr">
         <is>
-          <t>ICCNGB</t>
+          <t>ICCChina</t>
         </is>
       </c>
       <c r="F22" s="18" t="inlineStr">
         <is>
-          <t>UKSIT</t>
+          <t>EuropeSIT</t>
         </is>
       </c>
       <c r="G22" s="18" t="inlineStr">
         <is>
-          <t>UKWYF</t>
+          <t>EuropeMarketPlace</t>
         </is>
       </c>
       <c r="H22" s="17" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="C23" s="13" t="inlineStr">
         <is>
-          <t>Factory → NZ Warehouse → UK Wayfair</t>
+          <t>Factory → NZ Warehouse → EuropeMarketPlace</t>
         </is>
       </c>
       <c r="D23" s="14" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="F23" s="14" t="inlineStr">
         <is>
-          <t>UKSIT</t>
+          <t>EuropeSIT</t>
         </is>
       </c>
       <c r="G23" s="14" t="inlineStr">
         <is>
-          <t>UKWYF</t>
+          <t>EuropeMarketPlace</t>
         </is>
       </c>
       <c r="H23" s="13" t="inlineStr">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="C24" s="17" t="inlineStr">
         <is>
-          <t>Factory → ICC → NZ Warehouse → UK Wayfair</t>
+          <t>Factory → ICC → NZ Warehouse → EuropeMarketPlace</t>
         </is>
       </c>
       <c r="D24" s="18" t="inlineStr">
@@ -2436,22 +2436,22 @@
       </c>
       <c r="E24" s="18" t="inlineStr">
         <is>
-          <t>ICCNGB</t>
+          <t>ICCChina</t>
         </is>
       </c>
       <c r="F24" s="18" t="inlineStr">
         <is>
-          <t>ICCSIT + UKSIT</t>
+          <t>ICCSIT + EuropeSIT</t>
         </is>
       </c>
       <c r="G24" s="18" t="inlineStr">
         <is>
-          <t>UKWYF</t>
+          <t>EuropeMarketPlace</t>
         </is>
       </c>
       <c r="H24" s="17" t="inlineStr">
         <is>
-          <t>Two-Stage Stacked at NZ ($522) + UK Freight into UKWYF ($560)</t>
+          <t>Two-Stage Stacked at NZ ($522) + UK Freight into EuropeMarketPlace ($560)</t>
         </is>
       </c>
       <c r="I24" s="19" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="E25" s="14" t="inlineStr">
         <is>
-          <t>ICCNGB</t>
+          <t>ICCChina</t>
         </is>
       </c>
       <c r="F25" s="14" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="E26" s="18" t="inlineStr">
         <is>
-          <t>ICCNGB</t>
+          <t>ICCChina</t>
         </is>
       </c>
       <c r="F26" s="18" t="inlineStr">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="E27" s="14" t="inlineStr">
         <is>
-          <t>ICCNGB</t>
+          <t>ICCChina</t>
         </is>
       </c>
       <c r="F27" s="14" t="inlineStr">
@@ -2624,7 +2624,7 @@
       </c>
       <c r="E28" s="18" t="inlineStr">
         <is>
-          <t>ICCNGB</t>
+          <t>ICCChina</t>
         </is>
       </c>
       <c r="F28" s="18" t="inlineStr">
@@ -2634,7 +2634,7 @@
       </c>
       <c r="G28" s="18" t="inlineStr">
         <is>
-          <t>FDMSYD / BDLMEL</t>
+          <t>AU Warehouses</t>
         </is>
       </c>
       <c r="H28" s="17" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="E29" s="14" t="inlineStr">
         <is>
-          <t>FDMSYD</t>
+          <t>AU Warehouse</t>
         </is>
       </c>
       <c r="F29" s="14" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="G29" s="14" t="inlineStr">
         <is>
-          <t>ICCNGB → AU</t>
+          <t>ICCChina → AU</t>
         </is>
       </c>
       <c r="H29" s="13" t="inlineStr">
@@ -2728,7 +2728,7 @@
       </c>
       <c r="G30" s="18" t="inlineStr">
         <is>
-          <t>FDMSYD / NZNTH</t>
+          <t>AU Warehouse / NZNTH</t>
         </is>
       </c>
       <c r="H30" s="17" t="inlineStr">
@@ -3090,7 +3090,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>[Purchasing] Issue Direct Factory PO in USD (OPOR) @ FDMSYD → [Vendor Production Commitment]</t>
+          <t>[Purchasing] Issue Direct Factory PO in USD (OPOR) @ AU Warehouse → [Vendor Production Commitment]</t>
         </is>
       </c>
       <c r="D7" s="22" t="inlineStr">
@@ -3105,7 +3105,7 @@
       </c>
       <c r="F7" s="22" t="inlineStr">
         <is>
-          <t>FDMSYD</t>
+          <t>AU Warehouse</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
@@ -3117,7 +3117,7 @@
       <c r="H7" s="5" t="inlineStr">
         <is>
           <t>• Direct PO issued in USD (DocCur='USD', PriceFC=$260.00 USD)
-• POR1.OnOrder = +100 units at FDMSYD
+• POR1.OnOrder = +100 units at AU Warehouse
 • Unit Valuation: $0.00 (Purchase commitment)</t>
         </is>
       </c>
@@ -3141,7 +3141,7 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>[Logistics] Post Inward Factory GRPO (OPDN) @ FDMSYD → [Origin Spot FX Base Cost Capitalization]</t>
+          <t>[Logistics] Post Inward Factory GRPO (OPDN) @ AU Warehouse → [Origin Spot FX Base Cost Capitalization]</t>
         </is>
       </c>
       <c r="D8" s="23" t="inlineStr">
@@ -3156,25 +3156,25 @@
       </c>
       <c r="F8" s="23" t="inlineStr">
         <is>
-          <t>FDMSYD</t>
+          <t>AU Warehouse</t>
         </is>
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>FDMSYD (old_b1.db)
+          <t>AU Warehouse (old_b1.db)
 [OnHand = 100]</t>
         </is>
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
           <t>• Spot FX conversion: $260.00 USD / 0.65 DocRate = $400.00 AUD
-• Initial OITW.AvgPrice('FDMSYD') = $400.00 AUD
+• Initial OITW.AvgPrice('AU Warehouse') = $400.00 AUD
 • PDN1.LineTotal = $40,000.00 AUD</t>
         </is>
       </c>
       <c r="I8" s="7" t="inlineStr">
         <is>
-          <t>Dr 100010 (Inventory Asset - FDMSYD) $40,000.00
+          <t>Dr 100010 (Inventory Asset - AU Warehouse) $40,000.00
 Cr 200010 (Goods Receipt Allocation Clearing) $40,000.00</t>
         </is>
       </c>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>[Finance] Accrue Destination Estimated Landed Cost (OIPF 'E') @ FDMSYD → [Provisional Ocean Freight &amp; Tariff Allocation]</t>
+          <t>[Finance] Accrue Destination Estimated Landed Cost (OIPF 'E') @ AU Warehouse → [Provisional Ocean Freight &amp; Tariff Allocation]</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
@@ -3207,25 +3207,25 @@
       </c>
       <c r="F9" s="22" t="inlineStr">
         <is>
-          <t>FDMSYD</t>
+          <t>AU Warehouse</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>FDMSYD (old_b1.db)
+          <t>AU Warehouse (old_b1.db)
 [OnHand = 100]</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
           <t>• Inbound provisional ocean freight, AU duty &amp; wharfage (+ $122.00 AUD/unit)
-• Provisional OITW.AvgPrice('FDMSYD') = $400 + $122 = $522.00 AUD
+• Provisional OITW.AvgPrice('AU Warehouse') = $400 + $122 = $522.00 AUD
 • Accrued against G/L 200050</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>Dr 100010 (Inventory Asset - FDMSYD) $12,200.00
+          <t>Dr 100010 (Inventory Asset - AU Warehouse) $12,200.00
 Cr 200050 (Estimated Landed Cost Clearing) $12,200.00</t>
         </is>
       </c>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>[Finance] Overwrite Destination Actual Landed Cost (OIPF 'A') @ FDMSYD → [Final Stock Valuation &amp; G/L 200050 Reconciled]</t>
+          <t>[Finance] Overwrite Destination Actual Landed Cost (OIPF 'A') @ AU Warehouse → [Final Stock Valuation &amp; G/L 200050 Reconciled]</t>
         </is>
       </c>
       <c r="D10" s="23" t="inlineStr">
@@ -3258,19 +3258,19 @@
       </c>
       <c r="F10" s="23" t="inlineStr">
         <is>
-          <t>FDMSYD</t>
+          <t>AU Warehouse</t>
         </is>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>FDMSYD (old_b1.db)
+          <t>AU Warehouse (old_b1.db)
 [OnHand = 100]</t>
         </is>
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
           <t>• Overwrites provisional estimate upon carrier &amp; customs broker invoice arrival
-• Final OITW.AvgPrice('FDMSYD') locked at $522.00 AUD
+• Final OITW.AvgPrice('AU Warehouse') locked at $522.00 AUD
 • Reconciles G/L 200050 clearing balance to $0.00</t>
         </is>
       </c>
@@ -3294,7 +3294,7 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>[Sales] Book Domestic Customer Sales Order (ORDR) @ FDMSYD → [Finished Goods Inventory Allocation]</t>
+          <t>[Sales] Book Domestic Customer Sales Order (ORDR) @ AU Warehouse → [Finished Goods Inventory Allocation]</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -3309,18 +3309,18 @@
       </c>
       <c r="F11" s="22" t="inlineStr">
         <is>
-          <t>FDMSYD</t>
+          <t>AU Warehouse</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>FDMSYD (old_b1.db)
+          <t>AU Warehouse (old_b1.db)
 [Reserved: IsCommited = +100]</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>• Selling price = $850.00 AUD, stock reserved in FDMSYD
+          <t>• Selling price = $850.00 AUD, stock reserved in AU Warehouse
 • Inventory unit cost remains $522.00 AUD</t>
         </is>
       </c>
@@ -3344,7 +3344,7 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>[Logistics] Post Direct AR Tax Invoice (OINV) @ FDMSYD → [Customer Dispatch &amp; Revenue Recognition]</t>
+          <t>[Logistics] Post Direct AR Tax Invoice (OINV) @ AU Warehouse → [Customer Dispatch &amp; Revenue Recognition]</t>
         </is>
       </c>
       <c r="D12" s="23" t="inlineStr">
@@ -3359,13 +3359,13 @@
       </c>
       <c r="F12" s="23" t="inlineStr">
         <is>
-          <t>FDMSYD</t>
+          <t>AU Warehouse</t>
         </is>
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
           <t>Customer Custody
-[FDMSYD OnHand = 0]</t>
+[AU Warehouse OnHand = 0]</t>
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr">
@@ -3382,7 +3382,7 @@
 Dr 500010 (Cost of Goods Sold - COGS) $52,200.00
 Cr 400010 (Sales Revenue) $85,000.00
 Cr 200020 (GST Output Tax) $8,500.00
-Cr 100010 (Inventory Asset - FDMSYD) $52,200.00</t>
+Cr 100010 (Inventory Asset - AU Warehouse) $52,200.00</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>[Purchasing] Issue Direct Factory PO in USD (OPOR) @ FDMSYD → [Vendor Production Commitment]</t>
+          <t>[Purchasing] Issue Direct Factory PO in USD (OPOR) @ AU Warehouse → [Vendor Production Commitment]</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -3421,7 +3421,7 @@
       </c>
       <c r="F15" s="22" t="inlineStr">
         <is>
-          <t>FDMSYD</t>
+          <t>AU Warehouse</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
@@ -3433,7 +3433,7 @@
       <c r="H15" s="5" t="inlineStr">
         <is>
           <t>• Direct PO issued in USD (DocCur='USD', PriceFC=$260.00 USD)
-• POR1.OnOrder = +100 units at FDMSYD
+• POR1.OnOrder = +100 units at AU Warehouse
 • Unit Valuation: $0.00 (Purchase commitment)</t>
         </is>
       </c>
@@ -3457,7 +3457,7 @@
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>[Logistics] Post Inward Factory GRPO (OPDN) @ FDMSYD → [Origin Spot FX Base Cost Capitalization]</t>
+          <t>[Logistics] Post Inward Factory GRPO (OPDN) @ AU Warehouse → [Origin Spot FX Base Cost Capitalization]</t>
         </is>
       </c>
       <c r="D16" s="23" t="inlineStr">
@@ -3472,25 +3472,25 @@
       </c>
       <c r="F16" s="23" t="inlineStr">
         <is>
-          <t>FDMSYD</t>
+          <t>AU Warehouse</t>
         </is>
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>FDMSYD (old_b1.db)
+          <t>AU Warehouse (old_b1.db)
 [OnHand = 100]</t>
         </is>
       </c>
       <c r="H16" s="7" t="inlineStr">
         <is>
           <t>• Spot FX conversion: $260.00 USD / 0.65 DocRate = $400.00 AUD
-• Initial OITW.AvgPrice('FDMSYD') = $400.00 AUD
+• Initial OITW.AvgPrice('AU Warehouse') = $400.00 AUD
 • PDN1.LineTotal = $40,000.00 AUD</t>
         </is>
       </c>
       <c r="I16" s="7" t="inlineStr">
         <is>
-          <t>Dr 100010 (Inventory Asset - FDMSYD) $40,000.00
+          <t>Dr 100010 (Inventory Asset - AU Warehouse) $40,000.00
 Cr 200010 (Goods Receipt Allocation Clearing) $40,000.00</t>
         </is>
       </c>
@@ -3508,7 +3508,7 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>[Finance] Accrue Destination Estimated Landed Cost (OIPF 'E') @ FDMSYD → [Provisional Ocean Freight &amp; Tariff Allocation]</t>
+          <t>[Finance] Accrue Destination Estimated Landed Cost (OIPF 'E') @ AU Warehouse → [Provisional Ocean Freight &amp; Tariff Allocation]</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -3523,24 +3523,24 @@
       </c>
       <c r="F17" s="22" t="inlineStr">
         <is>
-          <t>FDMSYD</t>
+          <t>AU Warehouse</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>FDMSYD (old_b1.db)
+          <t>AU Warehouse (old_b1.db)
 [OnHand = 100]</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
           <t>• Inbound provisional ocean freight, AU duty &amp; wharfage (+ $122.00 AUD/unit)
-• Provisional OITW.AvgPrice('FDMSYD') = $400 + $122 = $522.00 AUD</t>
+• Provisional OITW.AvgPrice('AU Warehouse') = $400 + $122 = $522.00 AUD</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>Dr 100010 (Inventory Asset - FDMSYD) $12,200.00
+          <t>Dr 100010 (Inventory Asset - AU Warehouse) $12,200.00
 Cr 200050 (Estimated Landed Cost Clearing) $12,200.00</t>
         </is>
       </c>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>[Finance] Overwrite Destination Actual Landed Cost (OIPF 'A') @ FDMSYD → [Final Stock Valuation &amp; G/L 200050 Reconciled]</t>
+          <t>[Finance] Overwrite Destination Actual Landed Cost (OIPF 'A') @ AU Warehouse → [Final Stock Valuation &amp; G/L 200050 Reconciled]</t>
         </is>
       </c>
       <c r="D18" s="23" t="inlineStr">
@@ -3573,19 +3573,19 @@
       </c>
       <c r="F18" s="23" t="inlineStr">
         <is>
-          <t>FDMSYD</t>
+          <t>AU Warehouse</t>
         </is>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>FDMSYD (old_b1.db)
+          <t>AU Warehouse (old_b1.db)
 [OnHand = 100]</t>
         </is>
       </c>
       <c r="H18" s="7" t="inlineStr">
         <is>
           <t>• Overwrites provisional estimate upon broker invoice arrival
-• Final OITW.AvgPrice('FDMSYD') locked at $522.00 AUD
+• Final OITW.AvgPrice('AU Warehouse') locked at $522.00 AUD
 • Reconciles G/L 200050 clearing balance to $0.00</t>
         </is>
       </c>
@@ -3609,7 +3609,7 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>[Sales] Book Cross-Border Customer Sales Order (ORDR) @ FDMSYD → [NZ Export Stock Allocation]</t>
+          <t>[Sales] Book Cross-Border Customer Sales Order (ORDR) @ AU Warehouse → [NZ Export Stock Allocation]</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -3624,19 +3624,19 @@
       </c>
       <c r="F19" s="22" t="inlineStr">
         <is>
-          <t>FDMSYD</t>
+          <t>AU Warehouse</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>FDMSYD (old_b1.db)
+          <t>AU Warehouse (old_b1.db)
 [Reserved: IsCommited = +100]</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
           <t>• Cross-border export price = $920.00 AUD (incl trans-tasman courier)
-• Stock reserved in FDMSYD; Unit valuation = $522.00 AUD</t>
+• Stock reserved in AU Warehouse; Unit valuation = $522.00 AUD</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
@@ -3659,7 +3659,7 @@
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>[Logistics] Post Direct Export AR Tax Invoice (OINV) @ FDMSYD → [Cross-Border Dispatch &amp; Zero-Rated Revenue Recognition]</t>
+          <t>[Logistics] Post Direct Export AR Tax Invoice (OINV) @ AU Warehouse → [Cross-Border Dispatch &amp; Zero-Rated Revenue Recognition]</t>
         </is>
       </c>
       <c r="D20" s="23" t="inlineStr">
@@ -3674,13 +3674,13 @@
       </c>
       <c r="F20" s="23" t="inlineStr">
         <is>
-          <t>FDMSYD</t>
+          <t>AU Warehouse</t>
         </is>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
           <t>Customer Custody
-[FDMSYD OnHand = 0]</t>
+[AU Warehouse OnHand = 0]</t>
         </is>
       </c>
       <c r="H20" s="7" t="inlineStr">
@@ -3696,14 +3696,14 @@
 Dr 110010 (Accounts Receivable - Export) $92,000.00
 Dr 500010 (Cost of Goods Sold - COGS) $52,200.00
 Cr 400010 (Sales Revenue - Cross-Border) $92,000.00
-Cr 100010 (Inventory Asset - FDMSYD) $52,200.00</t>
+Cr 100010 (Inventory Asset - AU Warehouse) $52,200.00</t>
         </is>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1">
       <c r="A22" s="21" t="inlineStr">
         <is>
-          <t>Process 2.1.3: Factory → AU Warehouse → UK Wayfair (AU Hub Long-Haul Direct Wholesale Invoicing)</t>
+          <t>Process 2.1.3: Factory → AU Warehouse → EuropeMarketPlace (AU Hub Long-Haul Direct Wholesale Invoicing)</t>
         </is>
       </c>
     </row>
@@ -3720,7 +3720,7 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>[Purchasing] Issue Direct Factory PO in USD (OPOR) @ FDMSYD → [Vendor Production Commitment]</t>
+          <t>[Purchasing] Issue Direct Factory PO in USD (OPOR) @ AU Warehouse → [Vendor Production Commitment]</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -3735,7 +3735,7 @@
       </c>
       <c r="F23" s="22" t="inlineStr">
         <is>
-          <t>FDMSYD</t>
+          <t>AU Warehouse</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>[Logistics] Post Inward Factory GRPO (OPDN) @ FDMSYD → [Origin Spot FX Base Cost Capitalization]</t>
+          <t>[Logistics] Post Inward Factory GRPO (OPDN) @ AU Warehouse → [Origin Spot FX Base Cost Capitalization]</t>
         </is>
       </c>
       <c r="D24" s="23" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="F24" s="23" t="inlineStr">
         <is>
-          <t>FDMSYD</t>
+          <t>AU Warehouse</t>
         </is>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>FDMSYD [OnHand = 100]</t>
+          <t>AU Warehouse [OnHand = 100]</t>
         </is>
       </c>
       <c r="H24" s="7" t="inlineStr">
@@ -3814,7 +3814,7 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>[Finance] Accrue AU Inward Estimated Landed Cost (OIPF 'E') @ FDMSYD → [Provisional Ocean Freight Allocation]</t>
+          <t>[Finance] Accrue AU Inward Estimated Landed Cost (OIPF 'E') @ AU Warehouse → [Provisional Ocean Freight Allocation]</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -3829,12 +3829,12 @@
       </c>
       <c r="F25" s="22" t="inlineStr">
         <is>
-          <t>FDMSYD</t>
+          <t>AU Warehouse</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>FDMSYD [OnHand = 100]</t>
+          <t>AU Warehouse [OnHand = 100]</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">
@@ -3861,7 +3861,7 @@
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>[Finance] Overwrite AU Inward Actual Landed Cost (OIPF 'A') @ FDMSYD → [AU Stock Capitalization &amp; G/L 200050 Reconciled]</t>
+          <t>[Finance] Overwrite AU Inward Actual Landed Cost (OIPF 'A') @ AU Warehouse → [AU Stock Capitalization &amp; G/L 200050 Reconciled]</t>
         </is>
       </c>
       <c r="D26" s="23" t="inlineStr">
@@ -3876,12 +3876,12 @@
       </c>
       <c r="F26" s="23" t="inlineStr">
         <is>
-          <t>FDMSYD</t>
+          <t>AU Warehouse</t>
         </is>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>FDMSYD [OnHand = 100]</t>
+          <t>AU Warehouse [OnHand = 100]</t>
         </is>
       </c>
       <c r="H26" s="7" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>[Purchasing] Create Export Inventory Transfer Request (OWTQ) @ FDMSYD → [UK Voyage Picking Allocation]</t>
+          <t>[Purchasing] Create Export Inventory Transfer Request (OWTQ) @ AU Warehouse → [UK Voyage Picking Allocation]</t>
         </is>
       </c>
       <c r="D27" s="22" t="inlineStr">
@@ -3923,12 +3923,12 @@
       </c>
       <c r="F27" s="22" t="inlineStr">
         <is>
-          <t>FDMSYD → UKSIT</t>
+          <t>AU Warehouse → EuropeSIT</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>FDMSYD [Reserved: IsCommited = +100]</t>
+          <t>AU Warehouse [Reserved: IsCommited = +100]</t>
         </is>
       </c>
       <c r="H27" s="5" t="inlineStr">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>[Logistics] Post Long-Haul Maritime Transfer (OWTR) based on OWTQ @ FDMSYD to UKSIT → [UK Ocean Transit Balance Sheet Capitalization]</t>
+          <t>[Logistics] Post Long-Haul Maritime Transfer (OWTR) based on OWTQ @ AU Warehouse to EuropeSIT → [UK Ocean Transit Balance Sheet Capitalization]</t>
         </is>
       </c>
       <c r="D28" s="23" t="inlineStr">
@@ -3970,12 +3970,12 @@
       </c>
       <c r="F28" s="23" t="inlineStr">
         <is>
-          <t>FDMSYD → UKSIT</t>
+          <t>AU Warehouse → EuropeSIT</t>
         </is>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>UKSIT (Transit)
+          <t>EuropeSIT (Transit)
 [OnHand = 100]</t>
         </is>
       </c>
@@ -4003,7 +4003,7 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>[Logistics] Post UK Port Inward GRPO (OPDN) @ UKWYF → [UK Port Arrival Inbound Clearance]</t>
+          <t>[Logistics] Post UK Port Inward GRPO (OPDN) @ EuropeMarketPlace → [UK Port Arrival Inbound Clearance]</t>
         </is>
       </c>
       <c r="D29" s="22" t="inlineStr">
@@ -4018,22 +4018,22 @@
       </c>
       <c r="F29" s="22" t="inlineStr">
         <is>
-          <t>UKWYF</t>
+          <t>EuropeMarketPlace</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>UKWYF [OnHand = 100]</t>
+          <t>EuropeMarketPlace [OnHand = 100]</t>
         </is>
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>Receives stock from UKSIT at $522.00 AUD base cost</t>
+          <t>Receives stock from EuropeSIT at $522.00 AUD base cost</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>Dr 100010 (UKWYF) $52,200 / Cr 100050 (UKSIT) $52,200</t>
+          <t>Dr 100010 (EuropeMarketPlace) $52,200 / Cr 100050 (EuropeSIT) $52,200</t>
         </is>
       </c>
     </row>
@@ -4050,7 +4050,7 @@
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>[Finance] Accrue UK Port Estimated Landed Cost (OIPF 'E') @ UKWYF → [Provisional UK Duty &amp; Wharfage Allocation]</t>
+          <t>[Finance] Accrue UK Port Estimated Landed Cost (OIPF 'E') @ EuropeMarketPlace → [Provisional UK Duty &amp; Wharfage Allocation]</t>
         </is>
       </c>
       <c r="D30" s="23" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="F30" s="23" t="inlineStr">
         <is>
-          <t>UKWYF</t>
+          <t>EuropeMarketPlace</t>
         </is>
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>UKWYF [OnHand = 100]</t>
+          <t>EuropeMarketPlace [OnHand = 100]</t>
         </is>
       </c>
       <c r="H30" s="7" t="inlineStr">
@@ -4080,7 +4080,7 @@
       </c>
       <c r="I30" s="7" t="inlineStr">
         <is>
-          <t>Dr 100010 (UKWYF) $3,800 / Cr 200050 $3,800</t>
+          <t>Dr 100010 (EuropeMarketPlace) $3,800 / Cr 200050 $3,800</t>
         </is>
       </c>
     </row>
@@ -4097,7 +4097,7 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>[Finance] Overwrite UK Port Actual Landed Cost (OIPF 'A') @ UKWYF → [Final UK Warehouse Valuation &amp; G/L 200050 Reconciled]</t>
+          <t>[Finance] Overwrite UK Port Actual Landed Cost (OIPF 'A') @ EuropeMarketPlace → [Final UK Warehouse Valuation &amp; G/L 200050 Reconciled]</t>
         </is>
       </c>
       <c r="D31" s="22" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="F31" s="22" t="inlineStr">
         <is>
-          <t>UKWYF</t>
+          <t>EuropeMarketPlace</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>UKWYF [OnHand = 100]</t>
+          <t>EuropeMarketPlace [OnHand = 100]</t>
         </is>
       </c>
       <c r="H31" s="5" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>[Sales] Book Wholesale Customer Sales Order (ORDR) @ UKWYF → [Wayfair Channel Stock Allocation]</t>
+          <t>[Sales] Book Wholesale Customer Sales Order (ORDR) @ EuropeMarketPlace → [EuropeMarketPlace Channel Stock Allocation]</t>
         </is>
       </c>
       <c r="D32" s="23" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="F32" s="23" t="inlineStr">
         <is>
-          <t>UKWYF</t>
+          <t>EuropeMarketPlace</t>
         </is>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>UKWYF [Reserved = +100]</t>
+          <t>EuropeMarketPlace [Reserved = +100]</t>
         </is>
       </c>
       <c r="H32" s="7" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>[Logistics] Post Direct Wholesale AR Invoice (OINV) @ UKWYF → [Wayfair Dispatch &amp; Channel Revenue Recognition]</t>
+          <t>[Logistics] Post Direct Wholesale AR Invoice (OINV) @ EuropeMarketPlace → [EuropeMarketPlace Dispatch &amp; Channel Revenue Recognition]</t>
         </is>
       </c>
       <c r="D33" s="22" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="F33" s="22" t="inlineStr">
         <is>
-          <t>UKWYF</t>
+          <t>EuropeMarketPlace</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>Wayfair Hub Custody
+          <t>EuropeMarketPlace Hub Custody
 [OnHand = 0]</t>
         </is>
       </c>
@@ -4226,7 +4226,7 @@
 Dr 110010 (AR) $75,000
 Dr 500010 (COGS) $56,000
 Cr 400010 (Revenue) $75,000
-Cr 100010 (UKWYF) $56,000</t>
+Cr 100010 (EuropeMarketPlace) $56,000</t>
         </is>
       </c>
     </row>
@@ -4257,7 +4257,7 @@
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>[Purchasing] Issue Factory PO in USD (OPOR) @ ICCNGB → [Vendor Production Commitment]</t>
+          <t>[Purchasing] Issue Factory PO in USD (OPOR) @ ICCChina → [Vendor Production Commitment]</t>
         </is>
       </c>
       <c r="D38" s="23" t="inlineStr">
@@ -4272,7 +4272,7 @@
       </c>
       <c r="F38" s="23" t="inlineStr">
         <is>
-          <t>ICCNGB</t>
+          <t>ICCChina</t>
         </is>
       </c>
       <c r="G38" s="7" t="inlineStr">
@@ -4305,7 +4305,7 @@
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>[Logistics] Post Inward Factory GRPO (OPDN) @ ICCNGB → [Origin Spot FX Base Cost Capitalization]</t>
+          <t>[Logistics] Post Inward Factory GRPO (OPDN) @ ICCChina → [Origin Spot FX Base Cost Capitalization]</t>
         </is>
       </c>
       <c r="D39" s="22" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="F39" s="22" t="inlineStr">
         <is>
-          <t>ICCNGB</t>
+          <t>ICCChina</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>ICCNGB [OnHand = 100]</t>
+          <t>ICCChina [OnHand = 100]</t>
         </is>
       </c>
       <c r="H39" s="5" t="inlineStr">
@@ -4335,7 +4335,7 @@
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>Dr 100040 (ICCNGB) $40,000 / Cr 200060 $40,000</t>
+          <t>Dr 100040 (ICCChina) $40,000 / Cr 200060 $40,000</t>
         </is>
       </c>
     </row>
@@ -4352,7 +4352,7 @@
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>[Finance] Accrue Origin Estimated Landed Cost (OIPF 'E') @ ICCNGB → [Provisional Origin Handling Allocation]</t>
+          <t>[Finance] Accrue Origin Estimated Landed Cost (OIPF 'E') @ ICCChina → [Provisional Origin Handling Allocation]</t>
         </is>
       </c>
       <c r="D40" s="23" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="F40" s="23" t="inlineStr">
         <is>
-          <t>ICCNGB</t>
+          <t>ICCChina</t>
         </is>
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
-          <t>ICCNGB [OnHand = 100]</t>
+          <t>ICCChina [OnHand = 100]</t>
         </is>
       </c>
       <c r="H40" s="7" t="inlineStr">
@@ -4382,7 +4382,7 @@
       </c>
       <c r="I40" s="7" t="inlineStr">
         <is>
-          <t>Dr 100040 (ICCNGB) $2,400 / Cr 200060 $2,400</t>
+          <t>Dr 100040 (ICCChina) $2,400 / Cr 200060 $2,400</t>
         </is>
       </c>
     </row>
@@ -4399,7 +4399,7 @@
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>[Finance] Capitalize Origin Actual Landed Cost (OIPF 'A') @ ICCNGB → [Source MWAG Lock]</t>
+          <t>[Finance] Capitalize Origin Actual Landed Cost (OIPF 'A') @ ICCChina → [Source MWAG Lock]</t>
         </is>
       </c>
       <c r="D41" s="22" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="F41" s="22" t="inlineStr">
         <is>
-          <t>ICCNGB</t>
+          <t>ICCChina</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>ICCNGB [OnHand = 100]</t>
+          <t>ICCChina [OnHand = 100]</t>
         </is>
       </c>
       <c r="H41" s="5" t="inlineStr">
@@ -4446,7 +4446,7 @@
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>[Purchasing] Create Inventory Transfer Request (OWTQ) @ ICCNGB → [Sea Voyage Picking Allocation]</t>
+          <t>[Purchasing] Create Inventory Transfer Request (OWTQ) @ ICCChina → [Sea Voyage Picking Allocation]</t>
         </is>
       </c>
       <c r="D42" s="23" t="inlineStr">
@@ -4461,12 +4461,12 @@
       </c>
       <c r="F42" s="23" t="inlineStr">
         <is>
-          <t>ICCNGB → ICCSIT</t>
+          <t>ICCChina → ICCSIT</t>
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
-          <t>ICCNGB [Allocated:
+          <t>ICCChina [Allocated:
 IsCommited = +100,
 OnHand = 100]</t>
         </is>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>[Logistics] Post In-Transit Stock Transfer (OWTR) based on OWTQ @ ICCNGB to ICCSIT → [Goods In-Transit Balance Sheet Capitalization]</t>
+          <t>[Logistics] Post In-Transit Stock Transfer (OWTR) based on OWTQ @ ICCChina to ICCSIT → [Goods In-Transit Balance Sheet Capitalization]</t>
         </is>
       </c>
       <c r="D43" s="22" t="inlineStr">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="F43" s="22" t="inlineStr">
         <is>
-          <t>ICCNGB → ICCSIT</t>
+          <t>ICCChina → ICCSIT</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
@@ -4519,7 +4519,7 @@
           <t>ICCSIT (new_b1.db)
 [On the Water:
 OnHand = 100,
-ICCNGB IsCommited = 0]</t>
+ICCChina IsCommited = 0]</t>
         </is>
       </c>
       <c r="H43" s="5" t="inlineStr">
@@ -4530,7 +4530,7 @@
       <c r="I43" s="5" t="inlineStr">
         <is>
           <t>Dr 100050 (In-Transit Asset - ICCSIT) $42,400.00
-Cr 100040 (Inventory Asset - ICCNGB) $42,400.00</t>
+Cr 100040 (Inventory Asset - ICCChina) $42,400.00</t>
         </is>
       </c>
     </row>
@@ -4547,7 +4547,7 @@
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>[Purchasing] Issue Intercompany Tracking PO in AUD (OPOR) @ FDMSYD → [Vessel Voyage &amp; Container Inbound Tracking]</t>
+          <t>[Purchasing] Issue Intercompany Tracking PO in AUD (OPOR) @ AU Warehouse → [Vessel Voyage &amp; Container Inbound Tracking]</t>
         </is>
       </c>
       <c r="D44" s="23" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="F44" s="23" t="inlineStr">
         <is>
-          <t>FDMSYD / BDLMEL</t>
+          <t>AU Warehouses</t>
         </is>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
-          <t>FDMSYD (old_b1.db)
+          <t>AU Warehouse (old_b1.db)
 [Tracking Open PO:
 OnOrder = +100]</t>
         </is>
@@ -4597,7 +4597,7 @@
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>[Logistics] Post Cross-DB Intercompany GRPO (OPDN) Synchronized with Origin Goods Issue (OIGE) @ FDMSYD → [AU Port Arrival Inbound Clearance]</t>
+          <t>[Logistics] Post Cross-DB Intercompany GRPO (OPDN) Synchronized with Origin Goods Issue (OIGE) @ AU Warehouse → [AU Port Arrival Inbound Clearance]</t>
         </is>
       </c>
       <c r="D45" s="22" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="F45" s="22" t="inlineStr">
         <is>
-          <t>ICCSIT → FDMSYD/BDLMEL</t>
+          <t>ICCSIT → AU Warehouses</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>FDMSYD / BDLMEL
+          <t>AU Warehouses
 [OnHand = 100; ICCSIT = 0]</t>
         </is>
       </c>
@@ -4649,7 +4649,7 @@
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>[Finance] Accrue Destination Estimated Landed Cost (OIPF 'E') @ FDMSYD → [Provisional Ocean Freight Allocation]</t>
+          <t>[Finance] Accrue Destination Estimated Landed Cost (OIPF 'E') @ AU Warehouse → [Provisional Ocean Freight Allocation]</t>
         </is>
       </c>
       <c r="D46" s="23" t="inlineStr">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="F46" s="23" t="inlineStr">
         <is>
-          <t>FDMSYD / BDLMEL</t>
+          <t>AU Warehouses</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
-          <t>FDMSYD / BDLMEL
+          <t>AU Warehouses
 [OnHand = 100]</t>
         </is>
       </c>
@@ -4697,7 +4697,7 @@
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>[Finance] Overwrite Destination Actual Landed Cost (OIPF 'A') @ FDMSYD → [Final Stacked Valuation &amp; G/L 200050 Reconciled]</t>
+          <t>[Finance] Overwrite Destination Actual Landed Cost (OIPF 'A') @ AU Warehouse → [Final Stacked Valuation &amp; G/L 200050 Reconciled]</t>
         </is>
       </c>
       <c r="D47" s="22" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="F47" s="22" t="inlineStr">
         <is>
-          <t>FDMSYD / BDLMEL</t>
+          <t>AU Warehouses</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>FDMSYD / BDLMEL
+          <t>AU Warehouses
 [OnHand = 100]</t>
         </is>
       </c>
@@ -4745,7 +4745,7 @@
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>[Sales] Book Domestic Customer Sales Order (ORDR) @ FDMSYD → [Finished Goods Inventory Allocation]</t>
+          <t>[Sales] Book Domestic Customer Sales Order (ORDR) @ AU Warehouse → [Finished Goods Inventory Allocation]</t>
         </is>
       </c>
       <c r="D48" s="23" t="inlineStr">
@@ -4760,12 +4760,12 @@
       </c>
       <c r="F48" s="23" t="inlineStr">
         <is>
-          <t>FDMSYD / BDLMEL</t>
+          <t>AU Warehouses</t>
         </is>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
-          <t>FDMSYD / BDLMEL
+          <t>AU Warehouses
 [Reserved = +100]</t>
         </is>
       </c>
@@ -4793,7 +4793,7 @@
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>[Logistics] Post Direct AR Tax Invoice (OINV) @ FDMSYD → [Customer Dispatch &amp; Revenue Recognition]</t>
+          <t>[Logistics] Post Direct AR Tax Invoice (OINV) @ AU Warehouse → [Customer Dispatch &amp; Revenue Recognition]</t>
         </is>
       </c>
       <c r="D49" s="22" t="inlineStr">
@@ -4808,7 +4808,7 @@
       </c>
       <c r="F49" s="22" t="inlineStr">
         <is>
-          <t>FDMSYD / BDLMEL</t>
+          <t>AU Warehouses</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
@@ -4852,7 +4852,7 @@
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>[Purchasing] Issue Factory PO in USD (OPOR) @ ICCNGB → [Vendor Production Commitment]</t>
+          <t>[Purchasing] Issue Factory PO in USD (OPOR) @ ICCChina → [Vendor Production Commitment]</t>
         </is>
       </c>
       <c r="D52" s="23" t="inlineStr">
@@ -4867,7 +4867,7 @@
       </c>
       <c r="F52" s="23" t="inlineStr">
         <is>
-          <t>ICCNGB</t>
+          <t>ICCChina</t>
         </is>
       </c>
       <c r="G52" s="7" t="inlineStr">
@@ -4902,7 +4902,7 @@
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>[Logistics] Post Inward Factory GRPO (OPDN) @ ICCNGB → [Origin Spot FX Base Cost Capitalization]</t>
+          <t>[Logistics] Post Inward Factory GRPO (OPDN) @ ICCChina → [Origin Spot FX Base Cost Capitalization]</t>
         </is>
       </c>
       <c r="D53" s="22" t="inlineStr">
@@ -4917,24 +4917,24 @@
       </c>
       <c r="F53" s="22" t="inlineStr">
         <is>
-          <t>ICCNGB</t>
+          <t>ICCChina</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>ICCNGB (new_b1.db)
+          <t>ICCChina (new_b1.db)
 [OnHand = 100]</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr">
         <is>
           <t>• Converted Base Cost = $260.00 USD / 0.65 = $400.00 AUD
-• Initial OITW.AvgPrice('ICCNGB') = $400.00 AUD</t>
+• Initial OITW.AvgPrice('ICCChina') = $400.00 AUD</t>
         </is>
       </c>
       <c r="I53" s="5" t="inlineStr">
         <is>
-          <t>Dr 100040 (Inventory Asset - ICCNGB) $40,000.00
+          <t>Dr 100040 (Inventory Asset - ICCChina) $40,000.00
 Cr 200060 (Goods Receipt Allocation Clearing) $40,000.00</t>
         </is>
       </c>
@@ -4952,7 +4952,7 @@
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>[Finance] Accrue Origin Estimated Landed Cost (OIPF 'E') @ ICCNGB → [Provisional Origin Handling Allocation]</t>
+          <t>[Finance] Accrue Origin Estimated Landed Cost (OIPF 'E') @ ICCChina → [Provisional Origin Handling Allocation]</t>
         </is>
       </c>
       <c r="D54" s="23" t="inlineStr">
@@ -4967,12 +4967,12 @@
       </c>
       <c r="F54" s="23" t="inlineStr">
         <is>
-          <t>ICCNGB</t>
+          <t>ICCChina</t>
         </is>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
-          <t>ICCNGB (new_b1.db)
+          <t>ICCChina (new_b1.db)
 [OnHand = 100]</t>
         </is>
       </c>
@@ -4984,7 +4984,7 @@
       </c>
       <c r="I54" s="7" t="inlineStr">
         <is>
-          <t>Dr 100040 (Inventory Asset - ICCNGB) $2,400.00
+          <t>Dr 100040 (Inventory Asset - ICCChina) $2,400.00
 Cr 200060 (Origin Landed Cost Clearing) $2,400.00</t>
         </is>
       </c>
@@ -5002,7 +5002,7 @@
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>[Finance] Capitalize Origin Actual Landed Cost (OIPF 'A') @ ICCNGB → [Source MWAG Lock]</t>
+          <t>[Finance] Capitalize Origin Actual Landed Cost (OIPF 'A') @ ICCChina → [Source MWAG Lock]</t>
         </is>
       </c>
       <c r="D55" s="22" t="inlineStr">
@@ -5017,19 +5017,19 @@
       </c>
       <c r="F55" s="22" t="inlineStr">
         <is>
-          <t>ICCNGB</t>
+          <t>ICCChina</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>ICCNGB (new_b1.db)
+          <t>ICCChina (new_b1.db)
 [OnHand = 100]</t>
         </is>
       </c>
       <c r="H55" s="5" t="inlineStr">
         <is>
           <t>• Reconciles actual origin broker invoices
-• Locks OITW.AvgPrice('ICCNGB') = $424.00 AUD</t>
+• Locks OITW.AvgPrice('ICCChina') = $424.00 AUD</t>
         </is>
       </c>
       <c r="I55" s="5" t="inlineStr">
@@ -5052,7 +5052,7 @@
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>[Purchasing] Create Inventory Transfer Request (OWTQ) @ ICCNGB → [Sea Voyage Picking Allocation]</t>
+          <t>[Purchasing] Create Inventory Transfer Request (OWTQ) @ ICCChina → [Sea Voyage Picking Allocation]</t>
         </is>
       </c>
       <c r="D56" s="23" t="inlineStr">
@@ -5067,12 +5067,12 @@
       </c>
       <c r="F56" s="23" t="inlineStr">
         <is>
-          <t>ICCNGB → ICCSIT</t>
+          <t>ICCChina → ICCSIT</t>
         </is>
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
-          <t>ICCNGB (new_b1.db)
+          <t>ICCChina (new_b1.db)
 [Allocated:
 IsCommited = +100,
 OnHand = 100]</t>
@@ -5104,7 +5104,7 @@
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>[Logistics] Post In-Transit Stock Transfer (OWTR) based on OWTQ @ ICCNGB to ICCSIT → [Goods In-Transit Balance Sheet Capitalization]</t>
+          <t>[Logistics] Post In-Transit Stock Transfer (OWTR) based on OWTQ @ ICCChina to ICCSIT → [Goods In-Transit Balance Sheet Capitalization]</t>
         </is>
       </c>
       <c r="D57" s="22" t="inlineStr">
@@ -5119,7 +5119,7 @@
       </c>
       <c r="F57" s="22" t="inlineStr">
         <is>
-          <t>ICCNGB → ICCSIT</t>
+          <t>ICCChina → ICCSIT</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
@@ -5127,7 +5127,7 @@
           <t>ICCSIT (new_b1.db)
 [On the Water:
 OnHand = 100,
-ICCNGB IsCommited = 0]</t>
+ICCChina IsCommited = 0]</t>
         </is>
       </c>
       <c r="H57" s="5" t="inlineStr">
@@ -5139,7 +5139,7 @@
       <c r="I57" s="5" t="inlineStr">
         <is>
           <t>Dr 100050 (In-Transit Asset - ICCSIT) $42,400.00
-Cr 100040 (Inventory Asset - ICCNGB) $42,400.00</t>
+Cr 100040 (Inventory Asset - ICCChina) $42,400.00</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>[Purchasing] Issue Intercompany Tracking PO in AUD (OPOR) @ FDMSYD → [Vessel Voyage &amp; Container Inbound Tracking]</t>
+          <t>[Purchasing] Issue Intercompany Tracking PO in AUD (OPOR) @ AU Warehouse → [Vessel Voyage &amp; Container Inbound Tracking]</t>
         </is>
       </c>
       <c r="D58" s="23" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="F58" s="23" t="inlineStr">
         <is>
-          <t>FDMSYD / BDLMEL</t>
+          <t>AU Warehouses</t>
         </is>
       </c>
       <c r="G58" s="7" t="inlineStr">
         <is>
-          <t>FDMSYD (old_b1.db)
+          <t>AU Warehouse (old_b1.db)
 [Tracking Open PO:
 OnOrder = +100]</t>
         </is>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>[Logistics] Post Cross-DB Intercompany GRPO (OPDN) Synchronized with Origin Goods Issue (OIGE) @ FDMSYD → [AU Port Arrival Inbound Clearance]</t>
+          <t>[Logistics] Post Cross-DB Intercompany GRPO (OPDN) Synchronized with Origin Goods Issue (OIGE) @ AU Warehouse → [AU Port Arrival Inbound Clearance]</t>
         </is>
       </c>
       <c r="D59" s="22" t="inlineStr">
@@ -5224,12 +5224,12 @@
       </c>
       <c r="F59" s="22" t="inlineStr">
         <is>
-          <t>ICCSIT → FDMSYD/BDLMEL</t>
+          <t>ICCSIT → AU Warehouses</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>FDMSYD / BDLMEL
+          <t>AU Warehouses
 [OnHand = 100; ICCSIT = 0]</t>
         </is>
       </c>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>[Finance] Accrue Destination Estimated Landed Cost (OIPF 'E') @ FDMSYD → [Provisional Ocean Freight Allocation]</t>
+          <t>[Finance] Accrue Destination Estimated Landed Cost (OIPF 'E') @ AU Warehouse → [Provisional Ocean Freight Allocation]</t>
         </is>
       </c>
       <c r="D60" s="23" t="inlineStr">
@@ -5279,12 +5279,12 @@
       </c>
       <c r="F60" s="23" t="inlineStr">
         <is>
-          <t>FDMSYD / BDLMEL</t>
+          <t>AU Warehouses</t>
         </is>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
-          <t>FDMSYD / BDLMEL
+          <t>AU Warehouses
 [OnHand = 100]</t>
         </is>
       </c>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>[Finance] Overwrite Destination Actual Landed Cost (OIPF 'A') @ FDMSYD → [Final Stacked Cost &amp; G/L 200050 Reconciled]</t>
+          <t>[Finance] Overwrite Destination Actual Landed Cost (OIPF 'A') @ AU Warehouse → [Final Stacked Cost &amp; G/L 200050 Reconciled]</t>
         </is>
       </c>
       <c r="D61" s="22" t="inlineStr">
@@ -5329,12 +5329,12 @@
       </c>
       <c r="F61" s="22" t="inlineStr">
         <is>
-          <t>FDMSYD / BDLMEL</t>
+          <t>AU Warehouses</t>
         </is>
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>FDMSYD / BDLMEL
+          <t>AU Warehouses
 [OnHand = 100]</t>
         </is>
       </c>
@@ -5365,7 +5365,7 @@
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>[Sales] Book Cross-Border Customer Sales Order (ORDR) @ FDMSYD → [NZ Export Stock Allocation]</t>
+          <t>[Sales] Book Cross-Border Customer Sales Order (ORDR) @ AU Warehouse → [NZ Export Stock Allocation]</t>
         </is>
       </c>
       <c r="D62" s="23" t="inlineStr">
@@ -5380,19 +5380,19 @@
       </c>
       <c r="F62" s="23" t="inlineStr">
         <is>
-          <t>FDMSYD / BDLMEL</t>
+          <t>AU Warehouses</t>
         </is>
       </c>
       <c r="G62" s="7" t="inlineStr">
         <is>
-          <t>FDMSYD / BDLMEL
+          <t>AU Warehouses
 [Reserved: IsCommited = +100]</t>
         </is>
       </c>
       <c r="H62" s="7" t="inlineStr">
         <is>
           <t>• Cross-border export price = $920.00 AUD (incl trans-tasman courier)
-• Stock reserved in FDMSYD; Unit valuation = $522.00 AUD</t>
+• Stock reserved in AU Warehouse; Unit valuation = $522.00 AUD</t>
         </is>
       </c>
       <c r="I62" s="7" t="inlineStr">
@@ -5415,7 +5415,7 @@
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>[Logistics] Post Direct Export AR Tax Invoice (OINV) @ FDMSYD → [Cross-Border Dispatch &amp; Zero-Rated Revenue Recognition]</t>
+          <t>[Logistics] Post Direct Export AR Tax Invoice (OINV) @ AU Warehouse → [Cross-Border Dispatch &amp; Zero-Rated Revenue Recognition]</t>
         </is>
       </c>
       <c r="D63" s="22" t="inlineStr">
@@ -5430,7 +5430,7 @@
       </c>
       <c r="F63" s="22" t="inlineStr">
         <is>
-          <t>FDMSYD / BDLMEL</t>
+          <t>AU Warehouses</t>
         </is>
       </c>
       <c r="G63" s="5" t="inlineStr">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
-          <t>[Purchasing] Issue Factory PO in USD (OPOR) @ ICCNGB → [Vendor Production Commitment]</t>
+          <t>[Purchasing] Issue Factory PO in USD (OPOR) @ ICCChina → [Vendor Production Commitment]</t>
         </is>
       </c>
       <c r="D66" s="23" t="inlineStr">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="F66" s="23" t="inlineStr">
         <is>
-          <t>ICCNGB</t>
+          <t>ICCChina</t>
         </is>
       </c>
       <c r="G66" s="7" t="inlineStr">
@@ -5523,7 +5523,7 @@
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>[Logistics] Post Inward Factory GRPO (OPDN) @ ICCNGB → [Origin Spot FX Base Cost Capitalization]</t>
+          <t>[Logistics] Post Inward Factory GRPO (OPDN) @ ICCChina → [Origin Spot FX Base Cost Capitalization]</t>
         </is>
       </c>
       <c r="D67" s="22" t="inlineStr">
@@ -5538,12 +5538,12 @@
       </c>
       <c r="F67" s="22" t="inlineStr">
         <is>
-          <t>ICCNGB</t>
+          <t>ICCChina</t>
         </is>
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>ICCNGB [OnHand = 100]</t>
+          <t>ICCChina [OnHand = 100]</t>
         </is>
       </c>
       <c r="H67" s="5" t="inlineStr">
@@ -5570,7 +5570,7 @@
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
-          <t>[Finance] Accrue Origin Estimated Landed Cost (OIPF 'E') @ ICCNGB → [Provisional Origin Handling Allocation]</t>
+          <t>[Finance] Accrue Origin Estimated Landed Cost (OIPF 'E') @ ICCChina → [Provisional Origin Handling Allocation]</t>
         </is>
       </c>
       <c r="D68" s="23" t="inlineStr">
@@ -5585,12 +5585,12 @@
       </c>
       <c r="F68" s="23" t="inlineStr">
         <is>
-          <t>ICCNGB</t>
+          <t>ICCChina</t>
         </is>
       </c>
       <c r="G68" s="7" t="inlineStr">
         <is>
-          <t>ICCNGB [OnHand = 100]</t>
+          <t>ICCChina [OnHand = 100]</t>
         </is>
       </c>
       <c r="H68" s="7" t="inlineStr">
@@ -5617,7 +5617,7 @@
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>[Finance] Capitalize Origin Actual Landed Cost (OIPF 'A') @ ICCNGB → [Source MWAG Lock]</t>
+          <t>[Finance] Capitalize Origin Actual Landed Cost (OIPF 'A') @ ICCChina → [Source MWAG Lock]</t>
         </is>
       </c>
       <c r="D69" s="22" t="inlineStr">
@@ -5632,12 +5632,12 @@
       </c>
       <c r="F69" s="22" t="inlineStr">
         <is>
-          <t>ICCNGB</t>
+          <t>ICCChina</t>
         </is>
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
-          <t>ICCNGB [OnHand = 100]</t>
+          <t>ICCChina [OnHand = 100]</t>
         </is>
       </c>
       <c r="H69" s="5" t="inlineStr">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>[Purchasing] Create Inventory Transfer Request (OWTQ) @ ICCNGB → [Sea Voyage Picking Allocation]</t>
+          <t>[Purchasing] Create Inventory Transfer Request (OWTQ) @ ICCChina → [Sea Voyage Picking Allocation]</t>
         </is>
       </c>
       <c r="D70" s="23" t="inlineStr">
@@ -5679,12 +5679,12 @@
       </c>
       <c r="F70" s="23" t="inlineStr">
         <is>
-          <t>ICCNGB → ICCSIT</t>
+          <t>ICCChina → ICCSIT</t>
         </is>
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
-          <t>ICCNGB [IsCommited = +100]</t>
+          <t>ICCChina [IsCommited = +100]</t>
         </is>
       </c>
       <c r="H70" s="7" t="inlineStr">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>[Logistics] Post In-Transit Stock Transfer (OWTR) based on OWTQ @ ICCNGB to ICCSIT → [Goods In-Transit Balance Sheet Capitalization]</t>
+          <t>[Logistics] Post In-Transit Stock Transfer (OWTR) based on OWTQ @ ICCChina to ICCSIT → [Goods In-Transit Balance Sheet Capitalization]</t>
         </is>
       </c>
       <c r="D71" s="22" t="inlineStr">
@@ -5726,7 +5726,7 @@
       </c>
       <c r="F71" s="22" t="inlineStr">
         <is>
-          <t>ICCNGB → ICCSIT</t>
+          <t>ICCChina → ICCSIT</t>
         </is>
       </c>
       <c r="G71" s="5" t="inlineStr">
@@ -5758,7 +5758,7 @@
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>[Purchasing] Issue Intercompany Tracking PO in AUD (OPOR) @ FDMSYD → [AU Port Arrival Inbound Tracking]</t>
+          <t>[Purchasing] Issue Intercompany Tracking PO in AUD (OPOR) @ AU Warehouse → [AU Port Arrival Inbound Tracking]</t>
         </is>
       </c>
       <c r="D72" s="23" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="F72" s="23" t="inlineStr">
         <is>
-          <t>FDMSYD</t>
+          <t>AU Warehouse</t>
         </is>
       </c>
       <c r="G72" s="7" t="inlineStr">
         <is>
-          <t>FDMSYD [OnOrder = +100]</t>
+          <t>AU Warehouse [OnOrder = +100]</t>
         </is>
       </c>
       <c r="H72" s="7" t="inlineStr">
@@ -5805,7 +5805,7 @@
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>[Logistics] Post Cross-DB Intercompany GRPO (OPDN) Synchronized with Origin Goods Issue (OIGE) @ FDMSYD → [AU Port Arrival Inbound Clearance]</t>
+          <t>[Logistics] Post Cross-DB Intercompany GRPO (OPDN) Synchronized with Origin Goods Issue (OIGE) @ AU Warehouse → [AU Port Arrival Inbound Clearance]</t>
         </is>
       </c>
       <c r="D73" s="22" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="F73" s="22" t="inlineStr">
         <is>
-          <t>ICCSIT → FDMSYD</t>
+          <t>ICCSIT → AU Warehouse</t>
         </is>
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>FDMSYD [OnHand = 100]</t>
+          <t>AU Warehouse [OnHand = 100]</t>
         </is>
       </c>
       <c r="H73" s="5" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>[Finance] Overwrite AU Stacked Landed Cost (OIPF 'A') @ FDMSYD → [AU Stock Capitalization &amp; G/L 200050 Reconciled]</t>
+          <t>[Finance] Overwrite AU Stacked Landed Cost (OIPF 'A') @ AU Warehouse → [AU Stock Capitalization &amp; G/L 200050 Reconciled]</t>
         </is>
       </c>
       <c r="D74" s="23" t="inlineStr">
@@ -5868,12 +5868,12 @@
       </c>
       <c r="F74" s="23" t="inlineStr">
         <is>
-          <t>FDMSYD</t>
+          <t>AU Warehouse</t>
         </is>
       </c>
       <c r="G74" s="7" t="inlineStr">
         <is>
-          <t>FDMSYD [OnHand = 100]</t>
+          <t>AU Warehouse [OnHand = 100]</t>
         </is>
       </c>
       <c r="H74" s="7" t="inlineStr">
@@ -5900,7 +5900,7 @@
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>[Purchasing] Create Trans-Tasman Transfer Request (OWTQ) @ FDMSYD → [NZ Voyage Picking Allocation]</t>
+          <t>[Purchasing] Create Trans-Tasman Transfer Request (OWTQ) @ AU Warehouse → [NZ Voyage Picking Allocation]</t>
         </is>
       </c>
       <c r="D75" s="22" t="inlineStr">
@@ -5915,12 +5915,12 @@
       </c>
       <c r="F75" s="22" t="inlineStr">
         <is>
-          <t>FDMSYD → NZSIT</t>
+          <t>AU Warehouse → NZSIT</t>
         </is>
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>FDMSYD [IsCommited = +100]</t>
+          <t>AU Warehouse [IsCommited = +100]</t>
         </is>
       </c>
       <c r="H75" s="5" t="inlineStr">
@@ -5947,7 +5947,7 @@
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
-          <t>[Logistics] Post Trans-Tasman Stock Transfer (OWTR) based on OWTQ @ FDMSYD to NZSIT → [Trans-Tasman Sea Voyage Tracking]</t>
+          <t>[Logistics] Post Trans-Tasman Stock Transfer (OWTR) based on OWTQ @ AU Warehouse to NZSIT → [Trans-Tasman Sea Voyage Tracking]</t>
         </is>
       </c>
       <c r="D76" s="23" t="inlineStr">
@@ -5962,7 +5962,7 @@
       </c>
       <c r="F76" s="23" t="inlineStr">
         <is>
-          <t>FDMSYD → NZSIT</t>
+          <t>AU Warehouse → NZSIT</t>
         </is>
       </c>
       <c r="G76" s="7" t="inlineStr">
@@ -6194,7 +6194,7 @@
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>[Purchasing] Issue Factory PO in USD (OPOR) @ ICCNGB → [Vendor Production Commitment]</t>
+          <t>[Purchasing] Issue Factory PO in USD (OPOR) @ ICCChina → [Vendor Production Commitment]</t>
         </is>
       </c>
       <c r="D83" s="22" t="inlineStr">
@@ -6209,7 +6209,7 @@
       </c>
       <c r="F83" s="22" t="inlineStr">
         <is>
-          <t>ICCNGB</t>
+          <t>ICCChina</t>
         </is>
       </c>
       <c r="G83" s="5" t="inlineStr">
@@ -6241,7 +6241,7 @@
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
-          <t>[Logistics] Post Inward Factory GRPO (OPDN) @ ICCNGB → [Origin Spot FX Base Cost Capitalization]</t>
+          <t>[Logistics] Post Inward Factory GRPO (OPDN) @ ICCChina → [Origin Spot FX Base Cost Capitalization]</t>
         </is>
       </c>
       <c r="D84" s="23" t="inlineStr">
@@ -6256,12 +6256,12 @@
       </c>
       <c r="F84" s="23" t="inlineStr">
         <is>
-          <t>ICCNGB</t>
+          <t>ICCChina</t>
         </is>
       </c>
       <c r="G84" s="7" t="inlineStr">
         <is>
-          <t>ICCNGB [OnHand = 100]</t>
+          <t>ICCChina [OnHand = 100]</t>
         </is>
       </c>
       <c r="H84" s="7" t="inlineStr">
@@ -6288,7 +6288,7 @@
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>[Finance] Capitalize Origin Actual Landed Cost (OIPF 'A') @ ICCNGB → [Source MWAG Lock]</t>
+          <t>[Finance] Capitalize Origin Actual Landed Cost (OIPF 'A') @ ICCChina → [Source MWAG Lock]</t>
         </is>
       </c>
       <c r="D85" s="22" t="inlineStr">
@@ -6303,12 +6303,12 @@
       </c>
       <c r="F85" s="22" t="inlineStr">
         <is>
-          <t>ICCNGB</t>
+          <t>ICCChina</t>
         </is>
       </c>
       <c r="G85" s="5" t="inlineStr">
         <is>
-          <t>ICCNGB [OnHand = 100]</t>
+          <t>ICCChina [OnHand = 100]</t>
         </is>
       </c>
       <c r="H85" s="5" t="inlineStr">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
-          <t>[Purchasing] Create Inventory Transfer Request (OWTQ) @ ICCNGB → [NZ Sea Voyage Picking Allocation]</t>
+          <t>[Purchasing] Create Inventory Transfer Request (OWTQ) @ ICCChina → [NZ Sea Voyage Picking Allocation]</t>
         </is>
       </c>
       <c r="D86" s="23" t="inlineStr">
@@ -6350,12 +6350,12 @@
       </c>
       <c r="F86" s="23" t="inlineStr">
         <is>
-          <t>ICCNGB → ICCSIT</t>
+          <t>ICCChina → ICCSIT</t>
         </is>
       </c>
       <c r="G86" s="7" t="inlineStr">
         <is>
-          <t>ICCNGB [IsCommited = +100]</t>
+          <t>ICCChina [IsCommited = +100]</t>
         </is>
       </c>
       <c r="H86" s="7" t="inlineStr">
@@ -6382,7 +6382,7 @@
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>[Logistics] Post In-Transit Stock Transfer (OWTR) based on OWTQ @ ICCNGB to ICCSIT → [Ocean Transit Balance Sheet Capitalization]</t>
+          <t>[Logistics] Post In-Transit Stock Transfer (OWTR) based on OWTQ @ ICCChina to ICCSIT → [Ocean Transit Balance Sheet Capitalization]</t>
         </is>
       </c>
       <c r="D87" s="22" t="inlineStr">
@@ -6397,7 +6397,7 @@
       </c>
       <c r="F87" s="22" t="inlineStr">
         <is>
-          <t>ICCNGB → ICCSIT</t>
+          <t>ICCChina → ICCSIT</t>
         </is>
       </c>
       <c r="G87" s="5" t="inlineStr">
@@ -6617,7 +6617,7 @@
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
-          <t>[Logistics] Post AU Cross-DB Intercompany GRPO (OPDN) Synchronized with Origin Goods Issue (OIGE) @ FDMSYD → [AU Port Inbound Clearance]</t>
+          <t>[Logistics] Post AU Cross-DB Intercompany GRPO (OPDN) Synchronized with Origin Goods Issue (OIGE) @ AU Warehouse → [AU Port Inbound Clearance]</t>
         </is>
       </c>
       <c r="D92" s="23" t="inlineStr">
@@ -6632,12 +6632,12 @@
       </c>
       <c r="F92" s="23" t="inlineStr">
         <is>
-          <t>NZSIT → FDMSYD</t>
+          <t>NZSIT → AU Warehouse</t>
         </is>
       </c>
       <c r="G92" s="7" t="inlineStr">
         <is>
-          <t>FDMSYD [OnHand = 100]</t>
+          <t>AU Warehouse [OnHand = 100]</t>
         </is>
       </c>
       <c r="H92" s="7" t="inlineStr">
@@ -6665,7 +6665,7 @@
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>[Finance] Overwrite AU Inbound Landed Cost (OIPF 'A') @ FDMSYD → [Final AU Valuation &amp; G/L 200050 Reconciled]</t>
+          <t>[Finance] Overwrite AU Inbound Landed Cost (OIPF 'A') @ AU Warehouse → [Final AU Valuation &amp; G/L 200050 Reconciled]</t>
         </is>
       </c>
       <c r="D93" s="22" t="inlineStr">
@@ -6680,12 +6680,12 @@
       </c>
       <c r="F93" s="22" t="inlineStr">
         <is>
-          <t>FDMSYD</t>
+          <t>AU Warehouse</t>
         </is>
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>FDMSYD [OnHand = 100]</t>
+          <t>AU Warehouse [OnHand = 100]</t>
         </is>
       </c>
       <c r="H93" s="5" t="inlineStr">
@@ -6712,7 +6712,7 @@
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
-          <t>[Sales] Book Domestic Customer Sales Order (ORDR) @ FDMSYD → [Finished Goods Inventory Allocation]</t>
+          <t>[Sales] Book Domestic Customer Sales Order (ORDR) @ AU Warehouse → [Finished Goods Inventory Allocation]</t>
         </is>
       </c>
       <c r="D94" s="23" t="inlineStr">
@@ -6727,12 +6727,12 @@
       </c>
       <c r="F94" s="23" t="inlineStr">
         <is>
-          <t>FDMSYD</t>
+          <t>AU Warehouse</t>
         </is>
       </c>
       <c r="G94" s="7" t="inlineStr">
         <is>
-          <t>FDMSYD [Reserved = +100]</t>
+          <t>AU Warehouse [Reserved = +100]</t>
         </is>
       </c>
       <c r="H94" s="7" t="inlineStr">
@@ -6759,7 +6759,7 @@
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>[Logistics] Post Direct AR Tax Invoice (OINV) @ FDMSYD → [Customer Dispatch &amp; Revenue Recognition]</t>
+          <t>[Logistics] Post Direct AR Tax Invoice (OINV) @ AU Warehouse → [Customer Dispatch &amp; Revenue Recognition]</t>
         </is>
       </c>
       <c r="D95" s="22" t="inlineStr">
@@ -6774,7 +6774,7 @@
       </c>
       <c r="F95" s="22" t="inlineStr">
         <is>
-          <t>FDMSYD</t>
+          <t>AU Warehouse</t>
         </is>
       </c>
       <c r="G95" s="5" t="inlineStr">
@@ -6814,7 +6814,7 @@
       </c>
       <c r="C98" s="7" t="inlineStr">
         <is>
-          <t>[Purchasing] Issue Direct Factory PO in USD (OPOR) @ FDMSYD → [Vendor Production Commitment]</t>
+          <t>[Purchasing] Issue Direct Factory PO in USD (OPOR) @ AU Warehouse → [Vendor Production Commitment]</t>
         </is>
       </c>
       <c r="D98" s="23" t="inlineStr">
@@ -6829,7 +6829,7 @@
       </c>
       <c r="F98" s="23" t="inlineStr">
         <is>
-          <t>FDMSYD</t>
+          <t>AU Warehouse</t>
         </is>
       </c>
       <c r="G98" s="7" t="inlineStr">
@@ -6861,7 +6861,7 @@
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>[Logistics] Post Inward Factory GRPO (OPDN) @ FDMSYD → [Origin Spot FX Base Cost Capitalization]</t>
+          <t>[Logistics] Post Inward Factory GRPO (OPDN) @ AU Warehouse → [Origin Spot FX Base Cost Capitalization]</t>
         </is>
       </c>
       <c r="D99" s="22" t="inlineStr">
@@ -6876,12 +6876,12 @@
       </c>
       <c r="F99" s="22" t="inlineStr">
         <is>
-          <t>FDMSYD</t>
+          <t>AU Warehouse</t>
         </is>
       </c>
       <c r="G99" s="5" t="inlineStr">
         <is>
-          <t>FDMSYD [OnHand = 100]</t>
+          <t>AU Warehouse [OnHand = 100]</t>
         </is>
       </c>
       <c r="H99" s="5" t="inlineStr">
@@ -6908,7 +6908,7 @@
       </c>
       <c r="C100" s="7" t="inlineStr">
         <is>
-          <t>[Finance] Overwrite AU Destination Landed Cost (OIPF 'A') @ FDMSYD → [AU DC Stock Capitalization]</t>
+          <t>[Finance] Overwrite AU Destination Landed Cost (OIPF 'A') @ AU Warehouse → [AU DC Stock Capitalization]</t>
         </is>
       </c>
       <c r="D100" s="23" t="inlineStr">
@@ -6923,12 +6923,12 @@
       </c>
       <c r="F100" s="23" t="inlineStr">
         <is>
-          <t>FDMSYD</t>
+          <t>AU Warehouse</t>
         </is>
       </c>
       <c r="G100" s="7" t="inlineStr">
         <is>
-          <t>FDMSYD [OnHand = 100]</t>
+          <t>AU Warehouse [OnHand = 100]</t>
         </is>
       </c>
       <c r="H100" s="7" t="inlineStr">
@@ -6955,7 +6955,7 @@
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>[Purchasing] Create Trans-Tasman Transfer Request (OWTQ) @ FDMSYD → [NZ Relay Picking Allocation]</t>
+          <t>[Purchasing] Create Trans-Tasman Transfer Request (OWTQ) @ AU Warehouse → [NZ Relay Picking Allocation]</t>
         </is>
       </c>
       <c r="D101" s="22" t="inlineStr">
@@ -6970,12 +6970,12 @@
       </c>
       <c r="F101" s="22" t="inlineStr">
         <is>
-          <t>FDMSYD → NZSIT</t>
+          <t>AU Warehouse → NZSIT</t>
         </is>
       </c>
       <c r="G101" s="5" t="inlineStr">
         <is>
-          <t>FDMSYD [IsCommited = +100]</t>
+          <t>AU Warehouse [IsCommited = +100]</t>
         </is>
       </c>
       <c r="H101" s="5" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="C102" s="7" t="inlineStr">
         <is>
-          <t>[Logistics] Post Trans-Tasman Transfer (OWTR) based on OWTQ @ FDMSYD to NZSIT → [Maritime Transit Tracking]</t>
+          <t>[Logistics] Post Trans-Tasman Transfer (OWTR) based on OWTQ @ AU Warehouse to NZSIT → [Maritime Transit Tracking]</t>
         </is>
       </c>
       <c r="D102" s="23" t="inlineStr">
@@ -7017,7 +7017,7 @@
       </c>
       <c r="F102" s="23" t="inlineStr">
         <is>
-          <t>FDMSYD → NZSIT</t>
+          <t>AU Warehouse → NZSIT</t>
         </is>
       </c>
       <c r="G102" s="7" t="inlineStr">
@@ -7480,7 +7480,7 @@
       </c>
       <c r="C114" s="7" t="inlineStr">
         <is>
-          <t>[Logistics] Post AU Inward Intercompany GRPO (OPDN) @ FDMSYD → [Port Arrival Inbound Clearance]</t>
+          <t>[Logistics] Post AU Inward Intercompany GRPO (OPDN) @ AU Warehouse → [Port Arrival Inbound Clearance]</t>
         </is>
       </c>
       <c r="D114" s="23" t="inlineStr">
@@ -7495,12 +7495,12 @@
       </c>
       <c r="F114" s="23" t="inlineStr">
         <is>
-          <t>FDMSYD</t>
+          <t>AU Warehouse</t>
         </is>
       </c>
       <c r="G114" s="7" t="inlineStr">
         <is>
-          <t>FDMSYD [OnHand = 100]</t>
+          <t>AU Warehouse [OnHand = 100]</t>
         </is>
       </c>
       <c r="H114" s="7" t="inlineStr">
@@ -7510,7 +7510,7 @@
       </c>
       <c r="I114" s="7" t="inlineStr">
         <is>
-          <t>Dr 100010 (FDMSYD) $52,200 / Cr 200030 (IC AP) $52,200</t>
+          <t>Dr 100010 (AU Warehouse) $52,200 / Cr 200030 (IC AP) $52,200</t>
         </is>
       </c>
     </row>
@@ -7527,7 +7527,7 @@
       </c>
       <c r="C115" s="5" t="inlineStr">
         <is>
-          <t>[Finance] Capitalize AU Inbound Landed Cost (OIPF 'A') @ FDMSYD → [Final Stacked Valuation &amp; G/L 200050 Reconciled]</t>
+          <t>[Finance] Capitalize AU Inbound Landed Cost (OIPF 'A') @ AU Warehouse → [Final Stacked Valuation &amp; G/L 200050 Reconciled]</t>
         </is>
       </c>
       <c r="D115" s="22" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="F115" s="22" t="inlineStr">
         <is>
-          <t>FDMSYD</t>
+          <t>AU Warehouse</t>
         </is>
       </c>
       <c r="G115" s="5" t="inlineStr">
         <is>
-          <t>FDMSYD [OnHand = 100]</t>
+          <t>AU Warehouse [OnHand = 100]</t>
         </is>
       </c>
       <c r="H115" s="5" t="inlineStr">
@@ -7557,7 +7557,7 @@
       </c>
       <c r="I115" s="5" t="inlineStr">
         <is>
-          <t>Dr 100010 (FDMSYD) $2,300 / Cr 200010 ($2,300)</t>
+          <t>Dr 100010 (AU Warehouse) $2,300 / Cr 200010 ($2,300)</t>
         </is>
       </c>
     </row>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="C116" s="7" t="inlineStr">
         <is>
-          <t>[Sales] Book Domestic Customer Sales Order (ORDR) @ FDMSYD → [AU Customer Stock Allocation]</t>
+          <t>[Sales] Book Domestic Customer Sales Order (ORDR) @ AU Warehouse → [AU Customer Stock Allocation]</t>
         </is>
       </c>
       <c r="D116" s="23" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="F116" s="23" t="inlineStr">
         <is>
-          <t>FDMSYD</t>
+          <t>AU Warehouse</t>
         </is>
       </c>
       <c r="G116" s="7" t="inlineStr">
         <is>
-          <t>FDMSYD [Reserved = +100]</t>
+          <t>AU Warehouse [Reserved = +100]</t>
         </is>
       </c>
       <c r="H116" s="7" t="inlineStr">
@@ -7621,7 +7621,7 @@
       </c>
       <c r="C117" s="5" t="inlineStr">
         <is>
-          <t>[Logistics] Post Direct AR Tax Invoice (OINV) @ FDMSYD → [Customer Dispatch &amp; Revenue Recognition]</t>
+          <t>[Logistics] Post Direct AR Tax Invoice (OINV) @ AU Warehouse → [Customer Dispatch &amp; Revenue Recognition]</t>
         </is>
       </c>
       <c r="D117" s="22" t="inlineStr">
@@ -7636,7 +7636,7 @@
       </c>
       <c r="F117" s="22" t="inlineStr">
         <is>
-          <t>FDMSYD</t>
+          <t>AU Warehouse</t>
         </is>
       </c>
       <c r="G117" s="5" t="inlineStr">
@@ -7659,7 +7659,7 @@
     <row r="119" ht="24" customHeight="1">
       <c r="A119" s="21" t="inlineStr">
         <is>
-          <t>Process 2.2.7: Factory → ICC → AU Warehouse → UK Wayfair (Consolidated AU Re-Export Direct Invoicing)</t>
+          <t>Process 2.2.7: Factory → ICC → AU Warehouse → EuropeMarketPlace (Consolidated AU Re-Export Direct Invoicing)</t>
         </is>
       </c>
     </row>
@@ -7676,7 +7676,7 @@
       </c>
       <c r="C120" s="7" t="inlineStr">
         <is>
-          <t>[Purchasing] Issue Factory PO in USD (OPOR) @ ICCNGB → [Vendor Production Commitment]</t>
+          <t>[Purchasing] Issue Factory PO in USD (OPOR) @ ICCChina → [Vendor Production Commitment]</t>
         </is>
       </c>
       <c r="D120" s="23" t="inlineStr">
@@ -7691,7 +7691,7 @@
       </c>
       <c r="F120" s="23" t="inlineStr">
         <is>
-          <t>ICCNGB</t>
+          <t>ICCChina</t>
         </is>
       </c>
       <c r="G120" s="7" t="inlineStr">
@@ -7723,7 +7723,7 @@
       </c>
       <c r="C121" s="5" t="inlineStr">
         <is>
-          <t>[Logistics] Post Inward Factory GRPO (OPDN) @ ICCNGB → [Origin Spot FX Base Cost Capitalization]</t>
+          <t>[Logistics] Post Inward Factory GRPO (OPDN) @ ICCChina → [Origin Spot FX Base Cost Capitalization]</t>
         </is>
       </c>
       <c r="D121" s="22" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="F121" s="22" t="inlineStr">
         <is>
-          <t>ICCNGB</t>
+          <t>ICCChina</t>
         </is>
       </c>
       <c r="G121" s="5" t="inlineStr">
         <is>
-          <t>ICCNGB [OnHand = 100]</t>
+          <t>ICCChina [OnHand = 100]</t>
         </is>
       </c>
       <c r="H121" s="5" t="inlineStr">
@@ -7770,7 +7770,7 @@
       </c>
       <c r="C122" s="7" t="inlineStr">
         <is>
-          <t>[Finance] Capitalize Origin Actual Landed Cost (OIPF 'A') @ ICCNGB → [Source MWAG Lock]</t>
+          <t>[Finance] Capitalize Origin Actual Landed Cost (OIPF 'A') @ ICCChina → [Source MWAG Lock]</t>
         </is>
       </c>
       <c r="D122" s="23" t="inlineStr">
@@ -7785,12 +7785,12 @@
       </c>
       <c r="F122" s="23" t="inlineStr">
         <is>
-          <t>ICCNGB</t>
+          <t>ICCChina</t>
         </is>
       </c>
       <c r="G122" s="7" t="inlineStr">
         <is>
-          <t>ICCNGB [OnHand = 100]</t>
+          <t>ICCChina [OnHand = 100]</t>
         </is>
       </c>
       <c r="H122" s="7" t="inlineStr">
@@ -7817,7 +7817,7 @@
       </c>
       <c r="C123" s="5" t="inlineStr">
         <is>
-          <t>[Purchasing] Create Inventory Transfer Request (OWTQ) @ ICCNGB → [AU Sea Voyage Picking Allocation]</t>
+          <t>[Purchasing] Create Inventory Transfer Request (OWTQ) @ ICCChina → [AU Sea Voyage Picking Allocation]</t>
         </is>
       </c>
       <c r="D123" s="22" t="inlineStr">
@@ -7832,12 +7832,12 @@
       </c>
       <c r="F123" s="22" t="inlineStr">
         <is>
-          <t>ICCNGB → ICCSIT</t>
+          <t>ICCChina → ICCSIT</t>
         </is>
       </c>
       <c r="G123" s="5" t="inlineStr">
         <is>
-          <t>ICCNGB [IsCommited = +100]</t>
+          <t>ICCChina [IsCommited = +100]</t>
         </is>
       </c>
       <c r="H123" s="5" t="inlineStr">
@@ -7864,7 +7864,7 @@
       </c>
       <c r="C124" s="7" t="inlineStr">
         <is>
-          <t>[Logistics] Post In-Transit Stock Transfer (OWTR) based on OWTQ @ ICCNGB to ICCSIT → [Goods In-Transit Balance Sheet Capitalization]</t>
+          <t>[Logistics] Post In-Transit Stock Transfer (OWTR) based on OWTQ @ ICCChina to ICCSIT → [Goods In-Transit Balance Sheet Capitalization]</t>
         </is>
       </c>
       <c r="D124" s="23" t="inlineStr">
@@ -7879,7 +7879,7 @@
       </c>
       <c r="F124" s="23" t="inlineStr">
         <is>
-          <t>ICCNGB → ICCSIT</t>
+          <t>ICCChina → ICCSIT</t>
         </is>
       </c>
       <c r="G124" s="7" t="inlineStr">
@@ -7911,7 +7911,7 @@
       </c>
       <c r="C125" s="5" t="inlineStr">
         <is>
-          <t>[Logistics] Post AU Port Intercompany GRPO (OPDN) Synchronized with Origin Goods Issue (OIGE) @ FDMSYD → [AU Port Inbound Clearance]</t>
+          <t>[Logistics] Post AU Port Intercompany GRPO (OPDN) Synchronized with Origin Goods Issue (OIGE) @ AU Warehouse → [AU Port Inbound Clearance]</t>
         </is>
       </c>
       <c r="D125" s="22" t="inlineStr">
@@ -7926,12 +7926,12 @@
       </c>
       <c r="F125" s="22" t="inlineStr">
         <is>
-          <t>ICCSIT → FDMSYD</t>
+          <t>ICCSIT → AU Warehouse</t>
         </is>
       </c>
       <c r="G125" s="5" t="inlineStr">
         <is>
-          <t>FDMSYD [OnHand = 100]</t>
+          <t>AU Warehouse [OnHand = 100]</t>
         </is>
       </c>
       <c r="H125" s="5" t="inlineStr">
@@ -7959,7 +7959,7 @@
       </c>
       <c r="C126" s="7" t="inlineStr">
         <is>
-          <t>[Finance] Overwrite AU Destination Landed Cost (OIPF 'A') @ FDMSYD → [AU Stock Capitalization &amp; G/L 200050 Reconciled]</t>
+          <t>[Finance] Overwrite AU Destination Landed Cost (OIPF 'A') @ AU Warehouse → [AU Stock Capitalization &amp; G/L 200050 Reconciled]</t>
         </is>
       </c>
       <c r="D126" s="23" t="inlineStr">
@@ -7974,12 +7974,12 @@
       </c>
       <c r="F126" s="23" t="inlineStr">
         <is>
-          <t>FDMSYD</t>
+          <t>AU Warehouse</t>
         </is>
       </c>
       <c r="G126" s="7" t="inlineStr">
         <is>
-          <t>FDMSYD [OnHand = 100]</t>
+          <t>AU Warehouse [OnHand = 100]</t>
         </is>
       </c>
       <c r="H126" s="7" t="inlineStr">
@@ -8006,7 +8006,7 @@
       </c>
       <c r="C127" s="5" t="inlineStr">
         <is>
-          <t>[Purchasing] Create UK Export Transfer Request (OWTQ) @ FDMSYD → [UK Voyage Picking Allocation]</t>
+          <t>[Purchasing] Create UK Export Transfer Request (OWTQ) @ AU Warehouse → [UK Voyage Picking Allocation]</t>
         </is>
       </c>
       <c r="D127" s="22" t="inlineStr">
@@ -8021,12 +8021,12 @@
       </c>
       <c r="F127" s="22" t="inlineStr">
         <is>
-          <t>FDMSYD → UKSIT</t>
+          <t>AU Warehouse → EuropeSIT</t>
         </is>
       </c>
       <c r="G127" s="5" t="inlineStr">
         <is>
-          <t>FDMSYD [IsCommited = +100]</t>
+          <t>AU Warehouse [IsCommited = +100]</t>
         </is>
       </c>
       <c r="H127" s="5" t="inlineStr">
@@ -8053,7 +8053,7 @@
       </c>
       <c r="C128" s="7" t="inlineStr">
         <is>
-          <t>[Logistics] Post Re-Export Maritime Transfer (OWTR) based on OWTQ @ FDMSYD to UKSIT → [UK Transit Voyage Tracking]</t>
+          <t>[Logistics] Post Re-Export Maritime Transfer (OWTR) based on OWTQ @ AU Warehouse to EuropeSIT → [UK Transit Voyage Tracking]</t>
         </is>
       </c>
       <c r="D128" s="23" t="inlineStr">
@@ -8068,12 +8068,12 @@
       </c>
       <c r="F128" s="23" t="inlineStr">
         <is>
-          <t>FDMSYD → UKSIT</t>
+          <t>AU Warehouse → EuropeSIT</t>
         </is>
       </c>
       <c r="G128" s="7" t="inlineStr">
         <is>
-          <t>UKSIT [OnHand = 100]</t>
+          <t>EuropeSIT [OnHand = 100]</t>
         </is>
       </c>
       <c r="H128" s="7" t="inlineStr">
@@ -8100,7 +8100,7 @@
       </c>
       <c r="C129" s="5" t="inlineStr">
         <is>
-          <t>[Logistics] Post UK Inward GRPO (OPDN) @ UKWYF → [UK Port Arrival Inbound Clearance]</t>
+          <t>[Logistics] Post UK Inward GRPO (OPDN) @ EuropeMarketPlace → [UK Port Arrival Inbound Clearance]</t>
         </is>
       </c>
       <c r="D129" s="22" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="F129" s="22" t="inlineStr">
         <is>
-          <t>UKWYF</t>
+          <t>EuropeMarketPlace</t>
         </is>
       </c>
       <c r="G129" s="5" t="inlineStr">
         <is>
-          <t>UKWYF [OnHand = 100]</t>
+          <t>EuropeMarketPlace [OnHand = 100]</t>
         </is>
       </c>
       <c r="H129" s="5" t="inlineStr">
@@ -8130,7 +8130,7 @@
       </c>
       <c r="I129" s="5" t="inlineStr">
         <is>
-          <t>Dr 100040 (UKWYF) $52,200 / Cr 100050 ($52,200)</t>
+          <t>Dr 100040 (EuropeMarketPlace) $52,200 / Cr 100050 ($52,200)</t>
         </is>
       </c>
     </row>
@@ -8147,7 +8147,7 @@
       </c>
       <c r="C130" s="7" t="inlineStr">
         <is>
-          <t>[Finance] Capitalize UK Port Landed Cost (OIPF 'A') @ UKWYF → [Final Stacked Cost &amp; G/L 200050 Reconciled]</t>
+          <t>[Finance] Capitalize UK Port Landed Cost (OIPF 'A') @ EuropeMarketPlace → [Final Stacked Cost &amp; G/L 200050 Reconciled]</t>
         </is>
       </c>
       <c r="D130" s="23" t="inlineStr">
@@ -8162,12 +8162,12 @@
       </c>
       <c r="F130" s="23" t="inlineStr">
         <is>
-          <t>UKWYF</t>
+          <t>EuropeMarketPlace</t>
         </is>
       </c>
       <c r="G130" s="7" t="inlineStr">
         <is>
-          <t>UKWYF [OnHand = 100]</t>
+          <t>EuropeMarketPlace [OnHand = 100]</t>
         </is>
       </c>
       <c r="H130" s="7" t="inlineStr">
@@ -8177,7 +8177,7 @@
       </c>
       <c r="I130" s="7" t="inlineStr">
         <is>
-          <t>Dr 100040 (UKWYF) $3,800 / Cr 200010 ($3,800)</t>
+          <t>Dr 100040 (EuropeMarketPlace) $3,800 / Cr 200010 ($3,800)</t>
         </is>
       </c>
     </row>
@@ -8194,7 +8194,7 @@
       </c>
       <c r="C131" s="5" t="inlineStr">
         <is>
-          <t>[Sales] Book Wholesale Sales Order (ORDR) @ UKWYF → [Wayfair Channel Allocation]</t>
+          <t>[Sales] Book Wholesale Sales Order (ORDR) @ EuropeMarketPlace → [EuropeMarketPlace Channel Allocation]</t>
         </is>
       </c>
       <c r="D131" s="22" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="F131" s="22" t="inlineStr">
         <is>
-          <t>UKWYF</t>
+          <t>EuropeMarketPlace</t>
         </is>
       </c>
       <c r="G131" s="5" t="inlineStr">
         <is>
-          <t>UKWYF [Reserved = +100]</t>
+          <t>EuropeMarketPlace [Reserved = +100]</t>
         </is>
       </c>
       <c r="H131" s="5" t="inlineStr">
@@ -8241,7 +8241,7 @@
       </c>
       <c r="C132" s="7" t="inlineStr">
         <is>
-          <t>[Logistics] Post Direct Wholesale AR Invoice (OINV) @ UKWYF → [Wayfair Channel Revenue Recognition]</t>
+          <t>[Logistics] Post Direct Wholesale AR Invoice (OINV) @ EuropeMarketPlace → [EuropeMarketPlace Channel Revenue Recognition]</t>
         </is>
       </c>
       <c r="D132" s="23" t="inlineStr">
@@ -8256,12 +8256,12 @@
       </c>
       <c r="F132" s="23" t="inlineStr">
         <is>
-          <t>UKWYF</t>
+          <t>EuropeMarketPlace</t>
         </is>
       </c>
       <c r="G132" s="7" t="inlineStr">
         <is>
-          <t>Wayfair Custody
+          <t>EuropeMarketPlace Custody
 [OnHand = 0]</t>
         </is>
       </c>
@@ -8272,14 +8272,14 @@
       </c>
       <c r="I132" s="7" t="inlineStr">
         <is>
-          <t>Dr 110010 (AR) $75,000 / Dr 500010 (COGS UK) $56,000 / Cr 400010 (Revenue) $75,000 / Cr 100040 (UKWYF) $56,000</t>
+          <t>Dr 110010 (AR) $75,000 / Dr 500010 (COGS UK) $56,000 / Cr 400010 (Revenue) $75,000 / Cr 100040 (EuropeMarketPlace) $56,000</t>
         </is>
       </c>
     </row>
     <row r="134" ht="24" customHeight="1">
       <c r="A134" s="21" t="inlineStr">
         <is>
-          <t>Process 2.2.8: Factory → AU Warehouse → NZ Warehouse → UK Wayfair (AU to NZ Transshipment Direct Invoicing)</t>
+          <t>Process 2.2.8: Factory → AU Warehouse → NZ Warehouse → EuropeMarketPlace (AU to NZ Transshipment Direct Invoicing)</t>
         </is>
       </c>
     </row>
@@ -8296,7 +8296,7 @@
       </c>
       <c r="C135" s="5" t="inlineStr">
         <is>
-          <t>[Purchasing] Issue Direct Factory PO in USD (OPOR) @ FDMSYD → [Vendor Production Commitment]</t>
+          <t>[Purchasing] Issue Direct Factory PO in USD (OPOR) @ AU Warehouse → [Vendor Production Commitment]</t>
         </is>
       </c>
       <c r="D135" s="22" t="inlineStr">
@@ -8311,7 +8311,7 @@
       </c>
       <c r="F135" s="22" t="inlineStr">
         <is>
-          <t>FDMSYD</t>
+          <t>AU Warehouse</t>
         </is>
       </c>
       <c r="G135" s="5" t="inlineStr">
@@ -8343,7 +8343,7 @@
       </c>
       <c r="C136" s="7" t="inlineStr">
         <is>
-          <t>[Logistics] Post Inward Factory GRPO (OPDN) @ FDMSYD → [Origin Spot FX Base Cost Capitalization]</t>
+          <t>[Logistics] Post Inward Factory GRPO (OPDN) @ AU Warehouse → [Origin Spot FX Base Cost Capitalization]</t>
         </is>
       </c>
       <c r="D136" s="23" t="inlineStr">
@@ -8358,12 +8358,12 @@
       </c>
       <c r="F136" s="23" t="inlineStr">
         <is>
-          <t>FDMSYD</t>
+          <t>AU Warehouse</t>
         </is>
       </c>
       <c r="G136" s="7" t="inlineStr">
         <is>
-          <t>FDMSYD [OnHand = 100]</t>
+          <t>AU Warehouse [OnHand = 100]</t>
         </is>
       </c>
       <c r="H136" s="7" t="inlineStr">
@@ -8390,7 +8390,7 @@
       </c>
       <c r="C137" s="5" t="inlineStr">
         <is>
-          <t>[Finance] Overwrite AU Landed Cost (OIPF 'A') @ FDMSYD → [Direct AU DC Capitalization]</t>
+          <t>[Finance] Overwrite AU Landed Cost (OIPF 'A') @ AU Warehouse → [Direct AU DC Capitalization]</t>
         </is>
       </c>
       <c r="D137" s="22" t="inlineStr">
@@ -8405,12 +8405,12 @@
       </c>
       <c r="F137" s="22" t="inlineStr">
         <is>
-          <t>FDMSYD</t>
+          <t>AU Warehouse</t>
         </is>
       </c>
       <c r="G137" s="5" t="inlineStr">
         <is>
-          <t>FDMSYD [OnHand = 100]</t>
+          <t>AU Warehouse [OnHand = 100]</t>
         </is>
       </c>
       <c r="H137" s="5" t="inlineStr">
@@ -8437,7 +8437,7 @@
       </c>
       <c r="C138" s="7" t="inlineStr">
         <is>
-          <t>[Purchasing] Create Trans-Tasman Transfer Request (OWTQ) @ FDMSYD → [NZ Relay Picking Allocation]</t>
+          <t>[Purchasing] Create Trans-Tasman Transfer Request (OWTQ) @ AU Warehouse → [NZ Relay Picking Allocation]</t>
         </is>
       </c>
       <c r="D138" s="23" t="inlineStr">
@@ -8452,12 +8452,12 @@
       </c>
       <c r="F138" s="23" t="inlineStr">
         <is>
-          <t>FDMSYD → NZSIT</t>
+          <t>AU Warehouse → NZSIT</t>
         </is>
       </c>
       <c r="G138" s="7" t="inlineStr">
         <is>
-          <t>FDMSYD [IsCommited = +100]</t>
+          <t>AU Warehouse [IsCommited = +100]</t>
         </is>
       </c>
       <c r="H138" s="7" t="inlineStr">
@@ -8484,7 +8484,7 @@
       </c>
       <c r="C139" s="5" t="inlineStr">
         <is>
-          <t>[Logistics] Post Trans-Tasman Relay Transfer (OWTR) based on OWTQ @ FDMSYD to NZSIT → [Trans-Tasman Sea Voyage Tracking]</t>
+          <t>[Logistics] Post Trans-Tasman Relay Transfer (OWTR) based on OWTQ @ AU Warehouse to NZSIT → [Trans-Tasman Sea Voyage Tracking]</t>
         </is>
       </c>
       <c r="D139" s="22" t="inlineStr">
@@ -8499,7 +8499,7 @@
       </c>
       <c r="F139" s="22" t="inlineStr">
         <is>
-          <t>FDMSYD → NZSIT</t>
+          <t>AU Warehouse → NZSIT</t>
         </is>
       </c>
       <c r="G139" s="5" t="inlineStr">
@@ -8640,7 +8640,7 @@
       </c>
       <c r="F142" s="23" t="inlineStr">
         <is>
-          <t>NZNTH → UKSIT</t>
+          <t>NZNTH → EuropeSIT</t>
         </is>
       </c>
       <c r="G142" s="7" t="inlineStr">
@@ -8672,7 +8672,7 @@
       </c>
       <c r="C143" s="5" t="inlineStr">
         <is>
-          <t>[Logistics] Post UK Maritime Transfer (OWTR) based on OWTQ @ NZNTH to UKSIT → [Long-Haul Transit Tracking]</t>
+          <t>[Logistics] Post UK Maritime Transfer (OWTR) based on OWTQ @ NZNTH to EuropeSIT → [Long-Haul Transit Tracking]</t>
         </is>
       </c>
       <c r="D143" s="22" t="inlineStr">
@@ -8687,12 +8687,12 @@
       </c>
       <c r="F143" s="22" t="inlineStr">
         <is>
-          <t>NZNTH → UKSIT</t>
+          <t>NZNTH → EuropeSIT</t>
         </is>
       </c>
       <c r="G143" s="5" t="inlineStr">
         <is>
-          <t>UKSIT [OnHand = 100]</t>
+          <t>EuropeSIT [OnHand = 100]</t>
         </is>
       </c>
       <c r="H143" s="5" t="inlineStr">
@@ -8702,7 +8702,7 @@
       </c>
       <c r="I143" s="5" t="inlineStr">
         <is>
-          <t>Dr 100050 (UKSIT) $54,500 / Cr 100040 ($54,500)</t>
+          <t>Dr 100050 (EuropeSIT) $54,500 / Cr 100040 ($54,500)</t>
         </is>
       </c>
     </row>
@@ -8719,7 +8719,7 @@
       </c>
       <c r="C144" s="7" t="inlineStr">
         <is>
-          <t>[Logistics] Post UK Inward GRPO (OPDN) @ UKWYF → [UK Port Arrival Clearance]</t>
+          <t>[Logistics] Post UK Inward GRPO (OPDN) @ EuropeMarketPlace → [UK Port Arrival Clearance]</t>
         </is>
       </c>
       <c r="D144" s="23" t="inlineStr">
@@ -8734,12 +8734,12 @@
       </c>
       <c r="F144" s="23" t="inlineStr">
         <is>
-          <t>UKWYF</t>
+          <t>EuropeMarketPlace</t>
         </is>
       </c>
       <c r="G144" s="7" t="inlineStr">
         <is>
-          <t>UKWYF [OnHand = 100]</t>
+          <t>EuropeMarketPlace [OnHand = 100]</t>
         </is>
       </c>
       <c r="H144" s="7" t="inlineStr">
@@ -8749,7 +8749,7 @@
       </c>
       <c r="I144" s="7" t="inlineStr">
         <is>
-          <t>Dr 100040 (UKWYF) $54,500 / Cr 100050 ($54,500)</t>
+          <t>Dr 100040 (EuropeMarketPlace) $54,500 / Cr 100050 ($54,500)</t>
         </is>
       </c>
     </row>
@@ -8766,7 +8766,7 @@
       </c>
       <c r="C145" s="5" t="inlineStr">
         <is>
-          <t>[Finance] Capitalize UK Landed Cost (OIPF 'A') @ UKWYF → [Final Stacked Capitalization &amp; G/L 200050 Reconciled]</t>
+          <t>[Finance] Capitalize UK Landed Cost (OIPF 'A') @ EuropeMarketPlace → [Final Stacked Capitalization &amp; G/L 200050 Reconciled]</t>
         </is>
       </c>
       <c r="D145" s="22" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="F145" s="22" t="inlineStr">
         <is>
-          <t>UKWYF</t>
+          <t>EuropeMarketPlace</t>
         </is>
       </c>
       <c r="G145" s="5" t="inlineStr">
         <is>
-          <t>UKWYF [OnHand = 100]</t>
+          <t>EuropeMarketPlace [OnHand = 100]</t>
         </is>
       </c>
       <c r="H145" s="5" t="inlineStr">
@@ -8796,7 +8796,7 @@
       </c>
       <c r="I145" s="5" t="inlineStr">
         <is>
-          <t>Dr 100040 (UKWYF) $1,500 / Cr 200010 ($1,500)</t>
+          <t>Dr 100040 (EuropeMarketPlace) $1,500 / Cr 200010 ($1,500)</t>
         </is>
       </c>
     </row>
@@ -8813,7 +8813,7 @@
       </c>
       <c r="C146" s="7" t="inlineStr">
         <is>
-          <t>[Sales] Book Wholesale Sales Order (ORDR) @ UKWYF → [Wayfair Channel Allocation]</t>
+          <t>[Sales] Book Wholesale Sales Order (ORDR) @ EuropeMarketPlace → [EuropeMarketPlace Channel Allocation]</t>
         </is>
       </c>
       <c r="D146" s="23" t="inlineStr">
@@ -8828,12 +8828,12 @@
       </c>
       <c r="F146" s="23" t="inlineStr">
         <is>
-          <t>UKWYF</t>
+          <t>EuropeMarketPlace</t>
         </is>
       </c>
       <c r="G146" s="7" t="inlineStr">
         <is>
-          <t>UKWYF [Reserved = +100]</t>
+          <t>EuropeMarketPlace [Reserved = +100]</t>
         </is>
       </c>
       <c r="H146" s="7" t="inlineStr">
@@ -8860,7 +8860,7 @@
       </c>
       <c r="C147" s="5" t="inlineStr">
         <is>
-          <t>[Logistics] Post Direct Wholesale AR Invoice (OINV) @ UKWYF → [Wayfair Channel Revenue Recognition]</t>
+          <t>[Logistics] Post Direct Wholesale AR Invoice (OINV) @ EuropeMarketPlace → [EuropeMarketPlace Channel Revenue Recognition]</t>
         </is>
       </c>
       <c r="D147" s="22" t="inlineStr">
@@ -8875,12 +8875,12 @@
       </c>
       <c r="F147" s="22" t="inlineStr">
         <is>
-          <t>UKWYF</t>
+          <t>EuropeMarketPlace</t>
         </is>
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>Wayfair Custody
+          <t>EuropeMarketPlace Custody
 [OnHand = 0]</t>
         </is>
       </c>
@@ -8898,7 +8898,7 @@
     <row r="149" ht="24" customHeight="1">
       <c r="A149" s="21" t="inlineStr">
         <is>
-          <t>Process 2.2.9: Factory → NZ Warehouse → AU Warehouse → UK Wayfair (NZ to AU Transshipment Direct Invoicing)</t>
+          <t>Process 2.2.9: Factory → NZ Warehouse → AU Warehouse → EuropeMarketPlace (NZ to AU Transshipment Direct Invoicing)</t>
         </is>
       </c>
     </row>
@@ -9150,7 +9150,7 @@
       </c>
       <c r="C155" s="5" t="inlineStr">
         <is>
-          <t>[Logistics] Post AU Inward Intercompany GRPO (OPDN) @ FDMSYD → [AU Port Arrival Clearance]</t>
+          <t>[Logistics] Post AU Inward Intercompany GRPO (OPDN) @ AU Warehouse → [AU Port Arrival Clearance]</t>
         </is>
       </c>
       <c r="D155" s="22" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="F155" s="22" t="inlineStr">
         <is>
-          <t>FDMSYD</t>
+          <t>AU Warehouse</t>
         </is>
       </c>
       <c r="G155" s="5" t="inlineStr">
         <is>
-          <t>FDMSYD [OnHand = 100]</t>
+          <t>AU Warehouse [OnHand = 100]</t>
         </is>
       </c>
       <c r="H155" s="5" t="inlineStr">
@@ -9180,7 +9180,7 @@
       </c>
       <c r="I155" s="5" t="inlineStr">
         <is>
-          <t>Dr 100010 (FDMSYD) $52,200 / Cr 200030 ($52,200)</t>
+          <t>Dr 100010 (AU Warehouse) $52,200 / Cr 200030 ($52,200)</t>
         </is>
       </c>
     </row>
@@ -9197,7 +9197,7 @@
       </c>
       <c r="C156" s="7" t="inlineStr">
         <is>
-          <t>[Finance] Capitalize AU Landed Cost (OIPF 'A') @ FDMSYD → [AU Regional Moving Average Lock]</t>
+          <t>[Finance] Capitalize AU Landed Cost (OIPF 'A') @ AU Warehouse → [AU Regional Moving Average Lock]</t>
         </is>
       </c>
       <c r="D156" s="23" t="inlineStr">
@@ -9212,12 +9212,12 @@
       </c>
       <c r="F156" s="23" t="inlineStr">
         <is>
-          <t>FDMSYD</t>
+          <t>AU Warehouse</t>
         </is>
       </c>
       <c r="G156" s="7" t="inlineStr">
         <is>
-          <t>FDMSYD [OnHand = 100]</t>
+          <t>AU Warehouse [OnHand = 100]</t>
         </is>
       </c>
       <c r="H156" s="7" t="inlineStr">
@@ -9227,7 +9227,7 @@
       </c>
       <c r="I156" s="7" t="inlineStr">
         <is>
-          <t>Dr 100010 (FDMSYD) $2,300 / Cr 200010 ($2,300)</t>
+          <t>Dr 100010 (AU Warehouse) $2,300 / Cr 200010 ($2,300)</t>
         </is>
       </c>
     </row>
@@ -9244,7 +9244,7 @@
       </c>
       <c r="C157" s="5" t="inlineStr">
         <is>
-          <t>[Purchasing] Create UK Export Transfer Request (OWTQ) @ FDMSYD → [UK Voyage Picking Allocation]</t>
+          <t>[Purchasing] Create UK Export Transfer Request (OWTQ) @ AU Warehouse → [UK Voyage Picking Allocation]</t>
         </is>
       </c>
       <c r="D157" s="22" t="inlineStr">
@@ -9259,12 +9259,12 @@
       </c>
       <c r="F157" s="22" t="inlineStr">
         <is>
-          <t>FDMSYD → UKSIT</t>
+          <t>AU Warehouse → EuropeSIT</t>
         </is>
       </c>
       <c r="G157" s="5" t="inlineStr">
         <is>
-          <t>FDMSYD [IsCommited = +100]</t>
+          <t>AU Warehouse [IsCommited = +100]</t>
         </is>
       </c>
       <c r="H157" s="5" t="inlineStr">
@@ -9291,7 +9291,7 @@
       </c>
       <c r="C158" s="7" t="inlineStr">
         <is>
-          <t>[Logistics] Post UK Maritime Transfer (OWTR) based on OWTQ @ FDMSYD to UKSIT → [Long-Haul Transit Tracking]</t>
+          <t>[Logistics] Post UK Maritime Transfer (OWTR) based on OWTQ @ AU Warehouse to EuropeSIT → [Long-Haul Transit Tracking]</t>
         </is>
       </c>
       <c r="D158" s="23" t="inlineStr">
@@ -9306,12 +9306,12 @@
       </c>
       <c r="F158" s="23" t="inlineStr">
         <is>
-          <t>FDMSYD → UKSIT</t>
+          <t>AU Warehouse → EuropeSIT</t>
         </is>
       </c>
       <c r="G158" s="7" t="inlineStr">
         <is>
-          <t>UKSIT [OnHand = 100]</t>
+          <t>EuropeSIT [OnHand = 100]</t>
         </is>
       </c>
       <c r="H158" s="7" t="inlineStr">
@@ -9321,7 +9321,7 @@
       </c>
       <c r="I158" s="7" t="inlineStr">
         <is>
-          <t>Dr 100050 (UKSIT) $54,500 / Cr 100010 ($54,500)</t>
+          <t>Dr 100050 (EuropeSIT) $54,500 / Cr 100010 ($54,500)</t>
         </is>
       </c>
     </row>
@@ -9338,7 +9338,7 @@
       </c>
       <c r="C159" s="5" t="inlineStr">
         <is>
-          <t>[Logistics] Post UK Inward GRPO (OPDN) @ UKWYF → [UK Port Arrival Clearance]</t>
+          <t>[Logistics] Post UK Inward GRPO (OPDN) @ EuropeMarketPlace → [UK Port Arrival Clearance]</t>
         </is>
       </c>
       <c r="D159" s="22" t="inlineStr">
@@ -9353,12 +9353,12 @@
       </c>
       <c r="F159" s="22" t="inlineStr">
         <is>
-          <t>UKWYF</t>
+          <t>EuropeMarketPlace</t>
         </is>
       </c>
       <c r="G159" s="5" t="inlineStr">
         <is>
-          <t>UKWYF [OnHand = 100]</t>
+          <t>EuropeMarketPlace [OnHand = 100]</t>
         </is>
       </c>
       <c r="H159" s="5" t="inlineStr">
@@ -9368,7 +9368,7 @@
       </c>
       <c r="I159" s="5" t="inlineStr">
         <is>
-          <t>Dr 100040 (UKWYF) $54,500 / Cr 100050 ($54,500)</t>
+          <t>Dr 100040 (EuropeMarketPlace) $54,500 / Cr 100050 ($54,500)</t>
         </is>
       </c>
     </row>
@@ -9385,7 +9385,7 @@
       </c>
       <c r="C160" s="7" t="inlineStr">
         <is>
-          <t>[Finance] Capitalize UK Landed Cost (OIPF 'A') @ UKWYF → [Final Stacked Capitalization &amp; G/L 200050 Reconciled]</t>
+          <t>[Finance] Capitalize UK Landed Cost (OIPF 'A') @ EuropeMarketPlace → [Final Stacked Capitalization &amp; G/L 200050 Reconciled]</t>
         </is>
       </c>
       <c r="D160" s="23" t="inlineStr">
@@ -9400,12 +9400,12 @@
       </c>
       <c r="F160" s="23" t="inlineStr">
         <is>
-          <t>UKWYF</t>
+          <t>EuropeMarketPlace</t>
         </is>
       </c>
       <c r="G160" s="7" t="inlineStr">
         <is>
-          <t>UKWYF [OnHand = 100]</t>
+          <t>EuropeMarketPlace [OnHand = 100]</t>
         </is>
       </c>
       <c r="H160" s="7" t="inlineStr">
@@ -9415,7 +9415,7 @@
       </c>
       <c r="I160" s="7" t="inlineStr">
         <is>
-          <t>Dr 100040 (UKWYF) $1,500 / Cr 200010 ($1,500)</t>
+          <t>Dr 100040 (EuropeMarketPlace) $1,500 / Cr 200010 ($1,500)</t>
         </is>
       </c>
     </row>
@@ -9432,7 +9432,7 @@
       </c>
       <c r="C161" s="5" t="inlineStr">
         <is>
-          <t>[Sales] Book Wholesale Sales Order (ORDR) @ UKWYF → [Wayfair Channel Allocation]</t>
+          <t>[Sales] Book Wholesale Sales Order (ORDR) @ EuropeMarketPlace → [EuropeMarketPlace Channel Allocation]</t>
         </is>
       </c>
       <c r="D161" s="22" t="inlineStr">
@@ -9447,12 +9447,12 @@
       </c>
       <c r="F161" s="22" t="inlineStr">
         <is>
-          <t>UKWYF</t>
+          <t>EuropeMarketPlace</t>
         </is>
       </c>
       <c r="G161" s="5" t="inlineStr">
         <is>
-          <t>UKWYF [Reserved = +100]</t>
+          <t>EuropeMarketPlace [Reserved = +100]</t>
         </is>
       </c>
       <c r="H161" s="5" t="inlineStr">
@@ -9479,7 +9479,7 @@
       </c>
       <c r="C162" s="7" t="inlineStr">
         <is>
-          <t>[Logistics] Post Direct Wholesale AR Invoice (OINV) @ UKWYF → [Wayfair Channel Revenue Recognition]</t>
+          <t>[Logistics] Post Direct Wholesale AR Invoice (OINV) @ EuropeMarketPlace → [EuropeMarketPlace Channel Revenue Recognition]</t>
         </is>
       </c>
       <c r="D162" s="23" t="inlineStr">
@@ -9494,12 +9494,12 @@
       </c>
       <c r="F162" s="23" t="inlineStr">
         <is>
-          <t>UKWYF</t>
+          <t>EuropeMarketPlace</t>
         </is>
       </c>
       <c r="G162" s="7" t="inlineStr">
         <is>
-          <t>Wayfair Custody
+          <t>EuropeMarketPlace Custody
 [OnHand = 0]</t>
         </is>
       </c>
@@ -9517,7 +9517,7 @@
     <row r="164" ht="24" customHeight="1">
       <c r="A164" s="21" t="inlineStr">
         <is>
-          <t>Process 2.2.10: Factory → ICC → AU Whs → NZ Whs → UK Wayfair (Multi-Hub Intercompany Re-Export Direct Invoicing)</t>
+          <t>Process 2.2.10: Factory → ICC → AU Whs → NZ Whs → EuropeMarketPlace (Multi-Hub Intercompany Re-Export Direct Invoicing)</t>
         </is>
       </c>
     </row>
@@ -9534,7 +9534,7 @@
       </c>
       <c r="C165" s="5" t="inlineStr">
         <is>
-          <t>[Purchasing] Issue Factory PO in USD (OPOR) @ ICCNGB → [Vendor Production Commitment]</t>
+          <t>[Purchasing] Issue Factory PO in USD (OPOR) @ ICCChina → [Vendor Production Commitment]</t>
         </is>
       </c>
       <c r="D165" s="22" t="inlineStr">
@@ -9549,7 +9549,7 @@
       </c>
       <c r="F165" s="22" t="inlineStr">
         <is>
-          <t>ICCNGB</t>
+          <t>ICCChina</t>
         </is>
       </c>
       <c r="G165" s="5" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="C166" s="7" t="inlineStr">
         <is>
-          <t>[Logistics] Post Inward Factory GRPO (OPDN) @ ICCNGB → [Origin Spot FX Base Cost Capitalization]</t>
+          <t>[Logistics] Post Inward Factory GRPO (OPDN) @ ICCChina → [Origin Spot FX Base Cost Capitalization]</t>
         </is>
       </c>
       <c r="D166" s="23" t="inlineStr">
@@ -9596,12 +9596,12 @@
       </c>
       <c r="F166" s="23" t="inlineStr">
         <is>
-          <t>ICCNGB</t>
+          <t>ICCChina</t>
         </is>
       </c>
       <c r="G166" s="7" t="inlineStr">
         <is>
-          <t>ICCNGB [OnHand = 100]</t>
+          <t>ICCChina [OnHand = 100]</t>
         </is>
       </c>
       <c r="H166" s="7" t="inlineStr">
@@ -9628,7 +9628,7 @@
       </c>
       <c r="C167" s="5" t="inlineStr">
         <is>
-          <t>[Finance] Capitalize Origin Actual Landed Cost (OIPF 'A') @ ICCNGB → [Source MWAG Lock]</t>
+          <t>[Finance] Capitalize Origin Actual Landed Cost (OIPF 'A') @ ICCChina → [Source MWAG Lock]</t>
         </is>
       </c>
       <c r="D167" s="22" t="inlineStr">
@@ -9643,12 +9643,12 @@
       </c>
       <c r="F167" s="22" t="inlineStr">
         <is>
-          <t>ICCNGB</t>
+          <t>ICCChina</t>
         </is>
       </c>
       <c r="G167" s="5" t="inlineStr">
         <is>
-          <t>ICCNGB [OnHand = 100]</t>
+          <t>ICCChina [OnHand = 100]</t>
         </is>
       </c>
       <c r="H167" s="5" t="inlineStr">
@@ -9675,7 +9675,7 @@
       </c>
       <c r="C168" s="7" t="inlineStr">
         <is>
-          <t>[Purchasing] Create Inventory Transfer Request (OWTQ) @ ICCNGB → [Sea Voyage Picking Allocation]</t>
+          <t>[Purchasing] Create Inventory Transfer Request (OWTQ) @ ICCChina → [Sea Voyage Picking Allocation]</t>
         </is>
       </c>
       <c r="D168" s="23" t="inlineStr">
@@ -9690,12 +9690,12 @@
       </c>
       <c r="F168" s="23" t="inlineStr">
         <is>
-          <t>ICCNGB → ICCSIT</t>
+          <t>ICCChina → ICCSIT</t>
         </is>
       </c>
       <c r="G168" s="7" t="inlineStr">
         <is>
-          <t>ICCNGB [IsCommited = +100]</t>
+          <t>ICCChina [IsCommited = +100]</t>
         </is>
       </c>
       <c r="H168" s="7" t="inlineStr">
@@ -9722,7 +9722,7 @@
       </c>
       <c r="C169" s="5" t="inlineStr">
         <is>
-          <t>[Logistics] Post In-Transit Stock Transfer (OWTR) based on OWTQ @ ICCNGB to ICCSIT → [Goods In-Transit Balance Sheet Capitalization]</t>
+          <t>[Logistics] Post In-Transit Stock Transfer (OWTR) based on OWTQ @ ICCChina to ICCSIT → [Goods In-Transit Balance Sheet Capitalization]</t>
         </is>
       </c>
       <c r="D169" s="22" t="inlineStr">
@@ -9737,7 +9737,7 @@
       </c>
       <c r="F169" s="22" t="inlineStr">
         <is>
-          <t>ICCNGB → ICCSIT</t>
+          <t>ICCChina → ICCSIT</t>
         </is>
       </c>
       <c r="G169" s="5" t="inlineStr">
@@ -9769,7 +9769,7 @@
       </c>
       <c r="C170" s="7" t="inlineStr">
         <is>
-          <t>[Logistics] Post AU Port Intercompany GRPO (OPDN) Synchronized with Origin Goods Issue (OIGE) @ FDMSYD → [AU Port Arrival Inbound Clearance]</t>
+          <t>[Logistics] Post AU Port Intercompany GRPO (OPDN) Synchronized with Origin Goods Issue (OIGE) @ AU Warehouse → [AU Port Arrival Inbound Clearance]</t>
         </is>
       </c>
       <c r="D170" s="23" t="inlineStr">
@@ -9784,12 +9784,12 @@
       </c>
       <c r="F170" s="23" t="inlineStr">
         <is>
-          <t>ICCSIT → FDMSYD</t>
+          <t>ICCSIT → AU Warehouse</t>
         </is>
       </c>
       <c r="G170" s="7" t="inlineStr">
         <is>
-          <t>FDMSYD [OnHand = 100]</t>
+          <t>AU Warehouse [OnHand = 100]</t>
         </is>
       </c>
       <c r="H170" s="7" t="inlineStr">
@@ -9817,7 +9817,7 @@
       </c>
       <c r="C171" s="5" t="inlineStr">
         <is>
-          <t>[Finance] Overwrite AU Destination Landed Cost (OIPF 'A') @ FDMSYD → [AU DC Capitalization &amp; G/L 200050 Reconciled]</t>
+          <t>[Finance] Overwrite AU Destination Landed Cost (OIPF 'A') @ AU Warehouse → [AU DC Capitalization &amp; G/L 200050 Reconciled]</t>
         </is>
       </c>
       <c r="D171" s="22" t="inlineStr">
@@ -9832,12 +9832,12 @@
       </c>
       <c r="F171" s="22" t="inlineStr">
         <is>
-          <t>FDMSYD</t>
+          <t>AU Warehouse</t>
         </is>
       </c>
       <c r="G171" s="5" t="inlineStr">
         <is>
-          <t>FDMSYD [OnHand = 100]</t>
+          <t>AU Warehouse [OnHand = 100]</t>
         </is>
       </c>
       <c r="H171" s="5" t="inlineStr">
@@ -9864,7 +9864,7 @@
       </c>
       <c r="C172" s="7" t="inlineStr">
         <is>
-          <t>[Purchasing] Create Trans-Tasman Transfer Request (OWTQ) @ FDMSYD → [NZ Relay Picking Allocation]</t>
+          <t>[Purchasing] Create Trans-Tasman Transfer Request (OWTQ) @ AU Warehouse → [NZ Relay Picking Allocation]</t>
         </is>
       </c>
       <c r="D172" s="23" t="inlineStr">
@@ -9879,12 +9879,12 @@
       </c>
       <c r="F172" s="23" t="inlineStr">
         <is>
-          <t>FDMSYD → NZSIT</t>
+          <t>AU Warehouse → NZSIT</t>
         </is>
       </c>
       <c r="G172" s="7" t="inlineStr">
         <is>
-          <t>FDMSYD [IsCommited = +100]</t>
+          <t>AU Warehouse [IsCommited = +100]</t>
         </is>
       </c>
       <c r="H172" s="7" t="inlineStr">
@@ -9911,7 +9911,7 @@
       </c>
       <c r="C173" s="5" t="inlineStr">
         <is>
-          <t>[Logistics] Post Trans-Tasman Relay Transfer (OWTR) based on OWTQ @ FDMSYD to NZSIT → [Regional Transit Tracking]</t>
+          <t>[Logistics] Post Trans-Tasman Relay Transfer (OWTR) based on OWTQ @ AU Warehouse to NZSIT → [Regional Transit Tracking]</t>
         </is>
       </c>
       <c r="D173" s="22" t="inlineStr">
@@ -9926,7 +9926,7 @@
       </c>
       <c r="F173" s="22" t="inlineStr">
         <is>
-          <t>FDMSYD → NZSIT</t>
+          <t>AU Warehouse → NZSIT</t>
         </is>
       </c>
       <c r="G173" s="5" t="inlineStr">
@@ -10067,7 +10067,7 @@
       </c>
       <c r="F176" s="23" t="inlineStr">
         <is>
-          <t>NZNTH → UKSIT</t>
+          <t>NZNTH → EuropeSIT</t>
         </is>
       </c>
       <c r="G176" s="7" t="inlineStr">
@@ -10099,7 +10099,7 @@
       </c>
       <c r="C177" s="5" t="inlineStr">
         <is>
-          <t>[Logistics] Post UK Maritime Transfer (OWTR) based on OWTQ @ NZNTH to UKSIT → [Long-Haul Transit Tracking]</t>
+          <t>[Logistics] Post UK Maritime Transfer (OWTR) based on OWTQ @ NZNTH to EuropeSIT → [Long-Haul Transit Tracking]</t>
         </is>
       </c>
       <c r="D177" s="22" t="inlineStr">
@@ -10114,12 +10114,12 @@
       </c>
       <c r="F177" s="22" t="inlineStr">
         <is>
-          <t>NZNTH → UKSIT</t>
+          <t>NZNTH → EuropeSIT</t>
         </is>
       </c>
       <c r="G177" s="5" t="inlineStr">
         <is>
-          <t>UKSIT [OnHand = 100]</t>
+          <t>EuropeSIT [OnHand = 100]</t>
         </is>
       </c>
       <c r="H177" s="5" t="inlineStr">
@@ -10129,7 +10129,7 @@
       </c>
       <c r="I177" s="5" t="inlineStr">
         <is>
-          <t>Dr 100050 (UKSIT) $54,500 / Cr 100040 ($54,500)</t>
+          <t>Dr 100050 (EuropeSIT) $54,500 / Cr 100040 ($54,500)</t>
         </is>
       </c>
     </row>
@@ -10146,7 +10146,7 @@
       </c>
       <c r="C178" s="7" t="inlineStr">
         <is>
-          <t>[Logistics] Post UK Inward GRPO (OPDN) @ UKWYF → [UK Port Arrival Inbound Clearance]</t>
+          <t>[Logistics] Post UK Inward GRPO (OPDN) @ EuropeMarketPlace → [UK Port Arrival Inbound Clearance]</t>
         </is>
       </c>
       <c r="D178" s="23" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="F178" s="23" t="inlineStr">
         <is>
-          <t>UKWYF</t>
+          <t>EuropeMarketPlace</t>
         </is>
       </c>
       <c r="G178" s="7" t="inlineStr">
         <is>
-          <t>UKWYF [OnHand = 100]</t>
+          <t>EuropeMarketPlace [OnHand = 100]</t>
         </is>
       </c>
       <c r="H178" s="7" t="inlineStr">
@@ -10176,7 +10176,7 @@
       </c>
       <c r="I178" s="7" t="inlineStr">
         <is>
-          <t>Dr 100040 (UKWYF) $54,500 / Cr 100050 ($54,500)</t>
+          <t>Dr 100040 (EuropeMarketPlace) $54,500 / Cr 100050 ($54,500)</t>
         </is>
       </c>
     </row>
@@ -10193,7 +10193,7 @@
       </c>
       <c r="C179" s="5" t="inlineStr">
         <is>
-          <t>[Finance] Capitalize UK Landed Cost (OIPF 'A') @ UKWYF → [Final Stacked Capitalization &amp; G/L 200050 Reconciled]</t>
+          <t>[Finance] Capitalize UK Landed Cost (OIPF 'A') @ EuropeMarketPlace → [Final Stacked Capitalization &amp; G/L 200050 Reconciled]</t>
         </is>
       </c>
       <c r="D179" s="22" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="F179" s="22" t="inlineStr">
         <is>
-          <t>UKWYF</t>
+          <t>EuropeMarketPlace</t>
         </is>
       </c>
       <c r="G179" s="5" t="inlineStr">
         <is>
-          <t>UKWYF [OnHand = 100]</t>
+          <t>EuropeMarketPlace [OnHand = 100]</t>
         </is>
       </c>
       <c r="H179" s="5" t="inlineStr">
@@ -10223,7 +10223,7 @@
       </c>
       <c r="I179" s="5" t="inlineStr">
         <is>
-          <t>Dr 100040 (UKWYF) $1,500 / Cr 200010 ($1,500)</t>
+          <t>Dr 100040 (EuropeMarketPlace) $1,500 / Cr 200010 ($1,500)</t>
         </is>
       </c>
     </row>
@@ -10240,7 +10240,7 @@
       </c>
       <c r="C180" s="7" t="inlineStr">
         <is>
-          <t>[Sales] Book Wholesale Sales Order (ORDR) @ UKWYF → [Wayfair Channel Allocation]</t>
+          <t>[Sales] Book Wholesale Sales Order (ORDR) @ EuropeMarketPlace → [EuropeMarketPlace Channel Allocation]</t>
         </is>
       </c>
       <c r="D180" s="23" t="inlineStr">
@@ -10255,12 +10255,12 @@
       </c>
       <c r="F180" s="23" t="inlineStr">
         <is>
-          <t>UKWYF</t>
+          <t>EuropeMarketPlace</t>
         </is>
       </c>
       <c r="G180" s="7" t="inlineStr">
         <is>
-          <t>UKWYF [Reserved = +100]</t>
+          <t>EuropeMarketPlace [Reserved = +100]</t>
         </is>
       </c>
       <c r="H180" s="7" t="inlineStr">
@@ -10287,7 +10287,7 @@
       </c>
       <c r="C181" s="5" t="inlineStr">
         <is>
-          <t>[Logistics] Post Direct Wholesale AR Invoice (OINV) @ UKWYF → [Wayfair Channel Revenue Recognition]</t>
+          <t>[Logistics] Post Direct Wholesale AR Invoice (OINV) @ EuropeMarketPlace → [EuropeMarketPlace Channel Revenue Recognition]</t>
         </is>
       </c>
       <c r="D181" s="22" t="inlineStr">
@@ -10302,12 +10302,12 @@
       </c>
       <c r="F181" s="22" t="inlineStr">
         <is>
-          <t>UKWYF</t>
+          <t>EuropeMarketPlace</t>
         </is>
       </c>
       <c r="G181" s="5" t="inlineStr">
         <is>
-          <t>Wayfair Custody
+          <t>EuropeMarketPlace Custody
 [OnHand = 0]</t>
         </is>
       </c>
@@ -10325,7 +10325,7 @@
     <row r="183" ht="24" customHeight="1">
       <c r="A183" s="21" t="inlineStr">
         <is>
-          <t>Process 2.2.11: Factory → ICC → NZ Whs → AU Whs → UK Wayfair (Multi-Hub Intercompany Re-Export Direct Invoicing)</t>
+          <t>Process 2.2.11: Factory → ICC → NZ Whs → AU Whs → EuropeMarketPlace (Multi-Hub Intercompany Re-Export Direct Invoicing)</t>
         </is>
       </c>
     </row>
@@ -10342,7 +10342,7 @@
       </c>
       <c r="C184" s="7" t="inlineStr">
         <is>
-          <t>[Purchasing] Issue Factory PO in USD (OPOR) @ ICCNGB → [Vendor Production Commitment]</t>
+          <t>[Purchasing] Issue Factory PO in USD (OPOR) @ ICCChina → [Vendor Production Commitment]</t>
         </is>
       </c>
       <c r="D184" s="23" t="inlineStr">
@@ -10357,7 +10357,7 @@
       </c>
       <c r="F184" s="23" t="inlineStr">
         <is>
-          <t>ICCNGB</t>
+          <t>ICCChina</t>
         </is>
       </c>
       <c r="G184" s="7" t="inlineStr">
@@ -10389,7 +10389,7 @@
       </c>
       <c r="C185" s="5" t="inlineStr">
         <is>
-          <t>[Logistics] Post Inward Factory GRPO (OPDN) @ ICCNGB → [Origin Spot FX Base Cost Capitalization]</t>
+          <t>[Logistics] Post Inward Factory GRPO (OPDN) @ ICCChina → [Origin Spot FX Base Cost Capitalization]</t>
         </is>
       </c>
       <c r="D185" s="22" t="inlineStr">
@@ -10404,12 +10404,12 @@
       </c>
       <c r="F185" s="22" t="inlineStr">
         <is>
-          <t>ICCNGB</t>
+          <t>ICCChina</t>
         </is>
       </c>
       <c r="G185" s="5" t="inlineStr">
         <is>
-          <t>ICCNGB [OnHand = 100]</t>
+          <t>ICCChina [OnHand = 100]</t>
         </is>
       </c>
       <c r="H185" s="5" t="inlineStr">
@@ -10436,7 +10436,7 @@
       </c>
       <c r="C186" s="7" t="inlineStr">
         <is>
-          <t>[Finance] Capitalize Origin Actual Landed Cost (OIPF 'A') @ ICCNGB → [Source MWAG Lock]</t>
+          <t>[Finance] Capitalize Origin Actual Landed Cost (OIPF 'A') @ ICCChina → [Source MWAG Lock]</t>
         </is>
       </c>
       <c r="D186" s="23" t="inlineStr">
@@ -10451,12 +10451,12 @@
       </c>
       <c r="F186" s="23" t="inlineStr">
         <is>
-          <t>ICCNGB</t>
+          <t>ICCChina</t>
         </is>
       </c>
       <c r="G186" s="7" t="inlineStr">
         <is>
-          <t>ICCNGB [OnHand = 100]</t>
+          <t>ICCChina [OnHand = 100]</t>
         </is>
       </c>
       <c r="H186" s="7" t="inlineStr">
@@ -10483,7 +10483,7 @@
       </c>
       <c r="C187" s="5" t="inlineStr">
         <is>
-          <t>[Purchasing] Create Inventory Transfer Request (OWTQ) @ ICCNGB → [NZ Sea Voyage Picking Allocation]</t>
+          <t>[Purchasing] Create Inventory Transfer Request (OWTQ) @ ICCChina → [NZ Sea Voyage Picking Allocation]</t>
         </is>
       </c>
       <c r="D187" s="22" t="inlineStr">
@@ -10498,12 +10498,12 @@
       </c>
       <c r="F187" s="22" t="inlineStr">
         <is>
-          <t>ICCNGB → ICCSIT</t>
+          <t>ICCChina → ICCSIT</t>
         </is>
       </c>
       <c r="G187" s="5" t="inlineStr">
         <is>
-          <t>ICCNGB [IsCommited = +100]</t>
+          <t>ICCChina [IsCommited = +100]</t>
         </is>
       </c>
       <c r="H187" s="5" t="inlineStr">
@@ -10530,7 +10530,7 @@
       </c>
       <c r="C188" s="7" t="inlineStr">
         <is>
-          <t>[Logistics] Post In-Transit Stock Transfer (OWTR) based on OWTQ @ ICCNGB to ICCSIT → [Goods In-Transit Balance Sheet Capitalization]</t>
+          <t>[Logistics] Post In-Transit Stock Transfer (OWTR) based on OWTQ @ ICCChina to ICCSIT → [Goods In-Transit Balance Sheet Capitalization]</t>
         </is>
       </c>
       <c r="D188" s="23" t="inlineStr">
@@ -10545,7 +10545,7 @@
       </c>
       <c r="F188" s="23" t="inlineStr">
         <is>
-          <t>ICCNGB → ICCSIT</t>
+          <t>ICCChina → ICCSIT</t>
         </is>
       </c>
       <c r="G188" s="7" t="inlineStr">
@@ -10765,7 +10765,7 @@
       </c>
       <c r="C193" s="5" t="inlineStr">
         <is>
-          <t>[Logistics] Post AU Cross-DB Intercompany GRPO (OPDN) Synchronized with Origin Goods Issue (OIGE) @ FDMSYD → [AU Port Inbound Clearance]</t>
+          <t>[Logistics] Post AU Cross-DB Intercompany GRPO (OPDN) Synchronized with Origin Goods Issue (OIGE) @ AU Warehouse → [AU Port Inbound Clearance]</t>
         </is>
       </c>
       <c r="D193" s="22" t="inlineStr">
@@ -10780,12 +10780,12 @@
       </c>
       <c r="F193" s="22" t="inlineStr">
         <is>
-          <t>NZSIT → FDMSYD</t>
+          <t>NZSIT → AU Warehouse</t>
         </is>
       </c>
       <c r="G193" s="5" t="inlineStr">
         <is>
-          <t>FDMSYD [OnHand = 100]</t>
+          <t>AU Warehouse [OnHand = 100]</t>
         </is>
       </c>
       <c r="H193" s="5" t="inlineStr">
@@ -10813,7 +10813,7 @@
       </c>
       <c r="C194" s="7" t="inlineStr">
         <is>
-          <t>[Finance] Overwrite AU Landed Cost (OIPF 'A') @ FDMSYD → [AU DC Moving Average Lock]</t>
+          <t>[Finance] Overwrite AU Landed Cost (OIPF 'A') @ AU Warehouse → [AU DC Moving Average Lock]</t>
         </is>
       </c>
       <c r="D194" s="23" t="inlineStr">
@@ -10828,12 +10828,12 @@
       </c>
       <c r="F194" s="23" t="inlineStr">
         <is>
-          <t>FDMSYD</t>
+          <t>AU Warehouse</t>
         </is>
       </c>
       <c r="G194" s="7" t="inlineStr">
         <is>
-          <t>FDMSYD [OnHand = 100]</t>
+          <t>AU Warehouse [OnHand = 100]</t>
         </is>
       </c>
       <c r="H194" s="7" t="inlineStr">
@@ -10843,7 +10843,7 @@
       </c>
       <c r="I194" s="7" t="inlineStr">
         <is>
-          <t>Dr 100010 (FDMSYD) $2,300 / Cr 200010 ($2,300)</t>
+          <t>Dr 100010 (AU Warehouse) $2,300 / Cr 200010 ($2,300)</t>
         </is>
       </c>
     </row>
@@ -10860,7 +10860,7 @@
       </c>
       <c r="C195" s="5" t="inlineStr">
         <is>
-          <t>[Purchasing] Create UK Export Transfer Request (OWTQ) @ FDMSYD → [UK Voyage Picking Allocation]</t>
+          <t>[Purchasing] Create UK Export Transfer Request (OWTQ) @ AU Warehouse → [UK Voyage Picking Allocation]</t>
         </is>
       </c>
       <c r="D195" s="22" t="inlineStr">
@@ -10875,12 +10875,12 @@
       </c>
       <c r="F195" s="22" t="inlineStr">
         <is>
-          <t>FDMSYD → UKSIT</t>
+          <t>AU Warehouse → EuropeSIT</t>
         </is>
       </c>
       <c r="G195" s="5" t="inlineStr">
         <is>
-          <t>FDMSYD [IsCommited = +100]</t>
+          <t>AU Warehouse [IsCommited = +100]</t>
         </is>
       </c>
       <c r="H195" s="5" t="inlineStr">
@@ -10907,7 +10907,7 @@
       </c>
       <c r="C196" s="7" t="inlineStr">
         <is>
-          <t>[Logistics] Post UK Maritime Transfer (OWTR) based on OWTQ @ FDMSYD to UKSIT → [Long-Haul Transit Tracking]</t>
+          <t>[Logistics] Post UK Maritime Transfer (OWTR) based on OWTQ @ AU Warehouse to EuropeSIT → [Long-Haul Transit Tracking]</t>
         </is>
       </c>
       <c r="D196" s="23" t="inlineStr">
@@ -10922,12 +10922,12 @@
       </c>
       <c r="F196" s="23" t="inlineStr">
         <is>
-          <t>FDMSYD → UKSIT</t>
+          <t>AU Warehouse → EuropeSIT</t>
         </is>
       </c>
       <c r="G196" s="7" t="inlineStr">
         <is>
-          <t>UKSIT [OnHand = 100]</t>
+          <t>EuropeSIT [OnHand = 100]</t>
         </is>
       </c>
       <c r="H196" s="7" t="inlineStr">
@@ -10937,7 +10937,7 @@
       </c>
       <c r="I196" s="7" t="inlineStr">
         <is>
-          <t>Dr 100050 (UKSIT) $54,500 / Cr 100010 ($54,500)</t>
+          <t>Dr 100050 (EuropeSIT) $54,500 / Cr 100010 ($54,500)</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="C197" s="5" t="inlineStr">
         <is>
-          <t>[Logistics] Post UK Inward GRPO (OPDN) @ UKWYF → [UK Port Arrival Inbound Clearance]</t>
+          <t>[Logistics] Post UK Inward GRPO (OPDN) @ EuropeMarketPlace → [UK Port Arrival Inbound Clearance]</t>
         </is>
       </c>
       <c r="D197" s="22" t="inlineStr">
@@ -10969,12 +10969,12 @@
       </c>
       <c r="F197" s="22" t="inlineStr">
         <is>
-          <t>UKWYF</t>
+          <t>EuropeMarketPlace</t>
         </is>
       </c>
       <c r="G197" s="5" t="inlineStr">
         <is>
-          <t>UKWYF [OnHand = 100]</t>
+          <t>EuropeMarketPlace [OnHand = 100]</t>
         </is>
       </c>
       <c r="H197" s="5" t="inlineStr">
@@ -10984,7 +10984,7 @@
       </c>
       <c r="I197" s="5" t="inlineStr">
         <is>
-          <t>Dr 100040 (UKWYF) $54,500 / Cr 100050 ($54,500)</t>
+          <t>Dr 100040 (EuropeMarketPlace) $54,500 / Cr 100050 ($54,500)</t>
         </is>
       </c>
     </row>
@@ -11001,7 +11001,7 @@
       </c>
       <c r="C198" s="7" t="inlineStr">
         <is>
-          <t>[Finance] Capitalize UK Landed Cost (OIPF 'A') @ UKWYF → [Final Stacked Capitalization &amp; G/L 200050 Reconciled]</t>
+          <t>[Finance] Capitalize UK Landed Cost (OIPF 'A') @ EuropeMarketPlace → [Final Stacked Capitalization &amp; G/L 200050 Reconciled]</t>
         </is>
       </c>
       <c r="D198" s="23" t="inlineStr">
@@ -11016,12 +11016,12 @@
       </c>
       <c r="F198" s="23" t="inlineStr">
         <is>
-          <t>UKWYF</t>
+          <t>EuropeMarketPlace</t>
         </is>
       </c>
       <c r="G198" s="7" t="inlineStr">
         <is>
-          <t>UKWYF [OnHand = 100]</t>
+          <t>EuropeMarketPlace [OnHand = 100]</t>
         </is>
       </c>
       <c r="H198" s="7" t="inlineStr">
@@ -11031,7 +11031,7 @@
       </c>
       <c r="I198" s="7" t="inlineStr">
         <is>
-          <t>Dr 100040 (UKWYF) $1,500 / Cr 200010 ($1,500)</t>
+          <t>Dr 100040 (EuropeMarketPlace) $1,500 / Cr 200010 ($1,500)</t>
         </is>
       </c>
     </row>
@@ -11048,7 +11048,7 @@
       </c>
       <c r="C199" s="5" t="inlineStr">
         <is>
-          <t>[Sales] Book Wholesale Sales Order (ORDR) @ UKWYF → [Wayfair Channel Allocation]</t>
+          <t>[Sales] Book Wholesale Sales Order (ORDR) @ EuropeMarketPlace → [EuropeMarketPlace Channel Allocation]</t>
         </is>
       </c>
       <c r="D199" s="22" t="inlineStr">
@@ -11063,12 +11063,12 @@
       </c>
       <c r="F199" s="22" t="inlineStr">
         <is>
-          <t>UKWYF</t>
+          <t>EuropeMarketPlace</t>
         </is>
       </c>
       <c r="G199" s="5" t="inlineStr">
         <is>
-          <t>UKWYF [Reserved = +100]</t>
+          <t>EuropeMarketPlace [Reserved = +100]</t>
         </is>
       </c>
       <c r="H199" s="5" t="inlineStr">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C200" s="7" t="inlineStr">
         <is>
-          <t>[Logistics] Post Direct Wholesale AR Invoice (OINV) @ UKWYF → [Wayfair Channel Revenue Recognition]</t>
+          <t>[Logistics] Post Direct Wholesale AR Invoice (OINV) @ EuropeMarketPlace → [EuropeMarketPlace Channel Revenue Recognition]</t>
         </is>
       </c>
       <c r="D200" s="23" t="inlineStr">
@@ -11110,12 +11110,12 @@
       </c>
       <c r="F200" s="23" t="inlineStr">
         <is>
-          <t>UKWYF</t>
+          <t>EuropeMarketPlace</t>
         </is>
       </c>
       <c r="G200" s="7" t="inlineStr">
         <is>
-          <t>Wayfair Custody
+          <t>EuropeMarketPlace Custody
 [OnHand = 0]</t>
         </is>
       </c>
@@ -11451,7 +11451,7 @@
       </c>
       <c r="C213" s="5" t="inlineStr">
         <is>
-          <t>[Purchasing] Issue Factory PO in USD (OPOR) @ ICCNGB → [Vendor Production Commitment]</t>
+          <t>[Purchasing] Issue Factory PO in USD (OPOR) @ ICCChina → [Vendor Production Commitment]</t>
         </is>
       </c>
       <c r="D213" s="22" t="inlineStr">
@@ -11466,7 +11466,7 @@
       </c>
       <c r="F213" s="22" t="inlineStr">
         <is>
-          <t>ICCNGB</t>
+          <t>ICCChina</t>
         </is>
       </c>
       <c r="G213" s="5" t="inlineStr">
@@ -11499,7 +11499,7 @@
       </c>
       <c r="C214" s="7" t="inlineStr">
         <is>
-          <t>[Logistics] Post Inward Factory GRPO (OPDN) @ ICCNGB → [Origin Spot FX Base Cost Capitalization]</t>
+          <t>[Logistics] Post Inward Factory GRPO (OPDN) @ ICCChina → [Origin Spot FX Base Cost Capitalization]</t>
         </is>
       </c>
       <c r="D214" s="23" t="inlineStr">
@@ -11514,12 +11514,12 @@
       </c>
       <c r="F214" s="23" t="inlineStr">
         <is>
-          <t>ICCNGB</t>
+          <t>ICCChina</t>
         </is>
       </c>
       <c r="G214" s="7" t="inlineStr">
         <is>
-          <t>ICCNGB [OnHand=100]</t>
+          <t>ICCChina [OnHand=100]</t>
         </is>
       </c>
       <c r="H214" s="7" t="inlineStr">
@@ -11546,7 +11546,7 @@
       </c>
       <c r="C215" s="5" t="inlineStr">
         <is>
-          <t>[Finance] Capitalize Origin Actual Landed Cost (OIPF 'A') @ ICCNGB → [Source MWAG Lock]</t>
+          <t>[Finance] Capitalize Origin Actual Landed Cost (OIPF 'A') @ ICCChina → [Source MWAG Lock]</t>
         </is>
       </c>
       <c r="D215" s="22" t="inlineStr">
@@ -11561,12 +11561,12 @@
       </c>
       <c r="F215" s="22" t="inlineStr">
         <is>
-          <t>ICCNGB</t>
+          <t>ICCChina</t>
         </is>
       </c>
       <c r="G215" s="5" t="inlineStr">
         <is>
-          <t>ICCNGB [OnHand=100]</t>
+          <t>ICCChina [OnHand=100]</t>
         </is>
       </c>
       <c r="H215" s="5" t="inlineStr">
@@ -11593,7 +11593,7 @@
       </c>
       <c r="C216" s="7" t="inlineStr">
         <is>
-          <t>[Purchasing] Create Inventory Transfer Request (OWTQ) @ ICCNGB → [Sea Voyage Picking Allocation]</t>
+          <t>[Purchasing] Create Inventory Transfer Request (OWTQ) @ ICCChina → [Sea Voyage Picking Allocation]</t>
         </is>
       </c>
       <c r="D216" s="23" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="F216" s="23" t="inlineStr">
         <is>
-          <t>ICCNGB → ICCSIT</t>
+          <t>ICCChina → ICCSIT</t>
         </is>
       </c>
       <c r="G216" s="7" t="inlineStr">
         <is>
-          <t>ICCNGB [IsCommited = +100]</t>
+          <t>ICCChina [IsCommited = +100]</t>
         </is>
       </c>
       <c r="H216" s="7" t="inlineStr">
@@ -11640,7 +11640,7 @@
       </c>
       <c r="C217" s="5" t="inlineStr">
         <is>
-          <t>[Logistics] Post Ocean In-Transit Transfer (OWTR) based on OWTQ @ ICCNGB to ICCSIT → [Sea Voyage Tracking]</t>
+          <t>[Logistics] Post Ocean In-Transit Transfer (OWTR) based on OWTQ @ ICCChina to ICCSIT → [Sea Voyage Tracking]</t>
         </is>
       </c>
       <c r="D217" s="22" t="inlineStr">
@@ -11655,7 +11655,7 @@
       </c>
       <c r="F217" s="22" t="inlineStr">
         <is>
-          <t>ICCNGB → ICCSIT</t>
+          <t>ICCChina → ICCSIT</t>
         </is>
       </c>
       <c r="G217" s="5" t="inlineStr">
@@ -11964,7 +11964,7 @@
     <row r="225" ht="24" customHeight="1">
       <c r="A225" s="21" t="inlineStr">
         <is>
-          <t>Process 2.3.3: Factory → UK Wayfair (Direct Factory Shipment Direct Wholesale Invoicing)</t>
+          <t>Process 2.3.3: Factory → EuropeMarketPlace (Direct Factory Shipment Direct Wholesale Invoicing)</t>
         </is>
       </c>
     </row>
@@ -11981,7 +11981,7 @@
       </c>
       <c r="C226" s="7" t="inlineStr">
         <is>
-          <t>[Purchasing] Issue Direct Factory PO in USD (OPOR) @ UKWYF → [Vendor Production Commitment]</t>
+          <t>[Purchasing] Issue Direct Factory PO in USD (OPOR) @ EuropeMarketPlace → [Vendor Production Commitment]</t>
         </is>
       </c>
       <c r="D226" s="23" t="inlineStr">
@@ -11996,7 +11996,7 @@
       </c>
       <c r="F226" s="23" t="inlineStr">
         <is>
-          <t>UKWYF</t>
+          <t>EuropeMarketPlace</t>
         </is>
       </c>
       <c r="G226" s="7" t="inlineStr">
@@ -12028,7 +12028,7 @@
       </c>
       <c r="C227" s="5" t="inlineStr">
         <is>
-          <t>[Logistics] Post Direct Inbound GRPO (OPDN) @ UKWYF → [Spot FX Base Cost Capitalization]</t>
+          <t>[Logistics] Post Direct Inbound GRPO (OPDN) @ EuropeMarketPlace → [Spot FX Base Cost Capitalization]</t>
         </is>
       </c>
       <c r="D227" s="22" t="inlineStr">
@@ -12043,12 +12043,12 @@
       </c>
       <c r="F227" s="22" t="inlineStr">
         <is>
-          <t>UKWYF</t>
+          <t>EuropeMarketPlace</t>
         </is>
       </c>
       <c r="G227" s="5" t="inlineStr">
         <is>
-          <t>UKWYF [OnHand = 100]</t>
+          <t>EuropeMarketPlace [OnHand = 100]</t>
         </is>
       </c>
       <c r="H227" s="5" t="inlineStr">
@@ -12058,7 +12058,7 @@
       </c>
       <c r="I227" s="5" t="inlineStr">
         <is>
-          <t>Dr 100040 (UKWYF) $40,000 / Cr 200060 $40,000</t>
+          <t>Dr 100040 (EuropeMarketPlace) $40,000 / Cr 200060 $40,000</t>
         </is>
       </c>
     </row>
@@ -12075,7 +12075,7 @@
       </c>
       <c r="C228" s="7" t="inlineStr">
         <is>
-          <t>[Finance] Accrue UK Estimated Landed Cost (OIPF 'E') @ UKWYF → [Provisional Felixstowe Port Duty Allocation]</t>
+          <t>[Finance] Accrue UK Estimated Landed Cost (OIPF 'E') @ EuropeMarketPlace → [Provisional Felixstowe Port Duty Allocation]</t>
         </is>
       </c>
       <c r="D228" s="23" t="inlineStr">
@@ -12090,12 +12090,12 @@
       </c>
       <c r="F228" s="23" t="inlineStr">
         <is>
-          <t>UKWYF</t>
+          <t>EuropeMarketPlace</t>
         </is>
       </c>
       <c r="G228" s="7" t="inlineStr">
         <is>
-          <t>UKWYF [OnHand = 100]</t>
+          <t>EuropeMarketPlace [OnHand = 100]</t>
         </is>
       </c>
       <c r="H228" s="7" t="inlineStr">
@@ -12105,7 +12105,7 @@
       </c>
       <c r="I228" s="7" t="inlineStr">
         <is>
-          <t>Dr 100040 (UKWYF) $16,000 / Cr 200050 $16,000</t>
+          <t>Dr 100040 (EuropeMarketPlace) $16,000 / Cr 200050 $16,000</t>
         </is>
       </c>
     </row>
@@ -12122,7 +12122,7 @@
       </c>
       <c r="C229" s="5" t="inlineStr">
         <is>
-          <t>[Finance] Overwrite UK Actual Landed Cost (OIPF 'A') @ UKWYF → [Final Valuation &amp; G/L 200050 Reconciled]</t>
+          <t>[Finance] Overwrite UK Actual Landed Cost (OIPF 'A') @ EuropeMarketPlace → [Final Valuation &amp; G/L 200050 Reconciled]</t>
         </is>
       </c>
       <c r="D229" s="22" t="inlineStr">
@@ -12137,12 +12137,12 @@
       </c>
       <c r="F229" s="22" t="inlineStr">
         <is>
-          <t>UKWYF</t>
+          <t>EuropeMarketPlace</t>
         </is>
       </c>
       <c r="G229" s="5" t="inlineStr">
         <is>
-          <t>UKWYF [OnHand = 100]</t>
+          <t>EuropeMarketPlace [OnHand = 100]</t>
         </is>
       </c>
       <c r="H229" s="5" t="inlineStr">
@@ -12169,7 +12169,7 @@
       </c>
       <c r="C230" s="7" t="inlineStr">
         <is>
-          <t>[Sales] Book Wayfair EDI Wholesale Order (ORDR) @ UKWYF → [Channel Stock Allocation]</t>
+          <t>[Sales] Book EuropeMarketPlace EDI Wholesale Order (ORDR) @ EuropeMarketPlace → [Channel Stock Allocation]</t>
         </is>
       </c>
       <c r="D230" s="23" t="inlineStr">
@@ -12184,12 +12184,12 @@
       </c>
       <c r="F230" s="23" t="inlineStr">
         <is>
-          <t>UKWYF</t>
+          <t>EuropeMarketPlace</t>
         </is>
       </c>
       <c r="G230" s="7" t="inlineStr">
         <is>
-          <t>UKWYF [Reserved = +100]</t>
+          <t>EuropeMarketPlace [Reserved = +100]</t>
         </is>
       </c>
       <c r="H230" s="7" t="inlineStr">
@@ -12216,7 +12216,7 @@
       </c>
       <c r="C231" s="5" t="inlineStr">
         <is>
-          <t>[Logistics] Post Direct Wholesale AR Invoice (OINV) @ UKWYF → [Wayfair Revenue Recognition]</t>
+          <t>[Logistics] Post Direct Wholesale AR Invoice (OINV) @ EuropeMarketPlace → [EuropeMarketPlace Revenue Recognition]</t>
         </is>
       </c>
       <c r="D231" s="22" t="inlineStr">
@@ -12231,12 +12231,12 @@
       </c>
       <c r="F231" s="22" t="inlineStr">
         <is>
-          <t>UKWYF</t>
+          <t>EuropeMarketPlace</t>
         </is>
       </c>
       <c r="G231" s="5" t="inlineStr">
         <is>
-          <t>Wayfair Custody
+          <t>EuropeMarketPlace Custody
 [OnHand = 0]</t>
         </is>
       </c>
@@ -12250,14 +12250,14 @@
           <t>Dr 110010 (AR) $75,000
 Dr 500010 (COGS UK) $56,000
 Cr 400010 (Revenue) $75,000
-Cr 100040 (UKWYF) $56,000</t>
+Cr 100040 (EuropeMarketPlace) $56,000</t>
         </is>
       </c>
     </row>
     <row r="233" ht="24" customHeight="1">
       <c r="A233" s="21" t="inlineStr">
         <is>
-          <t>Process 2.3.4: Factory → ICC → UK Wayfair (Consolidated Movement Direct Wholesale Invoicing)</t>
+          <t>Process 2.3.4: Factory → ICC → EuropeMarketPlace (Consolidated Movement Direct Wholesale Invoicing)</t>
         </is>
       </c>
     </row>
@@ -12274,7 +12274,7 @@
       </c>
       <c r="C234" s="7" t="inlineStr">
         <is>
-          <t>[Purchasing] Issue Factory PO in USD (OPOR) @ ICCNGB → [Vendor Production Commitment]</t>
+          <t>[Purchasing] Issue Factory PO in USD (OPOR) @ ICCChina → [Vendor Production Commitment]</t>
         </is>
       </c>
       <c r="D234" s="23" t="inlineStr">
@@ -12289,7 +12289,7 @@
       </c>
       <c r="F234" s="23" t="inlineStr">
         <is>
-          <t>ICCNGB</t>
+          <t>ICCChina</t>
         </is>
       </c>
       <c r="G234" s="7" t="inlineStr">
@@ -12321,7 +12321,7 @@
       </c>
       <c r="C235" s="5" t="inlineStr">
         <is>
-          <t>[Logistics] Post Inward Factory GRPO (OPDN) @ ICCNGB → [Origin Spot FX Base Cost Capitalization]</t>
+          <t>[Logistics] Post Inward Factory GRPO (OPDN) @ ICCChina → [Origin Spot FX Base Cost Capitalization]</t>
         </is>
       </c>
       <c r="D235" s="22" t="inlineStr">
@@ -12336,12 +12336,12 @@
       </c>
       <c r="F235" s="22" t="inlineStr">
         <is>
-          <t>ICCNGB</t>
+          <t>ICCChina</t>
         </is>
       </c>
       <c r="G235" s="5" t="inlineStr">
         <is>
-          <t>ICCNGB [OnHand = 100]</t>
+          <t>ICCChina [OnHand = 100]</t>
         </is>
       </c>
       <c r="H235" s="5" t="inlineStr">
@@ -12368,7 +12368,7 @@
       </c>
       <c r="C236" s="7" t="inlineStr">
         <is>
-          <t>[Finance] Capitalize Origin Actual Landed Cost (OIPF 'A') @ ICCNGB → [Source MWAG Lock]</t>
+          <t>[Finance] Capitalize Origin Actual Landed Cost (OIPF 'A') @ ICCChina → [Source MWAG Lock]</t>
         </is>
       </c>
       <c r="D236" s="23" t="inlineStr">
@@ -12383,12 +12383,12 @@
       </c>
       <c r="F236" s="23" t="inlineStr">
         <is>
-          <t>ICCNGB</t>
+          <t>ICCChina</t>
         </is>
       </c>
       <c r="G236" s="7" t="inlineStr">
         <is>
-          <t>ICCNGB [OnHand = 100]</t>
+          <t>ICCChina [OnHand = 100]</t>
         </is>
       </c>
       <c r="H236" s="7" t="inlineStr">
@@ -12415,7 +12415,7 @@
       </c>
       <c r="C237" s="5" t="inlineStr">
         <is>
-          <t>[Purchasing] Create Export Transfer Request (OWTQ) @ ICCNGB → [UK Voyage Picking Allocation]</t>
+          <t>[Purchasing] Create Export Transfer Request (OWTQ) @ ICCChina → [UK Voyage Picking Allocation]</t>
         </is>
       </c>
       <c r="D237" s="22" t="inlineStr">
@@ -12430,12 +12430,12 @@
       </c>
       <c r="F237" s="22" t="inlineStr">
         <is>
-          <t>ICCNGB → UKSIT</t>
+          <t>ICCChina → EuropeSIT</t>
         </is>
       </c>
       <c r="G237" s="5" t="inlineStr">
         <is>
-          <t>ICCNGB [IsCommited = +100]</t>
+          <t>ICCChina [IsCommited = +100]</t>
         </is>
       </c>
       <c r="H237" s="5" t="inlineStr">
@@ -12462,7 +12462,7 @@
       </c>
       <c r="C238" s="7" t="inlineStr">
         <is>
-          <t>[Logistics] Post Ocean Transit Transfer (OWTR) based on OWTQ @ ICCNGB to UKSIT → [Maritime Voyage Tracking]</t>
+          <t>[Logistics] Post Ocean Transit Transfer (OWTR) based on OWTQ @ ICCChina to EuropeSIT → [Maritime Voyage Tracking]</t>
         </is>
       </c>
       <c r="D238" s="23" t="inlineStr">
@@ -12477,12 +12477,12 @@
       </c>
       <c r="F238" s="23" t="inlineStr">
         <is>
-          <t>ICCNGB → UKSIT</t>
+          <t>ICCChina → EuropeSIT</t>
         </is>
       </c>
       <c r="G238" s="7" t="inlineStr">
         <is>
-          <t>UKSIT [OnHand = 100]</t>
+          <t>EuropeSIT [OnHand = 100]</t>
         </is>
       </c>
       <c r="H238" s="7" t="inlineStr">
@@ -12492,7 +12492,7 @@
       </c>
       <c r="I238" s="7" t="inlineStr">
         <is>
-          <t>Dr 100050 (UKSIT) $42,400 / Cr 100040 ($42,400)</t>
+          <t>Dr 100050 (EuropeSIT) $42,400 / Cr 100040 ($42,400)</t>
         </is>
       </c>
     </row>
@@ -12509,7 +12509,7 @@
       </c>
       <c r="C239" s="5" t="inlineStr">
         <is>
-          <t>[Logistics] Post Inbound GRPO (OPDN) @ UKWYF → [UK Port Arrival Clearance]</t>
+          <t>[Logistics] Post Inbound GRPO (OPDN) @ EuropeMarketPlace → [UK Port Arrival Clearance]</t>
         </is>
       </c>
       <c r="D239" s="22" t="inlineStr">
@@ -12524,12 +12524,12 @@
       </c>
       <c r="F239" s="22" t="inlineStr">
         <is>
-          <t>UKWYF</t>
+          <t>EuropeMarketPlace</t>
         </is>
       </c>
       <c r="G239" s="5" t="inlineStr">
         <is>
-          <t>UKWYF [OnHand = 100]</t>
+          <t>EuropeMarketPlace [OnHand = 100]</t>
         </is>
       </c>
       <c r="H239" s="5" t="inlineStr">
@@ -12539,7 +12539,7 @@
       </c>
       <c r="I239" s="5" t="inlineStr">
         <is>
-          <t>Dr 100040 (UKWYF) $42,400 / Cr 100050 ($42,400)</t>
+          <t>Dr 100040 (EuropeMarketPlace) $42,400 / Cr 100050 ($42,400)</t>
         </is>
       </c>
     </row>
@@ -12556,7 +12556,7 @@
       </c>
       <c r="C240" s="7" t="inlineStr">
         <is>
-          <t>[Finance] Overwrite UK Landed Cost (OIPF 'A') @ UKWYF → [Final Stacked Valuation &amp; G/L 200050 Reconciled]</t>
+          <t>[Finance] Overwrite UK Landed Cost (OIPF 'A') @ EuropeMarketPlace → [Final Stacked Valuation &amp; G/L 200050 Reconciled]</t>
         </is>
       </c>
       <c r="D240" s="23" t="inlineStr">
@@ -12571,12 +12571,12 @@
       </c>
       <c r="F240" s="23" t="inlineStr">
         <is>
-          <t>UKWYF</t>
+          <t>EuropeMarketPlace</t>
         </is>
       </c>
       <c r="G240" s="7" t="inlineStr">
         <is>
-          <t>UKWYF [OnHand = 100]</t>
+          <t>EuropeMarketPlace [OnHand = 100]</t>
         </is>
       </c>
       <c r="H240" s="7" t="inlineStr">
@@ -12586,7 +12586,7 @@
       </c>
       <c r="I240" s="7" t="inlineStr">
         <is>
-          <t>Dr 100040 (UKWYF) $13,600 / Cr 200010 ($13,600)</t>
+          <t>Dr 100040 (EuropeMarketPlace) $13,600 / Cr 200010 ($13,600)</t>
         </is>
       </c>
     </row>
@@ -12603,7 +12603,7 @@
       </c>
       <c r="C241" s="5" t="inlineStr">
         <is>
-          <t>[Sales] Book Wayfair Wholesale Order (ORDR) @ UKWYF → [Finished Goods Allocation]</t>
+          <t>[Sales] Book EuropeMarketPlace Wholesale Order (ORDR) @ EuropeMarketPlace → [Finished Goods Allocation]</t>
         </is>
       </c>
       <c r="D241" s="22" t="inlineStr">
@@ -12618,12 +12618,12 @@
       </c>
       <c r="F241" s="22" t="inlineStr">
         <is>
-          <t>UKWYF</t>
+          <t>EuropeMarketPlace</t>
         </is>
       </c>
       <c r="G241" s="5" t="inlineStr">
         <is>
-          <t>UKWYF [Reserved = +100]</t>
+          <t>EuropeMarketPlace [Reserved = +100]</t>
         </is>
       </c>
       <c r="H241" s="5" t="inlineStr">
@@ -12650,7 +12650,7 @@
       </c>
       <c r="C242" s="7" t="inlineStr">
         <is>
-          <t>[Logistics] Post Direct Wholesale AR Invoice (OINV) @ UKWYF → [Wayfair Revenue Recognition]</t>
+          <t>[Logistics] Post Direct Wholesale AR Invoice (OINV) @ EuropeMarketPlace → [EuropeMarketPlace Revenue Recognition]</t>
         </is>
       </c>
       <c r="D242" s="23" t="inlineStr">
@@ -12665,12 +12665,12 @@
       </c>
       <c r="F242" s="23" t="inlineStr">
         <is>
-          <t>UKWYF</t>
+          <t>EuropeMarketPlace</t>
         </is>
       </c>
       <c r="G242" s="7" t="inlineStr">
         <is>
-          <t>Wayfair Custody
+          <t>EuropeMarketPlace Custody
 [OnHand = 0]</t>
         </is>
       </c>
@@ -12684,14 +12684,14 @@
           <t>Dr 110010 (AR) $75,000
 Dr 500010 (COGS UK) $56,000
 Cr 400010 (Revenue) $75,000
-Cr 100040 (UKWYF) $56,000</t>
+Cr 100040 (EuropeMarketPlace) $56,000</t>
         </is>
       </c>
     </row>
     <row r="244" ht="24" customHeight="1">
       <c r="A244" s="21" t="inlineStr">
         <is>
-          <t>Process 2.3.5: Factory → NZ Warehouse → UK Wayfair (NZ Hub Re-Export Direct Wholesale Invoicing)</t>
+          <t>Process 2.3.5: Factory → NZ Warehouse → EuropeMarketPlace (NZ Hub Re-Export Direct Wholesale Invoicing)</t>
         </is>
       </c>
     </row>
@@ -12864,7 +12864,7 @@
       </c>
       <c r="F248" s="23" t="inlineStr">
         <is>
-          <t>NZNTH → UKSIT</t>
+          <t>NZNTH → EuropeSIT</t>
         </is>
       </c>
       <c r="G248" s="7" t="inlineStr">
@@ -12896,7 +12896,7 @@
       </c>
       <c r="C249" s="5" t="inlineStr">
         <is>
-          <t>[Logistics] Post Maritime Transfer (OWTR) based on OWTQ @ NZNTH to UKSIT → [Re-Export Transit Tracking]</t>
+          <t>[Logistics] Post Maritime Transfer (OWTR) based on OWTQ @ NZNTH to EuropeSIT → [Re-Export Transit Tracking]</t>
         </is>
       </c>
       <c r="D249" s="22" t="inlineStr">
@@ -12911,12 +12911,12 @@
       </c>
       <c r="F249" s="22" t="inlineStr">
         <is>
-          <t>NZNTH → UKSIT</t>
+          <t>NZNTH → EuropeSIT</t>
         </is>
       </c>
       <c r="G249" s="5" t="inlineStr">
         <is>
-          <t>UKSIT [OnHand = 100]</t>
+          <t>EuropeSIT [OnHand = 100]</t>
         </is>
       </c>
       <c r="H249" s="5" t="inlineStr">
@@ -12926,7 +12926,7 @@
       </c>
       <c r="I249" s="5" t="inlineStr">
         <is>
-          <t>Dr 100050 (UKSIT) $52,200 / Cr 100040 ($52,200)</t>
+          <t>Dr 100050 (EuropeSIT) $52,200 / Cr 100040 ($52,200)</t>
         </is>
       </c>
     </row>
@@ -12943,7 +12943,7 @@
       </c>
       <c r="C250" s="7" t="inlineStr">
         <is>
-          <t>[Logistics] Post Inward GRPO (OPDN) @ UKWYF → [UK Port Arrival Inbound Clearance]</t>
+          <t>[Logistics] Post Inward GRPO (OPDN) @ EuropeMarketPlace → [UK Port Arrival Inbound Clearance]</t>
         </is>
       </c>
       <c r="D250" s="23" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="F250" s="23" t="inlineStr">
         <is>
-          <t>UKWYF</t>
+          <t>EuropeMarketPlace</t>
         </is>
       </c>
       <c r="G250" s="7" t="inlineStr">
         <is>
-          <t>UKWYF [OnHand = 100]</t>
+          <t>EuropeMarketPlace [OnHand = 100]</t>
         </is>
       </c>
       <c r="H250" s="7" t="inlineStr">
@@ -12973,7 +12973,7 @@
       </c>
       <c r="I250" s="7" t="inlineStr">
         <is>
-          <t>Dr 100040 (UKWYF) $52,200 / Cr 100050 ($52,200)</t>
+          <t>Dr 100040 (EuropeMarketPlace) $52,200 / Cr 100050 ($52,200)</t>
         </is>
       </c>
     </row>
@@ -12990,7 +12990,7 @@
       </c>
       <c r="C251" s="5" t="inlineStr">
         <is>
-          <t>[Finance] Capitalize UK Inbound Landed Cost (OIPF 'A') @ UKWYF → [Final Stacked Valuation &amp; G/L 200050 Reconciled]</t>
+          <t>[Finance] Capitalize UK Inbound Landed Cost (OIPF 'A') @ EuropeMarketPlace → [Final Stacked Valuation &amp; G/L 200050 Reconciled]</t>
         </is>
       </c>
       <c r="D251" s="22" t="inlineStr">
@@ -13005,12 +13005,12 @@
       </c>
       <c r="F251" s="22" t="inlineStr">
         <is>
-          <t>UKWYF</t>
+          <t>EuropeMarketPlace</t>
         </is>
       </c>
       <c r="G251" s="5" t="inlineStr">
         <is>
-          <t>UKWYF [OnHand = 100]</t>
+          <t>EuropeMarketPlace [OnHand = 100]</t>
         </is>
       </c>
       <c r="H251" s="5" t="inlineStr">
@@ -13020,7 +13020,7 @@
       </c>
       <c r="I251" s="5" t="inlineStr">
         <is>
-          <t>Dr 100040 (UKWYF) $3,800 / Cr 200010 ($3,800)</t>
+          <t>Dr 100040 (EuropeMarketPlace) $3,800 / Cr 200010 ($3,800)</t>
         </is>
       </c>
     </row>
@@ -13037,7 +13037,7 @@
       </c>
       <c r="C252" s="7" t="inlineStr">
         <is>
-          <t>[Sales] Book Wholesale Sales Order (ORDR) @ UKWYF → [Wayfair Channel Allocation]</t>
+          <t>[Sales] Book Wholesale Sales Order (ORDR) @ EuropeMarketPlace → [EuropeMarketPlace Channel Allocation]</t>
         </is>
       </c>
       <c r="D252" s="23" t="inlineStr">
@@ -13052,12 +13052,12 @@
       </c>
       <c r="F252" s="23" t="inlineStr">
         <is>
-          <t>UKWYF</t>
+          <t>EuropeMarketPlace</t>
         </is>
       </c>
       <c r="G252" s="7" t="inlineStr">
         <is>
-          <t>UKWYF [Reserved = +100]</t>
+          <t>EuropeMarketPlace [Reserved = +100]</t>
         </is>
       </c>
       <c r="H252" s="7" t="inlineStr">
@@ -13084,7 +13084,7 @@
       </c>
       <c r="C253" s="5" t="inlineStr">
         <is>
-          <t>[Logistics] Post Direct Wholesale AR Invoice (OINV) @ UKWYF → [Wayfair Channel Revenue Recognition]</t>
+          <t>[Logistics] Post Direct Wholesale AR Invoice (OINV) @ EuropeMarketPlace → [EuropeMarketPlace Channel Revenue Recognition]</t>
         </is>
       </c>
       <c r="D253" s="22" t="inlineStr">
@@ -13099,12 +13099,12 @@
       </c>
       <c r="F253" s="22" t="inlineStr">
         <is>
-          <t>UKWYF</t>
+          <t>EuropeMarketPlace</t>
         </is>
       </c>
       <c r="G253" s="5" t="inlineStr">
         <is>
-          <t>Wayfair Custody
+          <t>EuropeMarketPlace Custody
 [OnHand = 0]</t>
         </is>
       </c>
@@ -13122,7 +13122,7 @@
     <row r="255" ht="24" customHeight="1">
       <c r="A255" s="21" t="inlineStr">
         <is>
-          <t>Process 2.3.6: Factory → ICC → NZ Warehouse → UK Wayfair (Consolidated Transshipment Direct Wholesale Invoicing)</t>
+          <t>Process 2.3.6: Factory → ICC → NZ Warehouse → EuropeMarketPlace (Consolidated Transshipment Direct Wholesale Invoicing)</t>
         </is>
       </c>
     </row>
@@ -13139,7 +13139,7 @@
       </c>
       <c r="C256" s="7" t="inlineStr">
         <is>
-          <t>[Purchasing] Issue Factory PO in USD (OPOR) @ ICCNGB → [Vendor Production Commitment]</t>
+          <t>[Purchasing] Issue Factory PO in USD (OPOR) @ ICCChina → [Vendor Production Commitment]</t>
         </is>
       </c>
       <c r="D256" s="23" t="inlineStr">
@@ -13154,7 +13154,7 @@
       </c>
       <c r="F256" s="23" t="inlineStr">
         <is>
-          <t>ICCNGB</t>
+          <t>ICCChina</t>
         </is>
       </c>
       <c r="G256" s="7" t="inlineStr">
@@ -13186,7 +13186,7 @@
       </c>
       <c r="C257" s="5" t="inlineStr">
         <is>
-          <t>[Logistics] Post Inward Factory GRPO (OPDN) @ ICCNGB → [Origin Spot FX Base Cost Capitalization]</t>
+          <t>[Logistics] Post Inward Factory GRPO (OPDN) @ ICCChina → [Origin Spot FX Base Cost Capitalization]</t>
         </is>
       </c>
       <c r="D257" s="22" t="inlineStr">
@@ -13201,12 +13201,12 @@
       </c>
       <c r="F257" s="22" t="inlineStr">
         <is>
-          <t>ICCNGB</t>
+          <t>ICCChina</t>
         </is>
       </c>
       <c r="G257" s="5" t="inlineStr">
         <is>
-          <t>ICCNGB [OnHand = 100]</t>
+          <t>ICCChina [OnHand = 100]</t>
         </is>
       </c>
       <c r="H257" s="5" t="inlineStr">
@@ -13233,7 +13233,7 @@
       </c>
       <c r="C258" s="7" t="inlineStr">
         <is>
-          <t>[Finance] Capitalize Origin Actual Landed Cost (OIPF 'A') @ ICCNGB → [Source MWAG Lock]</t>
+          <t>[Finance] Capitalize Origin Actual Landed Cost (OIPF 'A') @ ICCChina → [Source MWAG Lock]</t>
         </is>
       </c>
       <c r="D258" s="23" t="inlineStr">
@@ -13248,12 +13248,12 @@
       </c>
       <c r="F258" s="23" t="inlineStr">
         <is>
-          <t>ICCNGB</t>
+          <t>ICCChina</t>
         </is>
       </c>
       <c r="G258" s="7" t="inlineStr">
         <is>
-          <t>ICCNGB [OnHand = 100]</t>
+          <t>ICCChina [OnHand = 100]</t>
         </is>
       </c>
       <c r="H258" s="7" t="inlineStr">
@@ -13280,7 +13280,7 @@
       </c>
       <c r="C259" s="5" t="inlineStr">
         <is>
-          <t>[Purchasing] Create Export Transfer Request (OWTQ) @ ICCNGB → [NZ Voyage Picking Allocation]</t>
+          <t>[Purchasing] Create Export Transfer Request (OWTQ) @ ICCChina → [NZ Voyage Picking Allocation]</t>
         </is>
       </c>
       <c r="D259" s="22" t="inlineStr">
@@ -13295,12 +13295,12 @@
       </c>
       <c r="F259" s="22" t="inlineStr">
         <is>
-          <t>ICCNGB → ICCSIT</t>
+          <t>ICCChina → ICCSIT</t>
         </is>
       </c>
       <c r="G259" s="5" t="inlineStr">
         <is>
-          <t>ICCNGB [IsCommited = +100]</t>
+          <t>ICCChina [IsCommited = +100]</t>
         </is>
       </c>
       <c r="H259" s="5" t="inlineStr">
@@ -13327,7 +13327,7 @@
       </c>
       <c r="C260" s="7" t="inlineStr">
         <is>
-          <t>[Logistics] Post Ocean Transit Transfer (OWTR) based on OWTQ @ ICCNGB to ICCSIT → [Sea Voyage Tracking]</t>
+          <t>[Logistics] Post Ocean Transit Transfer (OWTR) based on OWTQ @ ICCChina to ICCSIT → [Sea Voyage Tracking]</t>
         </is>
       </c>
       <c r="D260" s="23" t="inlineStr">
@@ -13342,7 +13342,7 @@
       </c>
       <c r="F260" s="23" t="inlineStr">
         <is>
-          <t>ICCNGB → ICCSIT</t>
+          <t>ICCChina → ICCSIT</t>
         </is>
       </c>
       <c r="G260" s="7" t="inlineStr">
@@ -13483,7 +13483,7 @@
       </c>
       <c r="F263" s="22" t="inlineStr">
         <is>
-          <t>NZNTH → UKSIT</t>
+          <t>NZNTH → EuropeSIT</t>
         </is>
       </c>
       <c r="G263" s="5" t="inlineStr">
@@ -13515,7 +13515,7 @@
       </c>
       <c r="C264" s="7" t="inlineStr">
         <is>
-          <t>[Logistics] Post UK Maritime Transfer (OWTR) based on OWTQ @ NZNTH to UKSIT → [Long-Haul Transit Tracking]</t>
+          <t>[Logistics] Post UK Maritime Transfer (OWTR) based on OWTQ @ NZNTH to EuropeSIT → [Long-Haul Transit Tracking]</t>
         </is>
       </c>
       <c r="D264" s="23" t="inlineStr">
@@ -13530,12 +13530,12 @@
       </c>
       <c r="F264" s="23" t="inlineStr">
         <is>
-          <t>NZNTH → UKSIT</t>
+          <t>NZNTH → EuropeSIT</t>
         </is>
       </c>
       <c r="G264" s="7" t="inlineStr">
         <is>
-          <t>UKSIT [OnHand = 100]</t>
+          <t>EuropeSIT [OnHand = 100]</t>
         </is>
       </c>
       <c r="H264" s="7" t="inlineStr">
@@ -13545,7 +13545,7 @@
       </c>
       <c r="I264" s="7" t="inlineStr">
         <is>
-          <t>Dr 100050 (UKSIT) $52,200 / Cr 100040 ($52,200)</t>
+          <t>Dr 100050 (EuropeSIT) $52,200 / Cr 100040 ($52,200)</t>
         </is>
       </c>
     </row>
@@ -13562,7 +13562,7 @@
       </c>
       <c r="C265" s="5" t="inlineStr">
         <is>
-          <t>[Logistics] Post UK Inward GRPO (OPDN) @ UKWYF → [UK Port Arrival Clearance]</t>
+          <t>[Logistics] Post UK Inward GRPO (OPDN) @ EuropeMarketPlace → [UK Port Arrival Clearance]</t>
         </is>
       </c>
       <c r="D265" s="22" t="inlineStr">
@@ -13577,12 +13577,12 @@
       </c>
       <c r="F265" s="22" t="inlineStr">
         <is>
-          <t>UKWYF</t>
+          <t>EuropeMarketPlace</t>
         </is>
       </c>
       <c r="G265" s="5" t="inlineStr">
         <is>
-          <t>UKWYF [OnHand = 100]</t>
+          <t>EuropeMarketPlace [OnHand = 100]</t>
         </is>
       </c>
       <c r="H265" s="5" t="inlineStr">
@@ -13592,7 +13592,7 @@
       </c>
       <c r="I265" s="5" t="inlineStr">
         <is>
-          <t>Dr 100040 (UKWYF) $52,200 / Cr 100050 ($52,200)</t>
+          <t>Dr 100040 (EuropeMarketPlace) $52,200 / Cr 100050 ($52,200)</t>
         </is>
       </c>
     </row>
@@ -13609,7 +13609,7 @@
       </c>
       <c r="C266" s="7" t="inlineStr">
         <is>
-          <t>[Finance] Capitalize UK Landed Cost (OIPF 'A') @ UKWYF → [Final Stacked Capitalization &amp; G/L 200050 Reconciled]</t>
+          <t>[Finance] Capitalize UK Landed Cost (OIPF 'A') @ EuropeMarketPlace → [Final Stacked Capitalization &amp; G/L 200050 Reconciled]</t>
         </is>
       </c>
       <c r="D266" s="23" t="inlineStr">
@@ -13624,12 +13624,12 @@
       </c>
       <c r="F266" s="23" t="inlineStr">
         <is>
-          <t>UKWYF</t>
+          <t>EuropeMarketPlace</t>
         </is>
       </c>
       <c r="G266" s="7" t="inlineStr">
         <is>
-          <t>UKWYF [OnHand = 100]</t>
+          <t>EuropeMarketPlace [OnHand = 100]</t>
         </is>
       </c>
       <c r="H266" s="7" t="inlineStr">
@@ -13639,7 +13639,7 @@
       </c>
       <c r="I266" s="7" t="inlineStr">
         <is>
-          <t>Dr 100040 (UKWYF) $3,800 / Cr 200010 ($3,800)</t>
+          <t>Dr 100040 (EuropeMarketPlace) $3,800 / Cr 200010 ($3,800)</t>
         </is>
       </c>
     </row>
@@ -13656,7 +13656,7 @@
       </c>
       <c r="C267" s="5" t="inlineStr">
         <is>
-          <t>[Sales] Book Wholesale Sales Order (ORDR) @ UKWYF → [Wayfair Channel Allocation]</t>
+          <t>[Sales] Book Wholesale Sales Order (ORDR) @ EuropeMarketPlace → [EuropeMarketPlace Channel Allocation]</t>
         </is>
       </c>
       <c r="D267" s="22" t="inlineStr">
@@ -13671,12 +13671,12 @@
       </c>
       <c r="F267" s="22" t="inlineStr">
         <is>
-          <t>UKWYF</t>
+          <t>EuropeMarketPlace</t>
         </is>
       </c>
       <c r="G267" s="5" t="inlineStr">
         <is>
-          <t>UKWYF [Reserved = +100]</t>
+          <t>EuropeMarketPlace [Reserved = +100]</t>
         </is>
       </c>
       <c r="H267" s="5" t="inlineStr">
@@ -13703,7 +13703,7 @@
       </c>
       <c r="C268" s="7" t="inlineStr">
         <is>
-          <t>[Logistics] Post Direct Wholesale AR Invoice (OINV) @ UKWYF → [Wayfair Channel Revenue Recognition]</t>
+          <t>[Logistics] Post Direct Wholesale AR Invoice (OINV) @ EuropeMarketPlace → [EuropeMarketPlace Channel Revenue Recognition]</t>
         </is>
       </c>
       <c r="D268" s="23" t="inlineStr">
@@ -13718,12 +13718,12 @@
       </c>
       <c r="F268" s="23" t="inlineStr">
         <is>
-          <t>UKWYF</t>
+          <t>EuropeMarketPlace</t>
         </is>
       </c>
       <c r="G268" s="7" t="inlineStr">
         <is>
-          <t>Wayfair Custody
+          <t>EuropeMarketPlace Custody
 [OnHand = 0]</t>
         </is>
       </c>
@@ -13758,7 +13758,7 @@
       </c>
       <c r="C271" s="5" t="inlineStr">
         <is>
-          <t>[Purchasing] Issue Factory PO in USD (OPOR) @ ICCNGB → [Vendor Production Commitment]</t>
+          <t>[Purchasing] Issue Factory PO in USD (OPOR) @ ICCChina → [Vendor Production Commitment]</t>
         </is>
       </c>
       <c r="D271" s="22" t="inlineStr">
@@ -13773,7 +13773,7 @@
       </c>
       <c r="F271" s="22" t="inlineStr">
         <is>
-          <t>ICCNGB</t>
+          <t>ICCChina</t>
         </is>
       </c>
       <c r="G271" s="5" t="inlineStr">
@@ -13805,7 +13805,7 @@
       </c>
       <c r="C272" s="7" t="inlineStr">
         <is>
-          <t>[Logistics] Post Inward Factory GRPO (OPDN) @ ICCNGB → [Base Cost Capitalization]</t>
+          <t>[Logistics] Post Inward Factory GRPO (OPDN) @ ICCChina → [Base Cost Capitalization]</t>
         </is>
       </c>
       <c r="D272" s="23" t="inlineStr">
@@ -13820,12 +13820,12 @@
       </c>
       <c r="F272" s="23" t="inlineStr">
         <is>
-          <t>ICCNGB</t>
+          <t>ICCChina</t>
         </is>
       </c>
       <c r="G272" s="7" t="inlineStr">
         <is>
-          <t>ICCNGB [OnHand = 100]</t>
+          <t>ICCChina [OnHand = 100]</t>
         </is>
       </c>
       <c r="H272" s="7" t="inlineStr">
@@ -13835,7 +13835,7 @@
       </c>
       <c r="I272" s="7" t="inlineStr">
         <is>
-          <t>Dr 100040 (ICCNGB) $40,000 / Cr 200060 $40,000</t>
+          <t>Dr 100040 (ICCChina) $40,000 / Cr 200060 $40,000</t>
         </is>
       </c>
     </row>
@@ -13852,7 +13852,7 @@
       </c>
       <c r="C273" s="5" t="inlineStr">
         <is>
-          <t>[Finance] Capitalize Air Freight Landed Cost (OIPF 'A') @ ICCNGB → [Drop-Ship Valuation &amp; G/L 200050 Reconciled]</t>
+          <t>[Finance] Capitalize Air Freight Landed Cost (OIPF 'A') @ ICCChina → [Drop-Ship Valuation &amp; G/L 200050 Reconciled]</t>
         </is>
       </c>
       <c r="D273" s="22" t="inlineStr">
@@ -13867,12 +13867,12 @@
       </c>
       <c r="F273" s="22" t="inlineStr">
         <is>
-          <t>ICCNGB</t>
+          <t>ICCChina</t>
         </is>
       </c>
       <c r="G273" s="5" t="inlineStr">
         <is>
-          <t>ICCNGB [OnHand = 100]</t>
+          <t>ICCChina [OnHand = 100]</t>
         </is>
       </c>
       <c r="H273" s="5" t="inlineStr">
@@ -13882,7 +13882,7 @@
       </c>
       <c r="I273" s="5" t="inlineStr">
         <is>
-          <t>Dr 100040 (ICCNGB) $18,000 / Cr 200010 $18,000</t>
+          <t>Dr 100040 (ICCChina) $18,000 / Cr 200010 $18,000</t>
         </is>
       </c>
     </row>
@@ -13899,7 +13899,7 @@
       </c>
       <c r="C274" s="7" t="inlineStr">
         <is>
-          <t>[Sales] Book D2C Consumer Sales Order (ORDR) @ ICCNGB → [AU Consumer Stock Allocation]</t>
+          <t>[Sales] Book D2C Consumer Sales Order (ORDR) @ ICCChina → [AU Consumer Stock Allocation]</t>
         </is>
       </c>
       <c r="D274" s="23" t="inlineStr">
@@ -13914,12 +13914,12 @@
       </c>
       <c r="F274" s="23" t="inlineStr">
         <is>
-          <t>ICCNGB</t>
+          <t>ICCChina</t>
         </is>
       </c>
       <c r="G274" s="7" t="inlineStr">
         <is>
-          <t>ICCNGB [Reserved = +100]</t>
+          <t>ICCChina [Reserved = +100]</t>
         </is>
       </c>
       <c r="H274" s="7" t="inlineStr">
@@ -13946,7 +13946,7 @@
       </c>
       <c r="C275" s="5" t="inlineStr">
         <is>
-          <t>[Logistics] Post Direct AR Tax Invoice (OINV) @ ICCNGB → [Direct Air Dispatch &amp; Revenue Recognition]</t>
+          <t>[Logistics] Post Direct AR Tax Invoice (OINV) @ ICCChina → [Direct Air Dispatch &amp; Revenue Recognition]</t>
         </is>
       </c>
       <c r="D275" s="22" t="inlineStr">
@@ -13961,13 +13961,13 @@
       </c>
       <c r="F275" s="22" t="inlineStr">
         <is>
-          <t>ICCNGB</t>
+          <t>ICCChina</t>
         </is>
       </c>
       <c r="G275" s="5" t="inlineStr">
         <is>
           <t>Customer Custody
-[ICCNGB OnHand = 0]</t>
+[ICCChina OnHand = 0]</t>
         </is>
       </c>
       <c r="H275" s="5" t="inlineStr">
@@ -13980,7 +13980,7 @@
           <t>Dr 110010 ($95,000)
 Dr 500010 (COGS D2C) $58,000
 Cr 400010 (Revenue) $95,000
-Cr 100040 (ICCNGB) $58,000</t>
+Cr 100040 (ICCChina) $58,000</t>
         </is>
       </c>
     </row>
@@ -14004,7 +14004,7 @@
       </c>
       <c r="C278" s="7" t="inlineStr">
         <is>
-          <t>[Purchasing] Issue Factory PO in USD (OPOR) @ ICCNGB → [Vendor Production Commitment]</t>
+          <t>[Purchasing] Issue Factory PO in USD (OPOR) @ ICCChina → [Vendor Production Commitment]</t>
         </is>
       </c>
       <c r="D278" s="23" t="inlineStr">
@@ -14019,7 +14019,7 @@
       </c>
       <c r="F278" s="23" t="inlineStr">
         <is>
-          <t>ICCNGB</t>
+          <t>ICCChina</t>
         </is>
       </c>
       <c r="G278" s="7" t="inlineStr">
@@ -14051,7 +14051,7 @@
       </c>
       <c r="C279" s="5" t="inlineStr">
         <is>
-          <t>[Logistics] Post Inward Factory GRPO (OPDN) @ ICCNGB → [Base Cost Capitalization]</t>
+          <t>[Logistics] Post Inward Factory GRPO (OPDN) @ ICCChina → [Base Cost Capitalization]</t>
         </is>
       </c>
       <c r="D279" s="22" t="inlineStr">
@@ -14066,12 +14066,12 @@
       </c>
       <c r="F279" s="22" t="inlineStr">
         <is>
-          <t>ICCNGB</t>
+          <t>ICCChina</t>
         </is>
       </c>
       <c r="G279" s="5" t="inlineStr">
         <is>
-          <t>ICCNGB [OnHand = 100]</t>
+          <t>ICCChina [OnHand = 100]</t>
         </is>
       </c>
       <c r="H279" s="5" t="inlineStr">
@@ -14081,7 +14081,7 @@
       </c>
       <c r="I279" s="5" t="inlineStr">
         <is>
-          <t>Dr 100040 (ICCNGB) $40,000 / Cr 200060 $40,000</t>
+          <t>Dr 100040 (ICCChina) $40,000 / Cr 200060 $40,000</t>
         </is>
       </c>
     </row>
@@ -14098,7 +14098,7 @@
       </c>
       <c r="C280" s="7" t="inlineStr">
         <is>
-          <t>[Finance] Capitalize Air Freight Landed Cost (OIPF 'A') @ ICCNGB → [Drop-Ship Valuation &amp; G/L 200050 Reconciled]</t>
+          <t>[Finance] Capitalize Air Freight Landed Cost (OIPF 'A') @ ICCChina → [Drop-Ship Valuation &amp; G/L 200050 Reconciled]</t>
         </is>
       </c>
       <c r="D280" s="23" t="inlineStr">
@@ -14113,12 +14113,12 @@
       </c>
       <c r="F280" s="23" t="inlineStr">
         <is>
-          <t>ICCNGB</t>
+          <t>ICCChina</t>
         </is>
       </c>
       <c r="G280" s="7" t="inlineStr">
         <is>
-          <t>ICCNGB [OnHand = 100]</t>
+          <t>ICCChina [OnHand = 100]</t>
         </is>
       </c>
       <c r="H280" s="7" t="inlineStr">
@@ -14128,7 +14128,7 @@
       </c>
       <c r="I280" s="7" t="inlineStr">
         <is>
-          <t>Dr 100040 (ICCNGB) $18,000 / Cr 200010 $18,000</t>
+          <t>Dr 100040 (ICCChina) $18,000 / Cr 200010 $18,000</t>
         </is>
       </c>
     </row>
@@ -14145,7 +14145,7 @@
       </c>
       <c r="C281" s="5" t="inlineStr">
         <is>
-          <t>[Sales] Book D2C Consumer Sales Order (ORDR) @ ICCNGB → [NZ Consumer Stock Allocation]</t>
+          <t>[Sales] Book D2C Consumer Sales Order (ORDR) @ ICCChina → [NZ Consumer Stock Allocation]</t>
         </is>
       </c>
       <c r="D281" s="22" t="inlineStr">
@@ -14160,12 +14160,12 @@
       </c>
       <c r="F281" s="22" t="inlineStr">
         <is>
-          <t>ICCNGB</t>
+          <t>ICCChina</t>
         </is>
       </c>
       <c r="G281" s="5" t="inlineStr">
         <is>
-          <t>ICCNGB [Reserved = +100]</t>
+          <t>ICCChina [Reserved = +100]</t>
         </is>
       </c>
       <c r="H281" s="5" t="inlineStr">
@@ -14192,7 +14192,7 @@
       </c>
       <c r="C282" s="7" t="inlineStr">
         <is>
-          <t>[Logistics] Post Direct AR Tax Invoice (OINV) @ ICCNGB → [Direct Air Dispatch &amp; Revenue Recognition]</t>
+          <t>[Logistics] Post Direct AR Tax Invoice (OINV) @ ICCChina → [Direct Air Dispatch &amp; Revenue Recognition]</t>
         </is>
       </c>
       <c r="D282" s="23" t="inlineStr">
@@ -14207,13 +14207,13 @@
       </c>
       <c r="F282" s="23" t="inlineStr">
         <is>
-          <t>ICCNGB</t>
+          <t>ICCChina</t>
         </is>
       </c>
       <c r="G282" s="7" t="inlineStr">
         <is>
           <t>Customer Custody
-[ICCNGB OnHand = 0]</t>
+[ICCChina OnHand = 0]</t>
         </is>
       </c>
       <c r="H282" s="7" t="inlineStr">
@@ -14226,7 +14226,7 @@
           <t>Dr 110010 ($95,000)
 Dr 500010 (COGS D2C) $58,000
 Cr 400010 (Revenue) $95,000
-Cr 100040 (ICCNGB) $58,000</t>
+Cr 100040 (ICCChina) $58,000</t>
         </is>
       </c>
     </row>
@@ -14250,7 +14250,7 @@
       </c>
       <c r="C285" s="5" t="inlineStr">
         <is>
-          <t>[Purchasing] Issue Factory PO in USD (OPOR) @ ICCNGB → [Vendor Production Commitment]</t>
+          <t>[Purchasing] Issue Factory PO in USD (OPOR) @ ICCChina → [Vendor Production Commitment]</t>
         </is>
       </c>
       <c r="D285" s="22" t="inlineStr">
@@ -14265,7 +14265,7 @@
       </c>
       <c r="F285" s="22" t="inlineStr">
         <is>
-          <t>ICCNGB</t>
+          <t>ICCChina</t>
         </is>
       </c>
       <c r="G285" s="5" t="inlineStr">
@@ -14297,7 +14297,7 @@
       </c>
       <c r="C286" s="7" t="inlineStr">
         <is>
-          <t>[Logistics] Post Inward Factory GRPO (OPDN) @ ICCNGB → [Base Cost Capitalization]</t>
+          <t>[Logistics] Post Inward Factory GRPO (OPDN) @ ICCChina → [Base Cost Capitalization]</t>
         </is>
       </c>
       <c r="D286" s="23" t="inlineStr">
@@ -14312,12 +14312,12 @@
       </c>
       <c r="F286" s="23" t="inlineStr">
         <is>
-          <t>ICCNGB</t>
+          <t>ICCChina</t>
         </is>
       </c>
       <c r="G286" s="7" t="inlineStr">
         <is>
-          <t>ICCNGB [OnHand = 100]</t>
+          <t>ICCChina [OnHand = 100]</t>
         </is>
       </c>
       <c r="H286" s="7" t="inlineStr">
@@ -14327,7 +14327,7 @@
       </c>
       <c r="I286" s="7" t="inlineStr">
         <is>
-          <t>Dr 100040 (ICCNGB) $40,000 / Cr 200060 $40,000</t>
+          <t>Dr 100040 (ICCChina) $40,000 / Cr 200060 $40,000</t>
         </is>
       </c>
     </row>
@@ -14344,7 +14344,7 @@
       </c>
       <c r="C287" s="5" t="inlineStr">
         <is>
-          <t>[Finance] Capitalize Air Freight Landed Cost (OIPF 'A') @ ICCNGB → [Drop-Ship Valuation &amp; G/L 200050 Reconciled]</t>
+          <t>[Finance] Capitalize Air Freight Landed Cost (OIPF 'A') @ ICCChina → [Drop-Ship Valuation &amp; G/L 200050 Reconciled]</t>
         </is>
       </c>
       <c r="D287" s="22" t="inlineStr">
@@ -14359,12 +14359,12 @@
       </c>
       <c r="F287" s="22" t="inlineStr">
         <is>
-          <t>ICCNGB</t>
+          <t>ICCChina</t>
         </is>
       </c>
       <c r="G287" s="5" t="inlineStr">
         <is>
-          <t>ICCNGB [OnHand = 100]</t>
+          <t>ICCChina [OnHand = 100]</t>
         </is>
       </c>
       <c r="H287" s="5" t="inlineStr">
@@ -14374,7 +14374,7 @@
       </c>
       <c r="I287" s="5" t="inlineStr">
         <is>
-          <t>Dr 100040 (ICCNGB) $19,500 / Cr 200010 $19,500</t>
+          <t>Dr 100040 (ICCChina) $19,500 / Cr 200010 $19,500</t>
         </is>
       </c>
     </row>
@@ -14391,7 +14391,7 @@
       </c>
       <c r="C288" s="7" t="inlineStr">
         <is>
-          <t>[Sales] Book D2C Consumer Sales Order (ORDR) @ ICCNGB → [UK Consumer Stock Allocation]</t>
+          <t>[Sales] Book D2C Consumer Sales Order (ORDR) @ ICCChina → [UK Consumer Stock Allocation]</t>
         </is>
       </c>
       <c r="D288" s="23" t="inlineStr">
@@ -14406,12 +14406,12 @@
       </c>
       <c r="F288" s="23" t="inlineStr">
         <is>
-          <t>ICCNGB</t>
+          <t>ICCChina</t>
         </is>
       </c>
       <c r="G288" s="7" t="inlineStr">
         <is>
-          <t>ICCNGB [Reserved = +100]</t>
+          <t>ICCChina [Reserved = +100]</t>
         </is>
       </c>
       <c r="H288" s="7" t="inlineStr">
@@ -14438,7 +14438,7 @@
       </c>
       <c r="C289" s="5" t="inlineStr">
         <is>
-          <t>[Logistics] Post Direct AR Tax Invoice (OINV) @ ICCNGB → [Direct Air Dispatch &amp; Revenue Recognition]</t>
+          <t>[Logistics] Post Direct AR Tax Invoice (OINV) @ ICCChina → [Direct Air Dispatch &amp; Revenue Recognition]</t>
         </is>
       </c>
       <c r="D289" s="22" t="inlineStr">
@@ -14453,13 +14453,13 @@
       </c>
       <c r="F289" s="22" t="inlineStr">
         <is>
-          <t>ICCNGB</t>
+          <t>ICCChina</t>
         </is>
       </c>
       <c r="G289" s="5" t="inlineStr">
         <is>
           <t>Customer Custody
-[ICCNGB OnHand = 0]</t>
+[ICCChina OnHand = 0]</t>
         </is>
       </c>
       <c r="H289" s="5" t="inlineStr">
@@ -14472,7 +14472,7 @@
           <t>Dr 110010 ($98,000)
 Dr 500010 (COGS D2C) $59,500
 Cr 400010 (Revenue) $98,000
-Cr 100040 (ICCNGB) $59,500</t>
+Cr 100040 (ICCChina) $59,500</t>
         </is>
       </c>
     </row>
@@ -14503,7 +14503,7 @@
       </c>
       <c r="C294" s="7" t="inlineStr">
         <is>
-          <t>[Purchasing] Cancel Origin Factory PO Line (OPOR) @ ICCNGB → [Commitment Release]</t>
+          <t>[Purchasing] Cancel Origin Factory PO Line (OPOR) @ ICCChina → [Commitment Release]</t>
         </is>
       </c>
       <c r="D294" s="23" t="inlineStr">
@@ -14518,7 +14518,7 @@
       </c>
       <c r="F294" s="23" t="inlineStr">
         <is>
-          <t>ICCNGB</t>
+          <t>ICCChina</t>
         </is>
       </c>
       <c r="G294" s="7" t="inlineStr">
@@ -14550,7 +14550,7 @@
       </c>
       <c r="C295" s="5" t="inlineStr">
         <is>
-          <t>[Purchasing] Re-Issue Direct Factory PO in USD (OPOR) @ FDMSYD → [AU Commitment Establishment]</t>
+          <t>[Purchasing] Re-Issue Direct Factory PO in USD (OPOR) @ AU Warehouse → [AU Commitment Establishment]</t>
         </is>
       </c>
       <c r="D295" s="22" t="inlineStr">
@@ -14565,7 +14565,7 @@
       </c>
       <c r="F295" s="22" t="inlineStr">
         <is>
-          <t>FDMSYD</t>
+          <t>AU Warehouse</t>
         </is>
       </c>
       <c r="G295" s="5" t="inlineStr">
@@ -14575,7 +14575,7 @@
       </c>
       <c r="H295" s="5" t="inlineStr">
         <is>
-          <t>Re-issues PO in USD targeting FDMSYD/BDLMEL in old_b1.db</t>
+          <t>Re-issues PO in USD targeting AU Warehouses in old_b1.db</t>
         </is>
       </c>
       <c r="I295" s="5" t="inlineStr">
@@ -14597,7 +14597,7 @@
       </c>
       <c r="C296" s="7" t="inlineStr">
         <is>
-          <t>[Logistics] Post Inward GRPO (OPDN) @ FDMSYD → [Direct AU Base Capitalization]</t>
+          <t>[Logistics] Post Inward GRPO (OPDN) @ AU Warehouse → [Direct AU Base Capitalization]</t>
         </is>
       </c>
       <c r="D296" s="23" t="inlineStr">
@@ -14612,12 +14612,12 @@
       </c>
       <c r="F296" s="23" t="inlineStr">
         <is>
-          <t>FDMSYD</t>
+          <t>AU Warehouse</t>
         </is>
       </c>
       <c r="G296" s="7" t="inlineStr">
         <is>
-          <t>FDMSYD [OnHand=100]</t>
+          <t>AU Warehouse [OnHand=100]</t>
         </is>
       </c>
       <c r="H296" s="7" t="inlineStr">
@@ -14644,7 +14644,7 @@
       </c>
       <c r="C297" s="5" t="inlineStr">
         <is>
-          <t>[Finance] Capitalize Destination Landed Cost (OIPF 'A') @ FDMSYD → [Final AU Stock Valuation &amp; G/L 200050 Reconciled]</t>
+          <t>[Finance] Capitalize Destination Landed Cost (OIPF 'A') @ AU Warehouse → [Final AU Stock Valuation &amp; G/L 200050 Reconciled]</t>
         </is>
       </c>
       <c r="D297" s="22" t="inlineStr">
@@ -14659,12 +14659,12 @@
       </c>
       <c r="F297" s="22" t="inlineStr">
         <is>
-          <t>FDMSYD</t>
+          <t>AU Warehouse</t>
         </is>
       </c>
       <c r="G297" s="5" t="inlineStr">
         <is>
-          <t>FDMSYD [OnHand=100]</t>
+          <t>AU Warehouse [OnHand=100]</t>
         </is>
       </c>
       <c r="H297" s="5" t="inlineStr">
@@ -14698,7 +14698,7 @@
       </c>
       <c r="C300" s="7" t="inlineStr">
         <is>
-          <t>[Purchasing] Cancel Direct AU PO Line (OPOR) @ FDMSYD → [Direct Commitment Release]</t>
+          <t>[Purchasing] Cancel Direct AU PO Line (OPOR) @ AU Warehouse → [Direct Commitment Release]</t>
         </is>
       </c>
       <c r="D300" s="23" t="inlineStr">
@@ -14713,7 +14713,7 @@
       </c>
       <c r="F300" s="23" t="inlineStr">
         <is>
-          <t>FDMSYD</t>
+          <t>AU Warehouse</t>
         </is>
       </c>
       <c r="G300" s="7" t="inlineStr">
@@ -14745,7 +14745,7 @@
       </c>
       <c r="C301" s="5" t="inlineStr">
         <is>
-          <t>[Purchasing] Issue Replacement Factory PO in USD (OPOR) @ ICCNGB → [Origin Consolidation Commitment]</t>
+          <t>[Purchasing] Issue Replacement Factory PO in USD (OPOR) @ ICCChina → [Origin Consolidation Commitment]</t>
         </is>
       </c>
       <c r="D301" s="22" t="inlineStr">
@@ -14760,7 +14760,7 @@
       </c>
       <c r="F301" s="22" t="inlineStr">
         <is>
-          <t>ICCNGB</t>
+          <t>ICCChina</t>
         </is>
       </c>
       <c r="G301" s="5" t="inlineStr">
@@ -14770,7 +14770,7 @@
       </c>
       <c r="H301" s="5" t="inlineStr">
         <is>
-          <t>Issues replacement PO in USD committed to ICCNGB hub</t>
+          <t>Issues replacement PO in USD committed to ICCChina hub</t>
         </is>
       </c>
       <c r="I301" s="5" t="inlineStr">
@@ -14792,7 +14792,7 @@
       </c>
       <c r="C302" s="7" t="inlineStr">
         <is>
-          <t>[Logistics] Post Inward Factory GRPO (OPDN) @ ICCNGB → [Base Cost Capitalization]</t>
+          <t>[Logistics] Post Inward Factory GRPO (OPDN) @ ICCChina → [Base Cost Capitalization]</t>
         </is>
       </c>
       <c r="D302" s="23" t="inlineStr">
@@ -14807,12 +14807,12 @@
       </c>
       <c r="F302" s="23" t="inlineStr">
         <is>
-          <t>ICCNGB</t>
+          <t>ICCChina</t>
         </is>
       </c>
       <c r="G302" s="7" t="inlineStr">
         <is>
-          <t>ICCNGB [OnHand=100]</t>
+          <t>ICCChina [OnHand=100]</t>
         </is>
       </c>
       <c r="H302" s="7" t="inlineStr">
@@ -14839,7 +14839,7 @@
       </c>
       <c r="C303" s="5" t="inlineStr">
         <is>
-          <t>[Finance] Capitalize Origin Landed Cost (OIPF 'A') @ ICCNGB → [Origin Hub Capitalization &amp; G/L 200050 Reconciled]</t>
+          <t>[Finance] Capitalize Origin Landed Cost (OIPF 'A') @ ICCChina → [Origin Hub Capitalization &amp; G/L 200050 Reconciled]</t>
         </is>
       </c>
       <c r="D303" s="22" t="inlineStr">
@@ -14854,12 +14854,12 @@
       </c>
       <c r="F303" s="22" t="inlineStr">
         <is>
-          <t>ICCNGB</t>
+          <t>ICCChina</t>
         </is>
       </c>
       <c r="G303" s="5" t="inlineStr">
         <is>
-          <t>ICCNGB [OnHand=100]</t>
+          <t>ICCChina [OnHand=100]</t>
         </is>
       </c>
       <c r="H303" s="5" t="inlineStr">
@@ -14893,7 +14893,7 @@
       </c>
       <c r="C306" s="7" t="inlineStr">
         <is>
-          <t>[Logistics] Log Physical Container Discrepancy (OPDN Audit) @ FDMSYD → [Variance Identification]</t>
+          <t>[Logistics] Log Physical Container Discrepancy (OPDN Audit) @ AU Warehouse → [Variance Identification]</t>
         </is>
       </c>
       <c r="D306" s="23" t="inlineStr">
@@ -14908,7 +14908,7 @@
       </c>
       <c r="F306" s="23" t="inlineStr">
         <is>
-          <t>FDMSYD</t>
+          <t>AU Warehouse</t>
         </is>
       </c>
       <c r="G306" s="7" t="inlineStr">
@@ -14940,7 +14940,7 @@
       </c>
       <c r="C307" s="5" t="inlineStr">
         <is>
-          <t>[Logistics] Post Partial Inbound GRPO (OPDN) @ FDMSYD → [Actual Delivered Stock Receipt]</t>
+          <t>[Logistics] Post Partial Inbound GRPO (OPDN) @ AU Warehouse → [Actual Delivered Stock Receipt]</t>
         </is>
       </c>
       <c r="D307" s="22" t="inlineStr">
@@ -14955,12 +14955,12 @@
       </c>
       <c r="F307" s="22" t="inlineStr">
         <is>
-          <t>FDMSYD</t>
+          <t>AU Warehouse</t>
         </is>
       </c>
       <c r="G307" s="5" t="inlineStr">
         <is>
-          <t>FDMSYD [OnHand=95]</t>
+          <t>AU Warehouse [OnHand=95]</t>
         </is>
       </c>
       <c r="H307" s="5" t="inlineStr">
@@ -15034,7 +15034,7 @@
       </c>
       <c r="C309" s="5" t="inlineStr">
         <is>
-          <t>[Logistics] Post Surplus Inward GRPO &amp; Supplementary Invoice (OPDN/OINV) @ FDMSYD &amp; ICCNGB → [Surplus Settlement]</t>
+          <t>[Logistics] Post Surplus Inward GRPO &amp; Supplementary Invoice (OPDN/OINV) @ AU Warehouse &amp; ICCChina → [Surplus Settlement]</t>
         </is>
       </c>
       <c r="D309" s="22" t="inlineStr">
@@ -15049,12 +15049,12 @@
       </c>
       <c r="F309" s="22" t="inlineStr">
         <is>
-          <t>FDMSYD &amp; ICCNGB</t>
+          <t>AU Warehouse &amp; ICCChina</t>
         </is>
       </c>
       <c r="G309" s="5" t="inlineStr">
         <is>
-          <t>FDMSYD [OnHand=105]</t>
+          <t>AU Warehouse [OnHand=105]</t>
         </is>
       </c>
       <c r="H309" s="5" t="inlineStr">
@@ -15215,7 +15215,7 @@
       </c>
       <c r="H316" s="7" t="inlineStr">
         <is>
-          <t>Verify all open ICCSIT/NZSIT/UKSIT quantities match un-discharged B/L shipments</t>
+          <t>Verify all open ICCSIT/NZSIT/EuropeSIT quantities match un-discharged B/L shipments</t>
         </is>
       </c>
       <c r="I316" s="7" t="inlineStr">
